--- a/Grille_collecte_test_operateur2.xlsx
+++ b/Grille_collecte_test_operateur2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louau\Projets\Ademe_RCP_FAI\modele-rcp-fai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aubet Louise\Projet\Ademe_RCP_FAI\modele-rcp-fai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF83F1DB-ABAC-4621-BB62-9BB8768C1B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56135205-6242-4C96-A973-2D8253C2323B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="achats_2022" sheetId="4" r:id="rId2"/>
     <sheet name="démontage_2022" sheetId="14" r:id="rId3"/>
     <sheet name="parc_entier" sheetId="15" r:id="rId4"/>
-    <sheet name="données_supplémentaires" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -800,7 +799,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="158">
   <si>
     <t>Câble cuivre</t>
   </si>
@@ -1519,15 +1518,6 @@
   </si>
   <si>
     <t>Cela signifie que l'opérateur A possède 100 routeurs dont 50 sont reconditionnés.</t>
-  </si>
-  <si>
-    <t>Nombre d'abonné.es</t>
-  </si>
-  <si>
-    <t>Quantité de données échangées (To)</t>
-  </si>
-  <si>
-    <t>Moyenne sur l'année 2022</t>
   </si>
   <si>
     <t>Impacts environnementaux (ACV équipementiers)</t>
@@ -1990,52 +1980,6 @@
     <t>Boucle locale fibre</t>
   </si>
   <si>
-    <t>7170000 (FTTH)
-5176000 (xDSL)</t>
-  </si>
-  <si>
-    <t>26894203,602 (Traffic downlink uniquement, exclut des petits trucs style VoD, VoIP)
-29185245330 (Traffic Uplink+Downlink)</t>
-  </si>
-  <si>
-    <t>25231645.8181818 (Active mobile data subscribers)
-2167526 (MVNO subscribers)</t>
-  </si>
-  <si>
-    <t>3215400.43859395 (Access Traffic = compte le trafic des clients Orange/Sosh en France + abonnés étrangers qui font du roaming sur le réseau d'Orange France + abonnés MVNO sur réseau Orange, mais pas les abonnés Orange (ou MVNO sur réseau Orange) qui sont à l'étranger)
-2550932091.809 (Core Traffic = compte le trafic des clients Orange/Sosh partout où ils sont dans le monde)</t>
-  </si>
-  <si>
-    <t>Réseau d'accès fixe</t>
-  </si>
-  <si>
-    <t>Réseaux collecte et transport</t>
-  </si>
-  <si>
-    <t>Réseaux d'accès opérateurs tiers</t>
-  </si>
-  <si>
-    <t>IT &amp; Plateformes de service (environ la moitié représente des éqts nécessaires au réseau télécom)</t>
-  </si>
-  <si>
-    <t>Conso électrique 2022 (en MWh)</t>
-  </si>
-  <si>
-    <t>Données ne comprenant pas l'environnement technique (je préconise de rajouter 20% sur chaque poste pour prendre en compte l'environnement technique)</t>
-  </si>
-  <si>
-    <t>Conso elec fixe (MWh)</t>
-  </si>
-  <si>
-    <t>Conso elec mobile (MWh)</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Valeurs utilisées</t>
-  </si>
-  <si>
     <t>operateur2, 50 / operateur3, 60 / operateur1, 30</t>
   </si>
 </sst>
@@ -2046,7 +1990,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2200,12 +2144,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2227,7 +2165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -2701,17 +2639,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2819,7 +2746,7 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2940,25 +2867,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2997,7 +2915,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3045,13 +2963,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3082,7 +3000,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3118,19 +3036,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3148,13 +3066,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3170,7 +3088,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3186,16 +3104,6 @@
     <xf numFmtId="1" fontId="4" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3211,23 +3119,26 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3253,47 +3164,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3698,12 +3573,12 @@
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.35">
@@ -3777,16 +3652,16 @@
     </row>
     <row r="30" spans="2:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="39"/>
-      <c r="C30" s="168" t="s">
+      <c r="C30" s="164" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="168"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="168"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="168"/>
-      <c r="J30" s="168"/>
+      <c r="D30" s="164"/>
+      <c r="E30" s="164"/>
+      <c r="F30" s="164"/>
+      <c r="G30" s="164"/>
+      <c r="H30" s="164"/>
+      <c r="I30" s="164"/>
+      <c r="J30" s="164"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="39"/>
@@ -3844,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3874,30 +3749,30 @@
       <c r="C43" s="39"/>
     </row>
     <row r="44" spans="2:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="168" t="s">
+      <c r="B44" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="168"/>
-      <c r="D44" s="168"/>
-      <c r="E44" s="168"/>
-      <c r="F44" s="168"/>
-      <c r="G44" s="168"/>
-      <c r="H44" s="168"/>
-      <c r="I44" s="168"/>
-      <c r="J44" s="168"/>
+      <c r="C44" s="164"/>
+      <c r="D44" s="164"/>
+      <c r="E44" s="164"/>
+      <c r="F44" s="164"/>
+      <c r="G44" s="164"/>
+      <c r="H44" s="164"/>
+      <c r="I44" s="164"/>
+      <c r="J44" s="164"/>
     </row>
     <row r="45" spans="2:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="168" t="s">
+      <c r="B45" s="164" t="s">
         <v>127</v>
       </c>
-      <c r="C45" s="168"/>
-      <c r="D45" s="168"/>
-      <c r="E45" s="168"/>
-      <c r="F45" s="168"/>
-      <c r="G45" s="168"/>
-      <c r="H45" s="168"/>
-      <c r="I45" s="168"/>
-      <c r="J45" s="168"/>
+      <c r="C45" s="164"/>
+      <c r="D45" s="164"/>
+      <c r="E45" s="164"/>
+      <c r="F45" s="164"/>
+      <c r="G45" s="164"/>
+      <c r="H45" s="164"/>
+      <c r="I45" s="164"/>
+      <c r="J45" s="164"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B46" s="47"/>
@@ -3911,30 +3786,30 @@
       <c r="J46" s="47"/>
     </row>
     <row r="47" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="168" t="s">
-        <v>144</v>
-      </c>
-      <c r="C47" s="168"/>
-      <c r="D47" s="168"/>
-      <c r="E47" s="168"/>
-      <c r="F47" s="168"/>
-      <c r="G47" s="168"/>
-      <c r="H47" s="168"/>
-      <c r="I47" s="168"/>
-      <c r="J47" s="168"/>
+      <c r="B47" s="164" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" s="164"/>
+      <c r="D47" s="164"/>
+      <c r="E47" s="164"/>
+      <c r="F47" s="164"/>
+      <c r="G47" s="164"/>
+      <c r="H47" s="164"/>
+      <c r="I47" s="164"/>
+      <c r="J47" s="164"/>
     </row>
     <row r="48" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="168" t="s">
-        <v>148</v>
-      </c>
-      <c r="C48" s="168"/>
-      <c r="D48" s="168"/>
-      <c r="E48" s="168"/>
-      <c r="F48" s="168"/>
-      <c r="G48" s="168"/>
-      <c r="H48" s="168"/>
-      <c r="I48" s="168"/>
-      <c r="J48" s="168"/>
+      <c r="B48" s="164" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" s="164"/>
+      <c r="D48" s="164"/>
+      <c r="E48" s="164"/>
+      <c r="F48" s="164"/>
+      <c r="G48" s="164"/>
+      <c r="H48" s="164"/>
+      <c r="I48" s="164"/>
+      <c r="J48" s="164"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B49" s="39"/>
@@ -4000,16 +3875,16 @@
       </c>
     </row>
     <row r="60" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="168" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" s="168"/>
-      <c r="D60" s="168"/>
-      <c r="E60" s="168"/>
-      <c r="F60" s="168"/>
-      <c r="G60" s="168"/>
-      <c r="H60" s="168"/>
-      <c r="I60" s="168"/>
+      <c r="B60" s="164" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="164"/>
+      <c r="D60" s="164"/>
+      <c r="E60" s="164"/>
+      <c r="F60" s="164"/>
+      <c r="G60" s="164"/>
+      <c r="H60" s="164"/>
+      <c r="I60" s="164"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B61" s="39" t="s">
@@ -4064,28 +3939,28 @@
     </row>
     <row r="68" spans="2:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B68" s="37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69" s="39"/>
     </row>
     <row r="70" spans="2:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="168" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="168"/>
-      <c r="D70" s="168"/>
-      <c r="E70" s="168"/>
-      <c r="F70" s="168"/>
-      <c r="G70" s="168"/>
-      <c r="H70" s="168"/>
-      <c r="I70" s="168"/>
-      <c r="J70" s="168"/>
+      <c r="B70" s="164" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="164"/>
+      <c r="D70" s="164"/>
+      <c r="E70" s="164"/>
+      <c r="F70" s="164"/>
+      <c r="G70" s="164"/>
+      <c r="H70" s="164"/>
+      <c r="I70" s="164"/>
+      <c r="J70" s="164"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B71" s="39" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.35">
@@ -4093,7 +3968,7 @@
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B73" s="39" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C73" s="39"/>
       <c r="D73" s="39"/>
@@ -4106,7 +3981,7 @@
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B74" s="40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C74" s="39"/>
       <c r="D74" s="39"/>
@@ -4119,7 +3994,7 @@
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B75" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C75" s="39"/>
       <c r="D75" s="39"/>
@@ -4132,7 +4007,7 @@
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76" s="40" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C76" s="39"/>
       <c r="D76" s="39"/>
@@ -4145,7 +4020,7 @@
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B77" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C77" s="39"/>
       <c r="D77" s="39"/>
@@ -4157,17 +4032,17 @@
       <c r="J77" s="39"/>
     </row>
     <row r="78" spans="2:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="167" t="s">
-        <v>147</v>
-      </c>
-      <c r="C78" s="167"/>
-      <c r="D78" s="167"/>
-      <c r="E78" s="167"/>
-      <c r="F78" s="167"/>
-      <c r="G78" s="167"/>
-      <c r="H78" s="167"/>
-      <c r="I78" s="167"/>
-      <c r="J78" s="167"/>
+      <c r="B78" s="163" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="163"/>
+      <c r="D78" s="163"/>
+      <c r="E78" s="163"/>
+      <c r="F78" s="163"/>
+      <c r="G78" s="163"/>
+      <c r="H78" s="163"/>
+      <c r="I78" s="163"/>
+      <c r="J78" s="163"/>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B79" s="39"/>
@@ -4297,7 +4172,7 @@
     <col min="4" max="4" width="9.81640625" customWidth="1"/>
     <col min="5" max="6" width="13.81640625" style="6" customWidth="1"/>
     <col min="7" max="7" width="26.54296875" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" style="77" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="74" customWidth="1"/>
     <col min="9" max="9" width="38.81640625" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="37.54296875" customWidth="1"/>
@@ -4310,7 +4185,7 @@
     <col min="18" max="18" width="16.1796875" customWidth="1"/>
     <col min="19" max="19" width="51.54296875" customWidth="1"/>
     <col min="20" max="20" width="9.1796875" customWidth="1"/>
-    <col min="21" max="21" width="11.81640625" style="84" customWidth="1"/>
+    <col min="21" max="21" width="11.81640625" style="81" customWidth="1"/>
     <col min="22" max="22" width="11.81640625" style="6" customWidth="1"/>
     <col min="23" max="23" width="27.453125" customWidth="1"/>
     <col min="24" max="24" width="22.1796875" style="6" customWidth="1"/>
@@ -4318,40 +4193,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="177"/>
-      <c r="B1" s="171" t="s">
+      <c r="A1" s="171"/>
+      <c r="B1" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="171" t="s">
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="173"/>
-      <c r="R1" s="171" t="s">
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="165" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="172"/>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="173"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="167"/>
     </row>
     <row r="2" spans="1:25" s="5" customFormat="1" ht="56.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="178"/>
+      <c r="A2" s="172"/>
       <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
@@ -4370,7 +4245,7 @@
       <c r="G2" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="H2" s="79" t="s">
         <v>125</v>
       </c>
       <c r="I2" s="27" t="s">
@@ -4408,7 +4283,7 @@
         <f t="shared" ref="Q2" si="1">I2</f>
         <v>Commentaire</v>
       </c>
-      <c r="R2" s="124" t="str">
+      <c r="R2" s="121" t="str">
         <f t="shared" ref="R2:X2" si="2">B2</f>
         <v>Catégorie</v>
       </c>
@@ -4442,10 +4317,10 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="174" t="s">
+      <c r="A3" s="168" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="104" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -4464,8 +4339,8 @@
       <c r="H3" s="12">
         <v>0.2</v>
       </c>
-      <c r="I3" s="142"/>
-      <c r="J3" s="97" t="s">
+      <c r="I3" s="139"/>
+      <c r="J3" s="94" t="s">
         <v>54</v>
       </c>
       <c r="K3" t="s">
@@ -4485,30 +4360,30 @@
         <v>0.2</v>
       </c>
       <c r="Q3" s="66"/>
-      <c r="R3" s="97" t="s">
+      <c r="R3" s="94" t="s">
         <v>51</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="89">
+      <c r="T3" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="86">
         <v>60</v>
       </c>
-      <c r="V3" s="78" t="s">
+      <c r="V3" s="75" t="s">
         <v>84</v>
       </c>
       <c r="W3" s="32"/>
-      <c r="X3" s="88">
+      <c r="X3" s="85">
         <v>0.5</v>
       </c>
       <c r="Y3" s="66"/>
     </row>
     <row r="4" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="175"/>
-      <c r="B4" s="104" t="s">
+      <c r="A4" s="169"/>
+      <c r="B4" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
@@ -4518,9 +4393,9 @@
         <v>47</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="114"/>
+      <c r="H4" s="111"/>
       <c r="I4" s="67"/>
-      <c r="J4" s="98" t="s">
+      <c r="J4" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K4" t="s">
@@ -4540,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="67"/>
-      <c r="R4" s="98" t="s">
+      <c r="R4" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S4" t="s">
@@ -4549,14 +4424,14 @@
       <c r="T4" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U4" s="86"/>
+      <c r="U4" s="83"/>
       <c r="W4" s="33"/>
-      <c r="X4" s="84"/>
+      <c r="X4" s="81"/>
       <c r="Y4" s="67"/>
     </row>
     <row r="5" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="175"/>
-      <c r="B5" s="104" t="s">
+      <c r="A5" s="169"/>
+      <c r="B5" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C5" t="s">
@@ -4566,9 +4441,9 @@
         <v>47</v>
       </c>
       <c r="G5" s="33"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="98" t="s">
+      <c r="H5" s="111"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K5" t="s">
@@ -4577,11 +4452,11 @@
       <c r="L5" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="163"/>
+      <c r="M5" s="156"/>
       <c r="O5" s="33"/>
-      <c r="P5" s="84"/>
+      <c r="P5" s="81"/>
       <c r="Q5" s="67"/>
-      <c r="R5" s="98" t="s">
+      <c r="R5" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S5" t="s">
@@ -4590,14 +4465,14 @@
       <c r="T5" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U5" s="86"/>
+      <c r="U5" s="83"/>
       <c r="W5" s="33"/>
-      <c r="X5" s="84"/>
+      <c r="X5" s="81"/>
       <c r="Y5" s="67"/>
     </row>
     <row r="6" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="175"/>
-      <c r="B6" s="104" t="s">
+      <c r="A6" s="169"/>
+      <c r="B6" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C6" t="s">
@@ -4606,11 +4481,11 @@
       <c r="D6" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="108"/>
+      <c r="E6" s="105"/>
       <c r="G6" s="33"/>
-      <c r="H6" s="109"/>
+      <c r="H6" s="106"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="98" t="s">
+      <c r="J6" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K6" t="s">
@@ -4619,11 +4494,11 @@
       <c r="L6" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="163"/>
+      <c r="M6" s="156"/>
       <c r="O6" s="33"/>
-      <c r="P6" s="84"/>
+      <c r="P6" s="81"/>
       <c r="Q6" s="67"/>
-      <c r="R6" s="98" t="s">
+      <c r="R6" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S6" t="s">
@@ -4632,14 +4507,14 @@
       <c r="T6" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U6" s="86"/>
+      <c r="U6" s="83"/>
       <c r="W6" s="33"/>
-      <c r="X6" s="84"/>
+      <c r="X6" s="81"/>
       <c r="Y6" s="67"/>
     </row>
     <row r="7" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="175"/>
-      <c r="B7" s="104" t="s">
+      <c r="A7" s="169"/>
+      <c r="B7" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C7" t="s">
@@ -4649,9 +4524,9 @@
         <v>47</v>
       </c>
       <c r="G7" s="33"/>
-      <c r="H7" s="109"/>
+      <c r="H7" s="106"/>
       <c r="I7" s="67"/>
-      <c r="J7" s="98" t="s">
+      <c r="J7" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K7" t="s">
@@ -4660,11 +4535,11 @@
       <c r="L7" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="163"/>
+      <c r="M7" s="156"/>
       <c r="O7" s="33"/>
-      <c r="P7" s="84"/>
+      <c r="P7" s="81"/>
       <c r="Q7" s="67"/>
-      <c r="R7" s="98" t="s">
+      <c r="R7" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S7" t="s">
@@ -4673,14 +4548,14 @@
       <c r="T7" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U7" s="86"/>
+      <c r="U7" s="83"/>
       <c r="W7" s="33"/>
-      <c r="X7" s="84"/>
+      <c r="X7" s="81"/>
       <c r="Y7" s="67"/>
     </row>
     <row r="8" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="175"/>
-      <c r="B8" s="104" t="s">
+      <c r="A8" s="169"/>
+      <c r="B8" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
@@ -4690,9 +4565,9 @@
         <v>47</v>
       </c>
       <c r="G8" s="33"/>
-      <c r="H8" s="109"/>
+      <c r="H8" s="106"/>
       <c r="I8" s="67"/>
-      <c r="J8" s="98" t="s">
+      <c r="J8" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K8" t="s">
@@ -4701,11 +4576,11 @@
       <c r="L8" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="163"/>
+      <c r="M8" s="156"/>
       <c r="O8" s="33"/>
-      <c r="P8" s="84"/>
+      <c r="P8" s="81"/>
       <c r="Q8" s="67"/>
-      <c r="R8" s="98" t="s">
+      <c r="R8" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S8" t="s">
@@ -4714,14 +4589,14 @@
       <c r="T8" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U8" s="86"/>
+      <c r="U8" s="83"/>
       <c r="W8" s="33"/>
-      <c r="X8" s="84"/>
+      <c r="X8" s="81"/>
       <c r="Y8" s="67"/>
     </row>
     <row r="9" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="175"/>
-      <c r="B9" s="104" t="s">
+      <c r="A9" s="169"/>
+      <c r="B9" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
@@ -4731,9 +4606,9 @@
         <v>47</v>
       </c>
       <c r="G9" s="33"/>
-      <c r="H9" s="114"/>
+      <c r="H9" s="111"/>
       <c r="I9" s="67"/>
-      <c r="J9" s="98" t="s">
+      <c r="J9" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K9" t="s">
@@ -4742,11 +4617,11 @@
       <c r="L9" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="163"/>
+      <c r="M9" s="156"/>
       <c r="O9" s="33"/>
-      <c r="P9" s="84"/>
+      <c r="P9" s="81"/>
       <c r="Q9" s="67"/>
-      <c r="R9" s="98" t="s">
+      <c r="R9" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S9" t="s">
@@ -4755,14 +4630,14 @@
       <c r="T9" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="86"/>
+      <c r="U9" s="83"/>
       <c r="W9" s="33"/>
-      <c r="X9" s="84"/>
+      <c r="X9" s="81"/>
       <c r="Y9" s="67"/>
     </row>
     <row r="10" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="175"/>
-      <c r="B10" s="104" t="s">
+      <c r="A10" s="169"/>
+      <c r="B10" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C10" t="s">
@@ -4772,9 +4647,9 @@
         <v>47</v>
       </c>
       <c r="G10" s="33"/>
-      <c r="H10" s="114"/>
+      <c r="H10" s="111"/>
       <c r="I10" s="67"/>
-      <c r="J10" s="98" t="s">
+      <c r="J10" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K10" t="s">
@@ -4783,11 +4658,11 @@
       <c r="L10" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="163"/>
+      <c r="M10" s="156"/>
       <c r="O10" s="33"/>
-      <c r="P10" s="84"/>
+      <c r="P10" s="81"/>
       <c r="Q10" s="67"/>
-      <c r="R10" s="99" t="s">
+      <c r="R10" s="96" t="s">
         <v>51</v>
       </c>
       <c r="S10" s="1" t="s">
@@ -4796,15 +4671,15 @@
       <c r="T10" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="U10" s="123"/>
-      <c r="V10" s="80"/>
+      <c r="U10" s="120"/>
+      <c r="V10" s="77"/>
       <c r="W10" s="35"/>
-      <c r="X10" s="87"/>
+      <c r="X10" s="84"/>
       <c r="Y10" s="68"/>
     </row>
     <row r="11" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="175"/>
-      <c r="B11" s="104" t="s">
+      <c r="A11" s="169"/>
+      <c r="B11" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C11" t="s">
@@ -4813,11 +4688,11 @@
       <c r="D11" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="139"/>
+      <c r="E11" s="136"/>
       <c r="G11" s="33"/>
-      <c r="H11" s="114"/>
+      <c r="H11" s="111"/>
       <c r="I11" s="67"/>
-      <c r="J11" s="98" t="s">
+      <c r="J11" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K11" t="s">
@@ -4826,11 +4701,11 @@
       <c r="L11" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="163"/>
+      <c r="M11" s="156"/>
       <c r="O11" s="33"/>
-      <c r="P11" s="84"/>
+      <c r="P11" s="81"/>
       <c r="Q11" s="67"/>
-      <c r="R11" s="100" t="s">
+      <c r="R11" s="97" t="s">
         <v>52</v>
       </c>
       <c r="S11" s="2" t="s">
@@ -4839,15 +4714,15 @@
       <c r="T11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="U11" s="85"/>
-      <c r="V11" s="79"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="76"/>
       <c r="W11" s="34"/>
-      <c r="X11" s="85"/>
+      <c r="X11" s="82"/>
       <c r="Y11" s="69"/>
     </row>
     <row r="12" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="175"/>
-      <c r="B12" s="104" t="s">
+      <c r="A12" s="169"/>
+      <c r="B12" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
@@ -4856,11 +4731,11 @@
       <c r="D12" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="140"/>
+      <c r="E12" s="137"/>
       <c r="G12" s="33"/>
-      <c r="H12" s="114"/>
+      <c r="H12" s="111"/>
       <c r="I12" s="67"/>
-      <c r="J12" s="104" t="s">
+      <c r="J12" s="101" t="s">
         <v>92</v>
       </c>
       <c r="K12" s="48" t="s">
@@ -4869,14 +4744,14 @@
       <c r="L12" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="161"/>
-      <c r="N12" s="83"/>
+      <c r="M12" s="154"/>
+      <c r="N12" s="80"/>
       <c r="O12" s="36"/>
-      <c r="P12" s="122"/>
+      <c r="P12" s="119"/>
       <c r="Q12" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="R12" s="101" t="s">
+      <c r="R12" s="98" t="s">
         <v>52</v>
       </c>
       <c r="S12" s="60" t="s">
@@ -4887,25 +4762,25 @@
       </c>
       <c r="U12" s="49"/>
       <c r="W12" s="33"/>
-      <c r="X12" s="84"/>
+      <c r="X12" s="81"/>
       <c r="Y12" s="67"/>
     </row>
     <row r="13" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="175"/>
-      <c r="B13" s="104" t="s">
+      <c r="A13" s="169"/>
+      <c r="B13" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D13" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="140"/>
+      <c r="E13" s="137"/>
       <c r="G13" s="33"/>
-      <c r="H13" s="114"/>
+      <c r="H13" s="111"/>
       <c r="I13" s="67"/>
-      <c r="J13" s="99" t="s">
+      <c r="J13" s="96" t="s">
         <v>93</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -4914,14 +4789,14 @@
       <c r="L13" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="M13" s="160"/>
-      <c r="N13" s="80"/>
+      <c r="M13" s="153"/>
+      <c r="N13" s="77"/>
       <c r="O13" s="35"/>
-      <c r="P13" s="87"/>
+      <c r="P13" s="84"/>
       <c r="Q13" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="R13" s="102" t="s">
+      <c r="R13" s="99" t="s">
         <v>52</v>
       </c>
       <c r="S13" s="61" t="s">
@@ -4930,42 +4805,42 @@
       <c r="T13" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="U13" s="87"/>
-      <c r="V13" s="80"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="77"/>
       <c r="W13" s="35"/>
-      <c r="X13" s="87"/>
+      <c r="X13" s="84"/>
       <c r="Y13" s="68"/>
     </row>
     <row r="14" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="175"/>
-      <c r="B14" s="104" t="s">
+      <c r="A14" s="169"/>
+      <c r="B14" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D14" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="140"/>
+      <c r="E14" s="137"/>
       <c r="G14" s="33"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="104" t="s">
-        <v>155</v>
+      <c r="H14" s="111"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="101" t="s">
+        <v>152</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L14" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="M14" s="83"/>
+        <v>154</v>
+      </c>
+      <c r="M14" s="80"/>
       <c r="N14" s="4"/>
       <c r="O14" s="36"/>
-      <c r="P14" s="133"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="101" t="s">
+      <c r="P14" s="130"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S14" s="60" t="s">
@@ -4975,30 +4850,30 @@
         <v>47</v>
       </c>
       <c r="W14" s="33"/>
-      <c r="X14" s="84"/>
+      <c r="X14" s="81"/>
       <c r="Y14" s="67"/>
     </row>
     <row r="15" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="175"/>
-      <c r="B15" s="104" t="s">
+      <c r="A15" s="169"/>
+      <c r="B15" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="140"/>
+      <c r="E15" s="137"/>
       <c r="G15" s="33"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="145"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="142"/>
       <c r="L15" s="6"/>
       <c r="N15"/>
       <c r="O15" s="33"/>
       <c r="P15" s="6"/>
-      <c r="R15" s="101" t="s">
+      <c r="R15" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S15" s="60" t="s">
@@ -5008,30 +4883,30 @@
         <v>47</v>
       </c>
       <c r="W15" s="33"/>
-      <c r="X15" s="84"/>
+      <c r="X15" s="81"/>
       <c r="Y15" s="67"/>
     </row>
     <row r="16" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="175"/>
-      <c r="B16" s="104" t="s">
+      <c r="A16" s="169"/>
+      <c r="B16" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D16" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="140"/>
+      <c r="E16" s="137"/>
       <c r="G16" s="33"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="145"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="142"/>
       <c r="L16" s="6"/>
       <c r="N16"/>
       <c r="O16" s="33"/>
       <c r="P16" s="6"/>
-      <c r="R16" s="101" t="s">
+      <c r="R16" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S16" s="60" t="s">
@@ -5041,12 +4916,12 @@
         <v>47</v>
       </c>
       <c r="W16" s="33"/>
-      <c r="X16" s="84"/>
+      <c r="X16" s="81"/>
       <c r="Y16" s="67"/>
     </row>
     <row r="17" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="175"/>
-      <c r="B17" s="110" t="s">
+      <c r="A17" s="169"/>
+      <c r="B17" s="107" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -5056,12 +4931,12 @@
         <v>47</v>
       </c>
       <c r="E17" s="50"/>
-      <c r="F17" s="79"/>
+      <c r="F17" s="76"/>
       <c r="G17" s="34"/>
-      <c r="H17" s="115"/>
+      <c r="H17" s="112"/>
       <c r="I17" s="71"/>
       <c r="O17" s="33"/>
-      <c r="R17" s="101" t="s">
+      <c r="R17" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S17" s="60" t="s">
@@ -5071,12 +4946,12 @@
         <v>47</v>
       </c>
       <c r="W17" s="33"/>
-      <c r="X17" s="84"/>
+      <c r="X17" s="81"/>
       <c r="Y17" s="67"/>
     </row>
     <row r="18" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="175"/>
-      <c r="B18" s="110" t="s">
+      <c r="A18" s="169"/>
+      <c r="B18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
@@ -5087,12 +4962,12 @@
       </c>
       <c r="E18" s="51"/>
       <c r="G18" s="33"/>
-      <c r="H18" s="114"/>
-      <c r="I18" s="132"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="129"/>
       <c r="J18" s="17"/>
       <c r="O18" s="33"/>
       <c r="Q18" s="13"/>
-      <c r="R18" s="101" t="s">
+      <c r="R18" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S18" s="60" t="s">
@@ -5102,12 +4977,12 @@
         <v>47</v>
       </c>
       <c r="W18" s="33"/>
-      <c r="X18" s="84"/>
+      <c r="X18" s="81"/>
       <c r="Y18" s="67"/>
     </row>
     <row r="19" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="175"/>
-      <c r="B19" s="110" t="s">
+      <c r="A19" s="169"/>
+      <c r="B19" s="107" t="s">
         <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -5116,14 +4991,14 @@
       <c r="D19" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="79"/>
+      <c r="F19" s="76"/>
       <c r="G19" s="34"/>
-      <c r="H19" s="115"/>
+      <c r="H19" s="112"/>
       <c r="I19" s="71"/>
       <c r="J19" s="17"/>
       <c r="O19" s="33"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="101" t="s">
+      <c r="R19" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S19" s="60" t="s">
@@ -5133,12 +5008,12 @@
         <v>47</v>
       </c>
       <c r="W19" s="33"/>
-      <c r="X19" s="84"/>
+      <c r="X19" s="81"/>
       <c r="Y19" s="67"/>
     </row>
     <row r="20" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="175"/>
-      <c r="B20" s="110" t="s">
+      <c r="A20" s="169"/>
+      <c r="B20" s="107" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -5147,14 +5022,14 @@
       <c r="D20" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="141"/>
-      <c r="F20" s="80"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="77"/>
       <c r="G20" s="35"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="144"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="141"/>
       <c r="J20" s="18"/>
       <c r="O20" s="33"/>
-      <c r="R20" s="101" t="s">
+      <c r="R20" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S20" s="60" t="s">
@@ -5164,12 +5039,12 @@
         <v>47</v>
       </c>
       <c r="W20" s="33"/>
-      <c r="X20" s="84"/>
+      <c r="X20" s="81"/>
       <c r="Y20" s="67"/>
     </row>
     <row r="21" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="175"/>
-      <c r="B21" s="104" t="s">
+      <c r="A21" s="169"/>
+      <c r="B21" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -5178,15 +5053,15 @@
       <c r="D21" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
       <c r="G21" s="34"/>
-      <c r="H21" s="115"/>
+      <c r="H21" s="112"/>
       <c r="I21" s="71" t="s">
         <v>106</v>
       </c>
       <c r="O21" s="33"/>
-      <c r="R21" s="102" t="s">
+      <c r="R21" s="99" t="s">
         <v>53</v>
       </c>
       <c r="S21" s="61" t="s">
@@ -5195,14 +5070,14 @@
       <c r="T21" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="V21" s="80"/>
+      <c r="V21" s="77"/>
       <c r="W21" s="35"/>
-      <c r="X21" s="87"/>
+      <c r="X21" s="84"/>
       <c r="Y21" s="68"/>
     </row>
     <row r="22" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="175"/>
-      <c r="B22" s="104" t="s">
+      <c r="A22" s="169"/>
+      <c r="B22" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -5213,10 +5088,10 @@
       </c>
       <c r="E22" s="49"/>
       <c r="G22" s="33"/>
-      <c r="H22" s="114"/>
+      <c r="H22" s="111"/>
       <c r="I22" s="67"/>
       <c r="O22" s="33"/>
-      <c r="R22" s="98" t="s">
+      <c r="R22" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S22" t="s">
@@ -5225,16 +5100,16 @@
       <c r="T22" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U22" s="125"/>
+      <c r="U22" s="122"/>
       <c r="W22" s="33"/>
-      <c r="X22" s="84"/>
+      <c r="X22" s="81"/>
       <c r="Y22" s="67" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="175"/>
-      <c r="B23" s="104" t="s">
+      <c r="A23" s="169"/>
+      <c r="B23" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -5244,12 +5119,12 @@
         <v>58</v>
       </c>
       <c r="E23" s="49"/>
-      <c r="F23" s="80"/>
+      <c r="F23" s="77"/>
       <c r="G23" s="35"/>
-      <c r="H23" s="116"/>
+      <c r="H23" s="113"/>
       <c r="I23" s="68"/>
       <c r="O23" s="33"/>
-      <c r="R23" s="98" t="s">
+      <c r="R23" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S23" s="14" t="s">
@@ -5258,14 +5133,14 @@
       <c r="T23" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="U23" s="86"/>
+      <c r="U23" s="83"/>
       <c r="W23" s="33"/>
-      <c r="X23" s="84"/>
+      <c r="X23" s="81"/>
       <c r="Y23" s="67"/>
     </row>
     <row r="24" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="175"/>
-      <c r="B24" s="104" t="s">
+      <c r="A24" s="169"/>
+      <c r="B24" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -5275,14 +5150,14 @@
         <v>47</v>
       </c>
       <c r="E24" s="50"/>
-      <c r="F24" s="79"/>
+      <c r="F24" s="76"/>
       <c r="G24" s="34"/>
-      <c r="H24" s="115"/>
+      <c r="H24" s="112"/>
       <c r="I24" s="71" t="s">
         <v>106</v>
       </c>
       <c r="O24" s="33"/>
-      <c r="R24" s="98" t="s">
+      <c r="R24" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S24" s="14" t="s">
@@ -5291,14 +5166,14 @@
       <c r="T24" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="U24" s="86"/>
+      <c r="U24" s="83"/>
       <c r="W24" s="33"/>
-      <c r="X24" s="84"/>
+      <c r="X24" s="81"/>
       <c r="Y24" s="67"/>
     </row>
     <row r="25" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="175"/>
-      <c r="B25" s="104" t="s">
+      <c r="A25" s="169"/>
+      <c r="B25" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -5309,11 +5184,11 @@
       </c>
       <c r="E25" s="49"/>
       <c r="G25" s="33"/>
-      <c r="H25" s="114"/>
+      <c r="H25" s="111"/>
       <c r="I25" s="67"/>
-      <c r="K25" s="136"/>
+      <c r="K25" s="133"/>
       <c r="O25" s="33"/>
-      <c r="R25" s="98" t="s">
+      <c r="R25" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S25" s="23" t="s">
@@ -5322,14 +5197,14 @@
       <c r="T25" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U25" s="86"/>
+      <c r="U25" s="83"/>
       <c r="W25" s="33"/>
-      <c r="X25" s="84"/>
+      <c r="X25" s="81"/>
       <c r="Y25" s="67"/>
     </row>
     <row r="26" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="175"/>
-      <c r="B26" s="104" t="s">
+      <c r="A26" s="169"/>
+      <c r="B26" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -5340,10 +5215,10 @@
       </c>
       <c r="E26" s="49"/>
       <c r="G26" s="33"/>
-      <c r="H26" s="114"/>
+      <c r="H26" s="111"/>
       <c r="I26" s="67"/>
       <c r="O26" s="33"/>
-      <c r="R26" s="98" t="s">
+      <c r="R26" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S26" s="23" t="s">
@@ -5352,14 +5227,14 @@
       <c r="T26" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U26" s="123"/>
+      <c r="U26" s="120"/>
       <c r="W26" s="33"/>
-      <c r="X26" s="84"/>
+      <c r="X26" s="81"/>
       <c r="Y26" s="67"/>
     </row>
     <row r="27" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="175"/>
-      <c r="B27" s="104" t="s">
+      <c r="A27" s="169"/>
+      <c r="B27" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -5370,32 +5245,32 @@
       </c>
       <c r="E27" s="49"/>
       <c r="G27" s="33"/>
-      <c r="H27" s="114"/>
+      <c r="H27" s="111"/>
       <c r="I27" s="67"/>
       <c r="J27" s="17"/>
       <c r="L27" s="6"/>
       <c r="O27" s="33"/>
       <c r="Q27" s="13"/>
-      <c r="R27" s="103" t="s">
-        <v>149</v>
+      <c r="R27" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T27" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="U27" s="86"/>
-      <c r="V27" s="79"/>
+      <c r="U27" s="83"/>
+      <c r="V27" s="76"/>
       <c r="W27" s="34"/>
-      <c r="X27" s="85"/>
+      <c r="X27" s="82"/>
       <c r="Y27" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="175"/>
-      <c r="B28" s="104" t="s">
+      <c r="A28" s="169"/>
+      <c r="B28" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -5406,13 +5281,13 @@
       </c>
       <c r="E28" s="49"/>
       <c r="G28" s="33"/>
-      <c r="H28" s="114"/>
+      <c r="H28" s="111"/>
       <c r="I28" s="67"/>
       <c r="J28" s="17"/>
       <c r="O28" s="33"/>
       <c r="Q28" s="13"/>
-      <c r="R28" s="98" t="s">
-        <v>149</v>
+      <c r="R28" s="95" t="s">
+        <v>146</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>75</v>
@@ -5420,14 +5295,14 @@
       <c r="T28" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="U28" s="86"/>
+      <c r="U28" s="83"/>
       <c r="W28" s="33"/>
-      <c r="X28" s="84"/>
+      <c r="X28" s="81"/>
       <c r="Y28" s="67"/>
     </row>
     <row r="29" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="175"/>
-      <c r="B29" s="104" t="s">
+      <c r="A29" s="169"/>
+      <c r="B29" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -5438,14 +5313,14 @@
       </c>
       <c r="E29" s="49"/>
       <c r="G29" s="33"/>
-      <c r="H29" s="114"/>
+      <c r="H29" s="111"/>
       <c r="I29" s="67"/>
       <c r="J29" s="17"/>
       <c r="L29" s="6"/>
       <c r="O29" s="33"/>
       <c r="Q29" s="13"/>
-      <c r="R29" s="99" t="s">
-        <v>149</v>
+      <c r="R29" s="96" t="s">
+        <v>146</v>
       </c>
       <c r="S29" s="22" t="s">
         <v>76</v>
@@ -5453,15 +5328,15 @@
       <c r="T29" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="U29" s="86"/>
-      <c r="V29" s="80"/>
+      <c r="U29" s="83"/>
+      <c r="V29" s="77"/>
       <c r="W29" s="35"/>
-      <c r="X29" s="87"/>
+      <c r="X29" s="84"/>
       <c r="Y29" s="68"/>
     </row>
     <row r="30" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="175"/>
-      <c r="B30" s="104" t="s">
+      <c r="A30" s="169"/>
+      <c r="B30" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -5472,32 +5347,32 @@
       </c>
       <c r="E30" s="49"/>
       <c r="G30" s="33"/>
-      <c r="H30" s="114"/>
+      <c r="H30" s="111"/>
       <c r="I30" s="67"/>
       <c r="J30" s="17"/>
       <c r="L30" s="6"/>
       <c r="O30" s="33"/>
       <c r="Q30" s="13"/>
-      <c r="R30" s="103" t="s">
-        <v>150</v>
+      <c r="R30" s="100" t="s">
+        <v>147</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="T30" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="U30" s="125"/>
-      <c r="V30" s="79"/>
+      <c r="U30" s="122"/>
+      <c r="V30" s="76"/>
       <c r="W30" s="34"/>
-      <c r="X30" s="85"/>
+      <c r="X30" s="82"/>
       <c r="Y30" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="175"/>
-      <c r="B31" s="104" t="s">
+      <c r="A31" s="169"/>
+      <c r="B31" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -5508,14 +5383,14 @@
       </c>
       <c r="E31" s="49"/>
       <c r="G31" s="33"/>
-      <c r="H31" s="114"/>
+      <c r="H31" s="111"/>
       <c r="I31" s="67"/>
       <c r="J31" s="17"/>
       <c r="L31" s="6"/>
       <c r="O31" s="33"/>
       <c r="Q31" s="13"/>
-      <c r="R31" s="98" t="s">
-        <v>150</v>
+      <c r="R31" s="95" t="s">
+        <v>147</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>75</v>
@@ -5523,14 +5398,14 @@
       <c r="T31" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="U31" s="86"/>
+      <c r="U31" s="83"/>
       <c r="W31" s="33"/>
-      <c r="X31" s="84"/>
+      <c r="X31" s="81"/>
       <c r="Y31" s="67"/>
     </row>
     <row r="32" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="175"/>
-      <c r="B32" s="104" t="s">
+      <c r="A32" s="169"/>
+      <c r="B32" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -5541,13 +5416,13 @@
       </c>
       <c r="E32" s="49"/>
       <c r="G32" s="33"/>
-      <c r="H32" s="114"/>
+      <c r="H32" s="111"/>
       <c r="I32" s="67"/>
       <c r="J32" s="17"/>
       <c r="O32" s="33"/>
       <c r="Q32" s="13"/>
-      <c r="R32" s="99" t="s">
-        <v>150</v>
+      <c r="R32" s="96" t="s">
+        <v>147</v>
       </c>
       <c r="S32" s="22" t="s">
         <v>76</v>
@@ -5555,15 +5430,15 @@
       <c r="T32" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="U32" s="123"/>
-      <c r="V32" s="80"/>
+      <c r="U32" s="120"/>
+      <c r="V32" s="77"/>
       <c r="W32" s="35"/>
-      <c r="X32" s="87"/>
+      <c r="X32" s="84"/>
       <c r="Y32" s="68"/>
     </row>
     <row r="33" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="175"/>
-      <c r="B33" s="104" t="s">
+      <c r="A33" s="169"/>
+      <c r="B33" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -5574,7 +5449,7 @@
       </c>
       <c r="E33" s="49"/>
       <c r="G33" s="33"/>
-      <c r="H33" s="114"/>
+      <c r="H33" s="111"/>
       <c r="I33" s="67"/>
       <c r="J33" s="17"/>
       <c r="O33" s="33"/>
@@ -5582,8 +5457,8 @@
       <c r="W33" s="33"/>
     </row>
     <row r="34" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="175"/>
-      <c r="B34" s="104" t="s">
+      <c r="A34" s="169"/>
+      <c r="B34" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="21" t="s">
@@ -5593,9 +5468,9 @@
         <v>47</v>
       </c>
       <c r="E34" s="51"/>
-      <c r="F34" s="80"/>
+      <c r="F34" s="77"/>
       <c r="G34" s="35"/>
-      <c r="H34" s="116"/>
+      <c r="H34" s="113"/>
       <c r="I34" s="68"/>
       <c r="J34" s="18"/>
       <c r="O34" s="33"/>
@@ -5603,8 +5478,8 @@
       <c r="W34" s="33"/>
     </row>
     <row r="35" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="175"/>
-      <c r="B35" s="104" t="s">
+      <c r="A35" s="169"/>
+      <c r="B35" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C35" t="s">
@@ -5615,7 +5490,7 @@
       </c>
       <c r="E35" s="49"/>
       <c r="G35" s="33"/>
-      <c r="H35" s="114"/>
+      <c r="H35" s="111"/>
       <c r="I35" s="71" t="s">
         <v>106</v>
       </c>
@@ -5625,8 +5500,8 @@
       <c r="W35" s="33"/>
     </row>
     <row r="36" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="175"/>
-      <c r="B36" s="104" t="s">
+      <c r="A36" s="169"/>
+      <c r="B36" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C36" s="14" t="s">
@@ -5637,7 +5512,7 @@
       </c>
       <c r="E36" s="49"/>
       <c r="G36" s="33"/>
-      <c r="H36" s="114"/>
+      <c r="H36" s="111"/>
       <c r="I36" s="67"/>
       <c r="J36" s="18"/>
       <c r="O36" s="33"/>
@@ -5645,8 +5520,8 @@
       <c r="W36" s="33"/>
     </row>
     <row r="37" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="175"/>
-      <c r="B37" s="104" t="s">
+      <c r="A37" s="169"/>
+      <c r="B37" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="14" t="s">
@@ -5657,7 +5532,7 @@
       </c>
       <c r="E37" s="49"/>
       <c r="G37" s="33"/>
-      <c r="H37" s="114"/>
+      <c r="H37" s="111"/>
       <c r="I37" s="67"/>
       <c r="J37" s="18"/>
       <c r="O37" s="33"/>
@@ -5667,8 +5542,8 @@
       <c r="Y37" s="13"/>
     </row>
     <row r="38" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="175"/>
-      <c r="B38" s="104" t="s">
+      <c r="A38" s="169"/>
+      <c r="B38" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C38" s="14" t="s">
@@ -5679,7 +5554,7 @@
       </c>
       <c r="E38" s="49"/>
       <c r="G38" s="33"/>
-      <c r="H38" s="114"/>
+      <c r="H38" s="111"/>
       <c r="I38" s="67"/>
       <c r="J38" s="18"/>
       <c r="O38" s="33"/>
@@ -5689,8 +5564,8 @@
       <c r="Y38" s="13"/>
     </row>
     <row r="39" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="175"/>
-      <c r="B39" s="104" t="s">
+      <c r="A39" s="169"/>
+      <c r="B39" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C39" s="14" t="s">
@@ -5701,7 +5576,7 @@
       </c>
       <c r="E39" s="49"/>
       <c r="G39" s="33"/>
-      <c r="H39" s="114"/>
+      <c r="H39" s="111"/>
       <c r="I39" s="67"/>
       <c r="J39" s="18"/>
       <c r="O39" s="33"/>
@@ -5711,8 +5586,8 @@
       <c r="Y39" s="13"/>
     </row>
     <row r="40" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="175"/>
-      <c r="B40" s="104" t="s">
+      <c r="A40" s="169"/>
+      <c r="B40" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C40" s="14" t="s">
@@ -5723,7 +5598,7 @@
       </c>
       <c r="E40" s="49"/>
       <c r="G40" s="33"/>
-      <c r="H40" s="114"/>
+      <c r="H40" s="111"/>
       <c r="I40" s="67"/>
       <c r="J40" s="18"/>
       <c r="O40" s="33"/>
@@ -5733,8 +5608,8 @@
       <c r="Y40" s="13"/>
     </row>
     <row r="41" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="175"/>
-      <c r="B41" s="104" t="s">
+      <c r="A41" s="169"/>
+      <c r="B41" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C41" s="14" t="s">
@@ -5745,7 +5620,7 @@
       </c>
       <c r="E41" s="49"/>
       <c r="G41" s="33"/>
-      <c r="H41" s="114"/>
+      <c r="H41" s="111"/>
       <c r="I41" s="67"/>
       <c r="J41" s="18"/>
       <c r="O41" s="33"/>
@@ -5755,8 +5630,8 @@
       <c r="Y41" s="13"/>
     </row>
     <row r="42" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="175"/>
-      <c r="B42" s="104" t="s">
+      <c r="A42" s="169"/>
+      <c r="B42" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="14" t="s">
@@ -5767,7 +5642,7 @@
       </c>
       <c r="E42" s="49"/>
       <c r="G42" s="33"/>
-      <c r="H42" s="114"/>
+      <c r="H42" s="111"/>
       <c r="I42" s="67"/>
       <c r="J42" s="18"/>
       <c r="O42" s="33"/>
@@ -5777,8 +5652,8 @@
       <c r="Y42" s="13"/>
     </row>
     <row r="43" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="175"/>
-      <c r="B43" s="104" t="s">
+      <c r="A43" s="169"/>
+      <c r="B43" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C43" s="14" t="s">
@@ -5789,7 +5664,7 @@
       </c>
       <c r="E43" s="49"/>
       <c r="G43" s="33"/>
-      <c r="H43" s="114"/>
+      <c r="H43" s="111"/>
       <c r="I43" s="67"/>
       <c r="J43" s="18"/>
       <c r="O43" s="33"/>
@@ -5800,8 +5675,8 @@
       <c r="Y43" s="13"/>
     </row>
     <row r="44" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="175"/>
-      <c r="B44" s="104" t="s">
+      <c r="A44" s="169"/>
+      <c r="B44" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -5812,7 +5687,7 @@
       </c>
       <c r="E44" s="49"/>
       <c r="G44" s="33"/>
-      <c r="H44" s="114"/>
+      <c r="H44" s="111"/>
       <c r="I44" s="67"/>
       <c r="J44" s="18"/>
       <c r="O44" s="33"/>
@@ -5823,8 +5698,8 @@
       <c r="Y44" s="13"/>
     </row>
     <row r="45" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="175"/>
-      <c r="B45" s="104" t="s">
+      <c r="A45" s="169"/>
+      <c r="B45" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -5835,7 +5710,7 @@
       </c>
       <c r="E45" s="49"/>
       <c r="G45" s="33"/>
-      <c r="H45" s="114"/>
+      <c r="H45" s="111"/>
       <c r="I45" s="67"/>
       <c r="J45" s="18"/>
       <c r="O45" s="33"/>
@@ -5846,8 +5721,8 @@
       <c r="Y45" s="13"/>
     </row>
     <row r="46" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="175"/>
-      <c r="B46" s="104" t="s">
+      <c r="A46" s="169"/>
+      <c r="B46" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -5858,7 +5733,7 @@
       </c>
       <c r="E46" s="49"/>
       <c r="G46" s="33"/>
-      <c r="H46" s="114"/>
+      <c r="H46" s="111"/>
       <c r="I46" s="67"/>
       <c r="J46" s="18"/>
       <c r="O46" s="33"/>
@@ -5869,8 +5744,8 @@
       <c r="Y46" s="13"/>
     </row>
     <row r="47" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="175"/>
-      <c r="B47" s="104" t="s">
+      <c r="A47" s="169"/>
+      <c r="B47" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -5881,7 +5756,7 @@
       </c>
       <c r="E47" s="49"/>
       <c r="G47" s="33"/>
-      <c r="H47" s="114"/>
+      <c r="H47" s="111"/>
       <c r="I47" s="67"/>
       <c r="J47" s="18"/>
       <c r="O47" s="33"/>
@@ -5892,8 +5767,8 @@
       <c r="Y47" s="13"/>
     </row>
     <row r="48" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="175"/>
-      <c r="B48" s="104" t="s">
+      <c r="A48" s="169"/>
+      <c r="B48" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -5904,7 +5779,7 @@
       </c>
       <c r="E48" s="49"/>
       <c r="G48" s="33"/>
-      <c r="H48" s="114"/>
+      <c r="H48" s="111"/>
       <c r="I48" s="67"/>
       <c r="J48" s="18"/>
       <c r="O48" s="33"/>
@@ -5914,20 +5789,20 @@
       <c r="Y48" s="13"/>
     </row>
     <row r="49" spans="1:25" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="176"/>
-      <c r="B49" s="111" t="s">
+      <c r="A49" s="170"/>
+      <c r="B49" s="108" t="s">
         <v>68</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D49" s="105" t="s">
+      <c r="D49" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="105"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="112"/>
-      <c r="H49" s="117"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="109"/>
+      <c r="H49" s="114"/>
       <c r="I49" s="72"/>
       <c r="J49" s="18"/>
       <c r="O49" s="33"/>
@@ -5935,23 +5810,23 @@
       <c r="R49" s="19"/>
       <c r="S49" s="15"/>
       <c r="T49" s="15"/>
-      <c r="U49" s="90"/>
-      <c r="V49" s="81"/>
-      <c r="W49" s="112"/>
-      <c r="X49" s="81"/>
+      <c r="U49" s="87"/>
+      <c r="V49" s="78"/>
+      <c r="W49" s="109"/>
+      <c r="X49" s="78"/>
       <c r="Y49" s="16"/>
     </row>
     <row r="50" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="174" t="s">
+      <c r="A50" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="118" t="s">
+      <c r="B50" s="115" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D50" s="76" t="s">
+      <c r="D50" s="73" t="s">
         <v>47</v>
       </c>
       <c r="E50" s="12">
@@ -5961,13 +5836,13 @@
         <v>84</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="H50" s="12">
         <v>0</v>
       </c>
       <c r="I50" s="66"/>
-      <c r="J50" s="92" t="s">
+      <c r="J50" s="89" t="s">
         <v>54</v>
       </c>
       <c r="K50" s="12" t="s">
@@ -5983,13 +5858,13 @@
         <v>84</v>
       </c>
       <c r="O50" s="12" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="P50" s="12">
         <v>0.2</v>
       </c>
       <c r="Q50" s="66"/>
-      <c r="R50" s="97" t="s">
+      <c r="R50" s="94" t="s">
         <v>51</v>
       </c>
       <c r="S50" s="12" t="s">
@@ -5998,23 +5873,23 @@
       <c r="T50" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="U50" s="88">
+      <c r="U50" s="85">
         <v>200</v>
       </c>
-      <c r="V50" s="78" t="s">
+      <c r="V50" s="75" t="s">
         <v>83</v>
       </c>
       <c r="W50" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="X50" s="78">
+        <v>157</v>
+      </c>
+      <c r="X50" s="75">
         <v>0.1</v>
       </c>
       <c r="Y50" s="66"/>
     </row>
     <row r="51" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="175"/>
-      <c r="B51" s="119" t="s">
+      <c r="A51" s="169"/>
+      <c r="B51" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C51" t="s">
@@ -6024,9 +5899,9 @@
         <v>47</v>
       </c>
       <c r="E51" s="49"/>
-      <c r="H51" s="114"/>
+      <c r="H51" s="111"/>
       <c r="I51" s="67"/>
-      <c r="J51" s="91" t="s">
+      <c r="J51" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K51" t="s">
@@ -6042,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="67"/>
-      <c r="R51" s="98" t="s">
+      <c r="R51" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S51" t="s">
@@ -6054,8 +5929,8 @@
       <c r="Y51" s="67"/>
     </row>
     <row r="52" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="175"/>
-      <c r="B52" s="119" t="s">
+      <c r="A52" s="169"/>
+      <c r="B52" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C52" t="s">
@@ -6065,9 +5940,9 @@
         <v>47</v>
       </c>
       <c r="E52" s="49"/>
-      <c r="H52" s="114"/>
+      <c r="H52" s="111"/>
       <c r="I52" s="67"/>
-      <c r="J52" s="91" t="s">
+      <c r="J52" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K52" t="s">
@@ -6083,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="67"/>
-      <c r="R52" s="98" t="s">
+      <c r="R52" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S52" t="s">
@@ -6095,8 +5970,8 @@
       <c r="Y52" s="67"/>
     </row>
     <row r="53" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="175"/>
-      <c r="B53" s="119" t="s">
+      <c r="A53" s="169"/>
+      <c r="B53" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C53" t="s">
@@ -6106,9 +5981,9 @@
         <v>47</v>
       </c>
       <c r="E53" s="49"/>
-      <c r="H53" s="114"/>
+      <c r="H53" s="111"/>
       <c r="I53" s="67"/>
-      <c r="J53" s="91" t="s">
+      <c r="J53" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K53" t="s">
@@ -6124,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="67"/>
-      <c r="R53" s="98" t="s">
+      <c r="R53" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S53" t="s">
@@ -6136,8 +6011,8 @@
       <c r="Y53" s="67"/>
     </row>
     <row r="54" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="175"/>
-      <c r="B54" s="119" t="s">
+      <c r="A54" s="169"/>
+      <c r="B54" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C54" t="s">
@@ -6147,9 +6022,9 @@
         <v>47</v>
       </c>
       <c r="E54" s="49"/>
-      <c r="H54" s="114"/>
+      <c r="H54" s="111"/>
       <c r="I54" s="67"/>
-      <c r="J54" s="91" t="s">
+      <c r="J54" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K54" t="s">
@@ -6165,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="67"/>
-      <c r="R54" s="98" t="s">
+      <c r="R54" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S54" t="s">
@@ -6177,8 +6052,8 @@
       <c r="Y54" s="67"/>
     </row>
     <row r="55" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="175"/>
-      <c r="B55" s="119" t="s">
+      <c r="A55" s="169"/>
+      <c r="B55" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C55" t="s">
@@ -6188,9 +6063,9 @@
         <v>47</v>
       </c>
       <c r="E55" s="49"/>
-      <c r="H55" s="114"/>
+      <c r="H55" s="111"/>
       <c r="I55" s="67"/>
-      <c r="J55" s="91" t="s">
+      <c r="J55" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K55" t="s">
@@ -6206,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="67"/>
-      <c r="R55" s="98" t="s">
+      <c r="R55" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S55" t="s">
@@ -6218,8 +6093,8 @@
       <c r="Y55" s="67"/>
     </row>
     <row r="56" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="175"/>
-      <c r="B56" s="119" t="s">
+      <c r="A56" s="169"/>
+      <c r="B56" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C56" t="s">
@@ -6229,9 +6104,9 @@
         <v>47</v>
       </c>
       <c r="E56" s="49"/>
-      <c r="H56" s="114"/>
+      <c r="H56" s="111"/>
       <c r="I56" s="67"/>
-      <c r="J56" s="91" t="s">
+      <c r="J56" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K56" t="s">
@@ -6247,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="67"/>
-      <c r="R56" s="98" t="s">
+      <c r="R56" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S56" s="58" t="s">
@@ -6259,8 +6134,8 @@
       <c r="Y56" s="67"/>
     </row>
     <row r="57" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="175"/>
-      <c r="B57" s="119" t="s">
+      <c r="A57" s="169"/>
+      <c r="B57" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C57" t="s">
@@ -6270,9 +6145,9 @@
         <v>47</v>
       </c>
       <c r="E57" s="49"/>
-      <c r="H57" s="114"/>
+      <c r="H57" s="111"/>
       <c r="I57" s="67"/>
-      <c r="J57" s="91" t="s">
+      <c r="J57" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K57" t="s">
@@ -6288,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="67"/>
-      <c r="R57" s="99" t="s">
+      <c r="R57" s="96" t="s">
         <v>51</v>
       </c>
       <c r="S57" s="58" t="s">
@@ -6297,15 +6172,15 @@
       <c r="T57" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U57" s="86"/>
-      <c r="V57" s="80"/>
+      <c r="U57" s="83"/>
+      <c r="V57" s="77"/>
       <c r="W57" s="1"/>
-      <c r="X57" s="80"/>
+      <c r="X57" s="77"/>
       <c r="Y57" s="68"/>
     </row>
     <row r="58" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="175"/>
-      <c r="B58" s="119" t="s">
+      <c r="A58" s="169"/>
+      <c r="B58" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C58" t="s">
@@ -6315,9 +6190,9 @@
         <v>36</v>
       </c>
       <c r="E58" s="49"/>
-      <c r="H58" s="114"/>
+      <c r="H58" s="111"/>
       <c r="I58" s="67"/>
-      <c r="J58" s="93" t="s">
+      <c r="J58" s="90" t="s">
         <v>54</v>
       </c>
       <c r="K58" s="1" t="s">
@@ -6333,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="67"/>
-      <c r="R58" s="100" t="s">
+      <c r="R58" s="97" t="s">
         <v>52</v>
       </c>
       <c r="S58" s="2" t="s">
@@ -6342,12 +6217,12 @@
       <c r="T58" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="U58" s="125"/>
+      <c r="U58" s="122"/>
       <c r="Y58" s="67"/>
     </row>
     <row r="59" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="175"/>
-      <c r="B59" s="119" t="s">
+      <c r="A59" s="169"/>
+      <c r="B59" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C59" t="s">
@@ -6357,9 +6232,9 @@
         <v>36</v>
       </c>
       <c r="E59" s="49"/>
-      <c r="H59" s="114"/>
+      <c r="H59" s="111"/>
       <c r="I59" s="67"/>
-      <c r="J59" s="104" t="s">
+      <c r="J59" s="101" t="s">
         <v>92</v>
       </c>
       <c r="K59" s="4" t="s">
@@ -6368,18 +6243,18 @@
       <c r="L59" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="M59" s="83">
+      <c r="M59" s="80">
         <v>0</v>
       </c>
-      <c r="N59" s="83"/>
+      <c r="N59" s="80"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="83">
+      <c r="P59" s="80">
         <v>0</v>
       </c>
       <c r="Q59" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="R59" s="101" t="s">
+      <c r="R59" s="98" t="s">
         <v>52</v>
       </c>
       <c r="S59" s="60" t="s">
@@ -6388,24 +6263,24 @@
       <c r="T59" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U59" s="86"/>
+      <c r="U59" s="83"/>
       <c r="Y59" s="67"/>
     </row>
     <row r="60" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="175"/>
-      <c r="B60" s="119" t="s">
+      <c r="A60" s="169"/>
+      <c r="B60" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D60" s="49" t="s">
         <v>36</v>
       </c>
       <c r="E60" s="49"/>
-      <c r="H60" s="114"/>
+      <c r="H60" s="111"/>
       <c r="I60" s="67"/>
-      <c r="J60" s="99" t="s">
+      <c r="J60" s="96" t="s">
         <v>93</v>
       </c>
       <c r="K60" s="1" t="s">
@@ -6414,18 +6289,18 @@
       <c r="L60" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="M60" s="80">
+      <c r="M60" s="77">
         <v>0</v>
       </c>
-      <c r="N60" s="80"/>
+      <c r="N60" s="77"/>
       <c r="O60" s="1"/>
-      <c r="P60" s="80">
+      <c r="P60" s="77">
         <v>0</v>
       </c>
       <c r="Q60" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="R60" s="102" t="s">
+      <c r="R60" s="99" t="s">
         <v>52</v>
       </c>
       <c r="S60" s="61" t="s">
@@ -6434,42 +6309,42 @@
       <c r="T60" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="U60" s="123"/>
+      <c r="U60" s="120"/>
       <c r="Y60" s="67"/>
     </row>
     <row r="61" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="175"/>
-      <c r="B61" s="119" t="s">
+      <c r="A61" s="169"/>
+      <c r="B61" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C61" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D61" s="49" t="s">
         <v>36</v>
       </c>
       <c r="E61" s="49"/>
-      <c r="H61" s="114"/>
+      <c r="H61" s="111"/>
       <c r="I61" s="67"/>
-      <c r="J61" s="104" t="s">
-        <v>155</v>
+      <c r="J61" s="101" t="s">
+        <v>152</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L61" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="M61" s="83">
+        <v>154</v>
+      </c>
+      <c r="M61" s="80">
         <v>0</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="133">
+      <c r="P61" s="130">
         <v>0</v>
       </c>
-      <c r="Q61" s="134"/>
-      <c r="R61" s="101" t="s">
+      <c r="Q61" s="131"/>
+      <c r="R61" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S61" s="57" t="s">
@@ -6478,32 +6353,32 @@
       <c r="T61" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="U61" s="86"/>
-      <c r="V61" s="79"/>
+      <c r="U61" s="83"/>
+      <c r="V61" s="76"/>
       <c r="W61" s="3"/>
-      <c r="X61" s="79"/>
+      <c r="X61" s="76"/>
       <c r="Y61" s="69"/>
     </row>
     <row r="62" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="175"/>
-      <c r="B62" s="119" t="s">
+      <c r="A62" s="169"/>
+      <c r="B62" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D62" s="49" t="s">
         <v>47</v>
       </c>
       <c r="E62" s="49"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="114"/>
+      <c r="H62" s="111"/>
       <c r="I62" s="67"/>
-      <c r="J62" s="145"/>
+      <c r="J62" s="142"/>
       <c r="L62" s="6"/>
       <c r="N62"/>
       <c r="P62" s="6"/>
-      <c r="R62" s="101" t="s">
+      <c r="R62" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S62" s="58" t="s">
@@ -6512,29 +6387,29 @@
       <c r="T62" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U62" s="86"/>
+      <c r="U62" s="83"/>
       <c r="Y62" s="67"/>
     </row>
     <row r="63" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="175"/>
-      <c r="B63" s="119" t="s">
+      <c r="A63" s="169"/>
+      <c r="B63" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>47</v>
       </c>
       <c r="E63" s="49"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="114"/>
+      <c r="H63" s="111"/>
       <c r="I63" s="67"/>
-      <c r="J63" s="145"/>
+      <c r="J63" s="142"/>
       <c r="L63" s="6"/>
       <c r="N63"/>
       <c r="P63" s="6"/>
-      <c r="R63" s="101" t="s">
+      <c r="R63" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S63" s="58" t="s">
@@ -6543,12 +6418,12 @@
       <c r="T63" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U63" s="86"/>
+      <c r="U63" s="83"/>
       <c r="Y63" s="67"/>
     </row>
     <row r="64" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="175"/>
-      <c r="B64" s="120" t="s">
+      <c r="A64" s="169"/>
+      <c r="B64" s="117" t="s">
         <v>52</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -6558,11 +6433,11 @@
         <v>47</v>
       </c>
       <c r="E64" s="50"/>
-      <c r="F64" s="79"/>
+      <c r="F64" s="76"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="115"/>
+      <c r="H64" s="112"/>
       <c r="I64" s="69"/>
-      <c r="R64" s="101" t="s">
+      <c r="R64" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S64" s="58" t="s">
@@ -6571,12 +6446,12 @@
       <c r="T64" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U64" s="86"/>
+      <c r="U64" s="83"/>
       <c r="Y64" s="67"/>
     </row>
     <row r="65" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="175"/>
-      <c r="B65" s="120" t="s">
+      <c r="A65" s="169"/>
+      <c r="B65" s="117" t="s">
         <v>52</v>
       </c>
       <c r="C65" t="s">
@@ -6586,13 +6461,13 @@
         <v>47</v>
       </c>
       <c r="E65" s="51"/>
-      <c r="F65" s="80"/>
+      <c r="F65" s="77"/>
       <c r="G65" s="1"/>
-      <c r="H65" s="116"/>
+      <c r="H65" s="113"/>
       <c r="I65" s="68"/>
       <c r="J65" s="18"/>
       <c r="Q65" s="13"/>
-      <c r="R65" s="101" t="s">
+      <c r="R65" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S65" s="58" t="s">
@@ -6601,12 +6476,12 @@
       <c r="T65" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U65" s="86"/>
+      <c r="U65" s="83"/>
       <c r="Y65" s="67"/>
     </row>
     <row r="66" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="175"/>
-      <c r="B66" s="120" t="s">
+      <c r="A66" s="169"/>
+      <c r="B66" s="117" t="s">
         <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -6616,11 +6491,11 @@
         <v>47</v>
       </c>
       <c r="E66" s="49"/>
-      <c r="H66" s="114"/>
+      <c r="H66" s="111"/>
       <c r="I66" s="67"/>
       <c r="J66" s="18"/>
       <c r="Q66" s="13"/>
-      <c r="R66" s="101" t="s">
+      <c r="R66" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S66" s="58" t="s">
@@ -6629,12 +6504,12 @@
       <c r="T66" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U66" s="86"/>
+      <c r="U66" s="83"/>
       <c r="Y66" s="67"/>
     </row>
     <row r="67" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="175"/>
-      <c r="B67" s="120" t="s">
+      <c r="A67" s="169"/>
+      <c r="B67" s="117" t="s">
         <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -6644,11 +6519,11 @@
         <v>47</v>
       </c>
       <c r="E67" s="49"/>
-      <c r="H67" s="114"/>
+      <c r="H67" s="111"/>
       <c r="I67" s="67"/>
       <c r="J67" s="18"/>
       <c r="Q67" s="13"/>
-      <c r="R67" s="101" t="s">
+      <c r="R67" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S67" s="58" t="s">
@@ -6657,12 +6532,12 @@
       <c r="T67" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U67" s="86"/>
+      <c r="U67" s="83"/>
       <c r="Y67" s="67"/>
     </row>
     <row r="68" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="175"/>
-      <c r="B68" s="119" t="s">
+      <c r="A68" s="169"/>
+      <c r="B68" s="116" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -6672,15 +6547,15 @@
         <v>47</v>
       </c>
       <c r="E68" s="50"/>
-      <c r="F68" s="79"/>
+      <c r="F68" s="76"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="115"/>
+      <c r="H68" s="112"/>
       <c r="I68" s="71" t="s">
         <v>106</v>
       </c>
       <c r="J68" s="18"/>
       <c r="Q68" s="13"/>
-      <c r="R68" s="102" t="s">
+      <c r="R68" s="99" t="s">
         <v>53</v>
       </c>
       <c r="S68" s="59" t="s">
@@ -6689,15 +6564,15 @@
       <c r="T68" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="U68" s="86"/>
-      <c r="V68" s="80"/>
+      <c r="U68" s="83"/>
+      <c r="V68" s="77"/>
       <c r="W68" s="1"/>
-      <c r="X68" s="80"/>
+      <c r="X68" s="77"/>
       <c r="Y68" s="68"/>
     </row>
     <row r="69" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="175"/>
-      <c r="B69" s="119" t="s">
+      <c r="A69" s="169"/>
+      <c r="B69" s="116" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -6707,11 +6582,11 @@
         <v>57</v>
       </c>
       <c r="E69" s="49"/>
-      <c r="H69" s="114"/>
+      <c r="H69" s="111"/>
       <c r="I69" s="67"/>
       <c r="J69" s="17"/>
       <c r="Q69" s="13"/>
-      <c r="R69" s="98" t="s">
+      <c r="R69" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S69" s="58" t="s">
@@ -6720,14 +6595,14 @@
       <c r="T69" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U69" s="125"/>
+      <c r="U69" s="122"/>
       <c r="Y69" s="67" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="175"/>
-      <c r="B70" s="119" t="s">
+      <c r="A70" s="169"/>
+      <c r="B70" s="116" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="21" t="s">
@@ -6737,13 +6612,13 @@
         <v>58</v>
       </c>
       <c r="E70" s="51"/>
-      <c r="F70" s="80"/>
+      <c r="F70" s="77"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="116"/>
+      <c r="H70" s="113"/>
       <c r="I70" s="68"/>
       <c r="J70" s="17"/>
       <c r="Q70" s="13"/>
-      <c r="R70" s="98" t="s">
+      <c r="R70" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S70" s="63" t="s">
@@ -6752,12 +6627,12 @@
       <c r="T70" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="U70" s="86"/>
+      <c r="U70" s="83"/>
       <c r="Y70" s="67"/>
     </row>
     <row r="71" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="175"/>
-      <c r="B71" s="119" t="s">
+      <c r="A71" s="169"/>
+      <c r="B71" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -6767,15 +6642,15 @@
         <v>47</v>
       </c>
       <c r="E71" s="49"/>
-      <c r="F71" s="79"/>
+      <c r="F71" s="76"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="115"/>
+      <c r="H71" s="112"/>
       <c r="I71" s="71" t="s">
         <v>106</v>
       </c>
       <c r="J71" s="18"/>
       <c r="Q71" s="13"/>
-      <c r="R71" s="98" t="s">
+      <c r="R71" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S71" s="63" t="s">
@@ -6784,12 +6659,12 @@
       <c r="T71" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="U71" s="86"/>
+      <c r="U71" s="83"/>
       <c r="Y71" s="67"/>
     </row>
     <row r="72" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="175"/>
-      <c r="B72" s="119" t="s">
+      <c r="A72" s="169"/>
+      <c r="B72" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C72" s="8" t="s">
@@ -6799,11 +6674,11 @@
         <v>57</v>
       </c>
       <c r="E72" s="49"/>
-      <c r="H72" s="114"/>
+      <c r="H72" s="111"/>
       <c r="I72" s="67"/>
       <c r="J72" s="18"/>
       <c r="Q72" s="13"/>
-      <c r="R72" s="98" t="s">
+      <c r="R72" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S72" s="64" t="s">
@@ -6812,12 +6687,12 @@
       <c r="T72" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U72" s="86"/>
+      <c r="U72" s="83"/>
       <c r="Y72" s="67"/>
     </row>
     <row r="73" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="175"/>
-      <c r="B73" s="119" t="s">
+      <c r="A73" s="169"/>
+      <c r="B73" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -6827,11 +6702,11 @@
         <v>58</v>
       </c>
       <c r="E73" s="49"/>
-      <c r="H73" s="114"/>
+      <c r="H73" s="111"/>
       <c r="I73" s="67"/>
       <c r="J73" s="18"/>
       <c r="Q73" s="13"/>
-      <c r="R73" s="98" t="s">
+      <c r="R73" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S73" s="64" t="s">
@@ -6840,12 +6715,12 @@
       <c r="T73" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U73" s="123"/>
+      <c r="U73" s="120"/>
       <c r="Y73" s="67"/>
     </row>
     <row r="74" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="175"/>
-      <c r="B74" s="119" t="s">
+      <c r="A74" s="169"/>
+      <c r="B74" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C74" s="8" t="s">
@@ -6855,29 +6730,29 @@
         <v>47</v>
       </c>
       <c r="E74" s="49"/>
-      <c r="H74" s="114"/>
+      <c r="H74" s="111"/>
       <c r="I74" s="67"/>
       <c r="J74" s="17"/>
       <c r="L74" s="6"/>
       <c r="Q74" s="13"/>
-      <c r="R74" s="103" t="s">
-        <v>149</v>
+      <c r="R74" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T74" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="U74" s="148"/>
-      <c r="V74" s="79"/>
+      <c r="U74" s="145"/>
+      <c r="V74" s="76"/>
       <c r="W74" s="3"/>
-      <c r="X74" s="79"/>
+      <c r="X74" s="76"/>
       <c r="Y74" s="69"/>
     </row>
     <row r="75" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="175"/>
-      <c r="B75" s="119" t="s">
+      <c r="A75" s="169"/>
+      <c r="B75" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -6887,12 +6762,12 @@
         <v>47</v>
       </c>
       <c r="E75" s="49"/>
-      <c r="H75" s="114"/>
+      <c r="H75" s="111"/>
       <c r="I75" s="67"/>
       <c r="J75" s="17"/>
       <c r="Q75" s="13"/>
-      <c r="R75" s="98" t="s">
-        <v>149</v>
+      <c r="R75" s="95" t="s">
+        <v>146</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>75</v>
@@ -6900,12 +6775,12 @@
       <c r="T75" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="U75" s="86"/>
+      <c r="U75" s="83"/>
       <c r="Y75" s="67"/>
     </row>
     <row r="76" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="175"/>
-      <c r="B76" s="119" t="s">
+      <c r="A76" s="169"/>
+      <c r="B76" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -6915,13 +6790,13 @@
         <v>47</v>
       </c>
       <c r="E76" s="49"/>
-      <c r="H76" s="114"/>
+      <c r="H76" s="111"/>
       <c r="I76" s="67"/>
       <c r="J76" s="17"/>
       <c r="L76" s="6"/>
       <c r="Q76" s="13"/>
-      <c r="R76" s="99" t="s">
-        <v>149</v>
+      <c r="R76" s="96" t="s">
+        <v>146</v>
       </c>
       <c r="S76" s="22" t="s">
         <v>76</v>
@@ -6929,15 +6804,15 @@
       <c r="T76" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="U76" s="86"/>
-      <c r="V76" s="80"/>
+      <c r="U76" s="83"/>
+      <c r="V76" s="77"/>
       <c r="W76" s="1"/>
-      <c r="X76" s="80"/>
+      <c r="X76" s="77"/>
       <c r="Y76" s="68"/>
     </row>
     <row r="77" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="175"/>
-      <c r="B77" s="119" t="s">
+      <c r="A77" s="169"/>
+      <c r="B77" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -6947,29 +6822,29 @@
         <v>47</v>
       </c>
       <c r="E77" s="49"/>
-      <c r="H77" s="114"/>
+      <c r="H77" s="111"/>
       <c r="I77" s="67"/>
       <c r="J77" s="17"/>
       <c r="L77" s="6"/>
       <c r="Q77" s="13"/>
-      <c r="R77" s="103" t="s">
-        <v>150</v>
+      <c r="R77" s="100" t="s">
+        <v>147</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="T77" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="U77" s="147"/>
-      <c r="V77" s="79"/>
+      <c r="U77" s="144"/>
+      <c r="V77" s="76"/>
       <c r="W77" s="3"/>
-      <c r="X77" s="79"/>
+      <c r="X77" s="76"/>
       <c r="Y77" s="69"/>
     </row>
     <row r="78" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="175"/>
-      <c r="B78" s="119" t="s">
+      <c r="A78" s="169"/>
+      <c r="B78" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="8" t="s">
@@ -6979,13 +6854,13 @@
         <v>47</v>
       </c>
       <c r="E78" s="49"/>
-      <c r="H78" s="114"/>
+      <c r="H78" s="111"/>
       <c r="I78" s="67"/>
       <c r="J78" s="17"/>
       <c r="L78" s="6"/>
       <c r="Q78" s="13"/>
-      <c r="R78" s="98" t="s">
-        <v>150</v>
+      <c r="R78" s="95" t="s">
+        <v>147</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>75</v>
@@ -6993,12 +6868,12 @@
       <c r="T78" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="U78" s="86"/>
+      <c r="U78" s="83"/>
       <c r="Y78" s="67"/>
     </row>
     <row r="79" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="175"/>
-      <c r="B79" s="119" t="s">
+      <c r="A79" s="169"/>
+      <c r="B79" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="8" t="s">
@@ -7008,12 +6883,12 @@
         <v>47</v>
       </c>
       <c r="E79" s="49"/>
-      <c r="H79" s="114"/>
+      <c r="H79" s="111"/>
       <c r="I79" s="67"/>
       <c r="J79" s="17"/>
       <c r="Q79" s="13"/>
-      <c r="R79" s="99" t="s">
-        <v>150</v>
+      <c r="R79" s="96" t="s">
+        <v>147</v>
       </c>
       <c r="S79" s="22" t="s">
         <v>76</v>
@@ -7021,15 +6896,15 @@
       <c r="T79" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="U79" s="123"/>
-      <c r="V79" s="80"/>
+      <c r="U79" s="120"/>
+      <c r="V79" s="77"/>
       <c r="W79" s="1"/>
-      <c r="X79" s="80"/>
+      <c r="X79" s="77"/>
       <c r="Y79" s="68"/>
     </row>
     <row r="80" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="175"/>
-      <c r="B80" s="119" t="s">
+      <c r="A80" s="169"/>
+      <c r="B80" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -7039,14 +6914,14 @@
         <v>47</v>
       </c>
       <c r="E80" s="49"/>
-      <c r="H80" s="114"/>
+      <c r="H80" s="111"/>
       <c r="I80" s="67"/>
       <c r="J80" s="17"/>
       <c r="Q80" s="13"/>
     </row>
     <row r="81" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="175"/>
-      <c r="B81" s="119" t="s">
+      <c r="A81" s="169"/>
+      <c r="B81" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="21" t="s">
@@ -7056,16 +6931,16 @@
         <v>47</v>
       </c>
       <c r="E81" s="49"/>
-      <c r="F81" s="80"/>
+      <c r="F81" s="77"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="116"/>
+      <c r="H81" s="113"/>
       <c r="I81" s="68"/>
       <c r="J81" s="18"/>
       <c r="Q81" s="13"/>
     </row>
     <row r="82" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="175"/>
-      <c r="B82" s="119" t="s">
+      <c r="A82" s="169"/>
+      <c r="B82" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C82" t="s">
@@ -7075,7 +6950,7 @@
         <v>47</v>
       </c>
       <c r="E82" s="50"/>
-      <c r="H82" s="114"/>
+      <c r="H82" s="111"/>
       <c r="I82" s="71" t="s">
         <v>106</v>
       </c>
@@ -7083,8 +6958,8 @@
       <c r="Q82" s="13"/>
     </row>
     <row r="83" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="175"/>
-      <c r="B83" s="119" t="s">
+      <c r="A83" s="169"/>
+      <c r="B83" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="14" t="s">
@@ -7094,14 +6969,14 @@
         <v>57</v>
       </c>
       <c r="E83" s="49"/>
-      <c r="H83" s="114"/>
+      <c r="H83" s="111"/>
       <c r="I83" s="67"/>
       <c r="J83" s="18"/>
       <c r="Q83" s="13"/>
     </row>
     <row r="84" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="175"/>
-      <c r="B84" s="119" t="s">
+      <c r="A84" s="169"/>
+      <c r="B84" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C84" s="14" t="s">
@@ -7111,7 +6986,7 @@
         <v>58</v>
       </c>
       <c r="E84" s="49"/>
-      <c r="H84" s="114"/>
+      <c r="H84" s="111"/>
       <c r="I84" s="67"/>
       <c r="J84" s="18"/>
       <c r="Q84" s="13"/>
@@ -7119,8 +6994,8 @@
       <c r="Y84" s="13"/>
     </row>
     <row r="85" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="175"/>
-      <c r="B85" s="119" t="s">
+      <c r="A85" s="169"/>
+      <c r="B85" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C85" s="14" t="s">
@@ -7130,7 +7005,7 @@
         <v>47</v>
       </c>
       <c r="E85" s="49"/>
-      <c r="H85" s="114"/>
+      <c r="H85" s="111"/>
       <c r="I85" s="67"/>
       <c r="J85" s="18"/>
       <c r="Q85" s="13"/>
@@ -7138,8 +7013,8 @@
       <c r="Y85" s="13"/>
     </row>
     <row r="86" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="175"/>
-      <c r="B86" s="119" t="s">
+      <c r="A86" s="169"/>
+      <c r="B86" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C86" s="14" t="s">
@@ -7149,7 +7024,7 @@
         <v>47</v>
       </c>
       <c r="E86" s="49"/>
-      <c r="H86" s="114"/>
+      <c r="H86" s="111"/>
       <c r="I86" s="67"/>
       <c r="J86" s="18"/>
       <c r="Q86" s="13"/>
@@ -7157,8 +7032,8 @@
       <c r="Y86" s="13"/>
     </row>
     <row r="87" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="175"/>
-      <c r="B87" s="119" t="s">
+      <c r="A87" s="169"/>
+      <c r="B87" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C87" s="14" t="s">
@@ -7168,7 +7043,7 @@
         <v>47</v>
       </c>
       <c r="E87" s="49"/>
-      <c r="H87" s="114"/>
+      <c r="H87" s="111"/>
       <c r="I87" s="67"/>
       <c r="J87" s="18"/>
       <c r="Q87" s="13"/>
@@ -7176,8 +7051,8 @@
       <c r="Y87" s="13"/>
     </row>
     <row r="88" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="175"/>
-      <c r="B88" s="119" t="s">
+      <c r="A88" s="169"/>
+      <c r="B88" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="14" t="s">
@@ -7187,7 +7062,7 @@
         <v>47</v>
       </c>
       <c r="E88" s="49"/>
-      <c r="H88" s="114"/>
+      <c r="H88" s="111"/>
       <c r="I88" s="67"/>
       <c r="J88" s="18"/>
       <c r="Q88" s="13"/>
@@ -7195,8 +7070,8 @@
       <c r="Y88" s="13"/>
     </row>
     <row r="89" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="175"/>
-      <c r="B89" s="104" t="s">
+      <c r="A89" s="169"/>
+      <c r="B89" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -7206,7 +7081,7 @@
         <v>47</v>
       </c>
       <c r="E89" s="49"/>
-      <c r="H89" s="114"/>
+      <c r="H89" s="111"/>
       <c r="I89" s="67"/>
       <c r="J89" s="18"/>
       <c r="Q89" s="13"/>
@@ -7214,8 +7089,8 @@
       <c r="Y89" s="13"/>
     </row>
     <row r="90" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="175"/>
-      <c r="B90" s="119" t="s">
+      <c r="A90" s="169"/>
+      <c r="B90" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="14" t="s">
@@ -7225,7 +7100,7 @@
         <v>47</v>
       </c>
       <c r="E90" s="49"/>
-      <c r="H90" s="114"/>
+      <c r="H90" s="111"/>
       <c r="I90" s="67"/>
       <c r="J90" s="18"/>
       <c r="Q90" s="13"/>
@@ -7234,8 +7109,8 @@
       <c r="Y90" s="13"/>
     </row>
     <row r="91" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="175"/>
-      <c r="B91" s="119" t="s">
+      <c r="A91" s="169"/>
+      <c r="B91" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C91" s="14" t="s">
@@ -7245,7 +7120,7 @@
         <v>47</v>
       </c>
       <c r="E91" s="49"/>
-      <c r="H91" s="114"/>
+      <c r="H91" s="111"/>
       <c r="I91" s="67"/>
       <c r="J91" s="18"/>
       <c r="Q91" s="13"/>
@@ -7254,8 +7129,8 @@
       <c r="Y91" s="13"/>
     </row>
     <row r="92" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="175"/>
-      <c r="B92" s="119" t="s">
+      <c r="A92" s="169"/>
+      <c r="B92" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="14" t="s">
@@ -7265,7 +7140,7 @@
         <v>47</v>
       </c>
       <c r="E92" s="49"/>
-      <c r="H92" s="114"/>
+      <c r="H92" s="111"/>
       <c r="I92" s="67"/>
       <c r="J92" s="18"/>
       <c r="Q92" s="13"/>
@@ -7274,8 +7149,8 @@
       <c r="Y92" s="13"/>
     </row>
     <row r="93" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="175"/>
-      <c r="B93" s="119" t="s">
+      <c r="A93" s="169"/>
+      <c r="B93" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C93" s="14" t="s">
@@ -7285,7 +7160,7 @@
         <v>47</v>
       </c>
       <c r="E93" s="49"/>
-      <c r="H93" s="114"/>
+      <c r="H93" s="111"/>
       <c r="I93" s="67"/>
       <c r="J93" s="18"/>
       <c r="Q93" s="13"/>
@@ -7294,8 +7169,8 @@
       <c r="Y93" s="13"/>
     </row>
     <row r="94" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="175"/>
-      <c r="B94" s="119" t="s">
+      <c r="A94" s="169"/>
+      <c r="B94" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C94" s="14" t="s">
@@ -7305,7 +7180,7 @@
         <v>47</v>
       </c>
       <c r="E94" s="49"/>
-      <c r="H94" s="114"/>
+      <c r="H94" s="111"/>
       <c r="I94" s="67"/>
       <c r="J94" s="18"/>
       <c r="Q94" s="13"/>
@@ -7314,8 +7189,8 @@
       <c r="Y94" s="13"/>
     </row>
     <row r="95" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="175"/>
-      <c r="B95" s="119" t="s">
+      <c r="A95" s="169"/>
+      <c r="B95" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C95" s="14" t="s">
@@ -7325,7 +7200,7 @@
         <v>36</v>
       </c>
       <c r="E95" s="49"/>
-      <c r="H95" s="114"/>
+      <c r="H95" s="111"/>
       <c r="I95" s="67"/>
       <c r="J95" s="18"/>
       <c r="Q95" s="13"/>
@@ -7333,36 +7208,36 @@
       <c r="Y95" s="13"/>
     </row>
     <row r="96" spans="1:25" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="176"/>
-      <c r="B96" s="121" t="s">
+      <c r="A96" s="170"/>
+      <c r="B96" s="118" t="s">
         <v>68</v>
       </c>
       <c r="C96" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D96" s="105" t="s">
+      <c r="D96" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="E96" s="105"/>
-      <c r="F96" s="81"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="78"/>
       <c r="G96" s="15"/>
-      <c r="H96" s="117"/>
+      <c r="H96" s="114"/>
       <c r="I96" s="72"/>
       <c r="J96" s="19"/>
       <c r="K96" s="15"/>
       <c r="L96" s="15"/>
-      <c r="M96" s="81"/>
-      <c r="N96" s="81"/>
+      <c r="M96" s="78"/>
+      <c r="N96" s="78"/>
       <c r="O96" s="15"/>
       <c r="P96" s="15"/>
       <c r="Q96" s="16"/>
       <c r="R96" s="19"/>
       <c r="S96" s="15"/>
       <c r="T96" s="15"/>
-      <c r="U96" s="90"/>
-      <c r="V96" s="81"/>
+      <c r="U96" s="87"/>
+      <c r="V96" s="78"/>
       <c r="W96" s="15"/>
-      <c r="X96" s="81"/>
+      <c r="X96" s="78"/>
       <c r="Y96" s="16"/>
     </row>
     <row r="97" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7400,9 +7275,9 @@
       <c r="B102" s="45"/>
       <c r="C102" s="14"/>
       <c r="D102" s="6"/>
-      <c r="F102" s="143"/>
-      <c r="G102" s="137"/>
-      <c r="H102" s="138"/>
+      <c r="F102" s="140"/>
+      <c r="G102" s="134"/>
+      <c r="H102" s="135"/>
       <c r="T102" s="6"/>
     </row>
     <row r="103" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7410,7 +7285,7 @@
       <c r="B103" s="45"/>
       <c r="C103" s="14"/>
       <c r="D103" s="6"/>
-      <c r="F103" s="169"/>
+      <c r="F103" s="173"/>
       <c r="T103" s="6"/>
     </row>
     <row r="104" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7418,7 +7293,7 @@
       <c r="B104" s="45"/>
       <c r="C104" s="14"/>
       <c r="D104" s="6"/>
-      <c r="F104" s="169"/>
+      <c r="F104" s="173"/>
       <c r="T104" s="6"/>
     </row>
     <row r="105" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7426,14 +7301,14 @@
       <c r="B105" s="45"/>
       <c r="C105" s="14"/>
       <c r="D105" s="6"/>
-      <c r="F105" s="169"/>
+      <c r="F105" s="173"/>
     </row>
     <row r="106" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="46"/>
       <c r="B106" s="45"/>
       <c r="C106" s="14"/>
       <c r="D106" s="6"/>
-      <c r="F106" s="169"/>
+      <c r="F106" s="173"/>
       <c r="T106" s="6"/>
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7447,14 +7322,14 @@
       <c r="A108" s="9"/>
       <c r="B108" s="7"/>
       <c r="D108" s="6"/>
-      <c r="F108" s="170"/>
+      <c r="F108" s="174"/>
       <c r="T108" s="6"/>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" s="9"/>
       <c r="B109" s="7"/>
       <c r="D109" s="6"/>
-      <c r="F109" s="170"/>
+      <c r="F109" s="174"/>
       <c r="T109" s="6"/>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.35">
@@ -7467,14 +7342,14 @@
       <c r="A111" s="9"/>
       <c r="B111" s="7"/>
       <c r="D111" s="6"/>
-      <c r="F111" s="170"/>
+      <c r="F111" s="174"/>
       <c r="T111" s="6"/>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" s="9"/>
       <c r="B112" s="7"/>
       <c r="D112" s="6"/>
-      <c r="F112" s="170"/>
+      <c r="F112" s="174"/>
       <c r="T112" s="6"/>
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.35">
@@ -7487,21 +7362,21 @@
       <c r="A114" s="9"/>
       <c r="B114" s="7"/>
       <c r="D114" s="6"/>
-      <c r="F114" s="170"/>
+      <c r="F114" s="174"/>
       <c r="T114" s="6"/>
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" s="9"/>
       <c r="B115" s="7"/>
       <c r="D115" s="6"/>
-      <c r="F115" s="170"/>
+      <c r="F115" s="174"/>
       <c r="T115" s="6"/>
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" s="9"/>
       <c r="B116" s="7"/>
       <c r="D116" s="6"/>
-      <c r="F116" s="170"/>
+      <c r="F116" s="174"/>
       <c r="T116" s="6"/>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.35">
@@ -7514,7 +7389,7 @@
       <c r="A118" s="9"/>
       <c r="B118" s="7"/>
       <c r="D118" s="6"/>
-      <c r="F118" s="170"/>
+      <c r="F118" s="174"/>
       <c r="T118" s="6"/>
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.35">
@@ -7522,43 +7397,43 @@
       <c r="B119" s="7"/>
       <c r="C119" s="10"/>
       <c r="D119" s="6"/>
-      <c r="F119" s="170"/>
+      <c r="F119" s="174"/>
       <c r="T119" s="6"/>
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F120" s="170"/>
+      <c r="F120" s="174"/>
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F121" s="170"/>
+      <c r="F121" s="174"/>
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F122" s="170"/>
+      <c r="F122" s="174"/>
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F123" s="170"/>
+      <c r="F123" s="174"/>
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F124" s="170"/>
+      <c r="F124" s="174"/>
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F125" s="170"/>
+      <c r="F125" s="174"/>
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="F126" s="170"/>
+      <c r="F126" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="F103:F106"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="F111:F112"/>
+    <mergeCell ref="F114:F116"/>
+    <mergeCell ref="F118:F126"/>
     <mergeCell ref="R1:Y1"/>
     <mergeCell ref="A50:A96"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
     <mergeCell ref="A3:A49"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="F103:F106"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="F111:F112"/>
-    <mergeCell ref="F114:F116"/>
-    <mergeCell ref="F118:F126"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7611,40 +7486,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="177"/>
-      <c r="B1" s="171" t="s">
+      <c r="A1" s="171"/>
+      <c r="B1" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="171" t="s">
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="173"/>
-      <c r="R1" s="171" t="s">
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="165" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="172"/>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="173"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="167"/>
     </row>
     <row r="2" spans="1:25" s="5" customFormat="1" ht="56.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="178"/>
+      <c r="A2" s="172"/>
       <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
@@ -7701,7 +7576,7 @@
         <f t="shared" si="0"/>
         <v>Commentaire</v>
       </c>
-      <c r="R2" s="124" t="str">
+      <c r="R2" s="121" t="str">
         <f t="shared" ref="R2:Y2" si="1">B2</f>
         <v>Catégorie</v>
       </c>
@@ -7735,10 +7610,10 @@
       </c>
     </row>
     <row r="3" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="174" t="s">
+      <c r="A3" s="168" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="104" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -7747,7 +7622,7 @@
       <c r="D3" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="75">
         <v>10</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -7758,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="66"/>
-      <c r="J3" s="97" t="s">
+      <c r="J3" s="94" t="s">
         <v>54</v>
       </c>
       <c r="K3" t="s">
@@ -7767,7 +7642,7 @@
       <c r="L3" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="189">
+      <c r="M3" s="160">
         <v>10</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -7778,30 +7653,30 @@
         <v>0</v>
       </c>
       <c r="Q3" s="66"/>
-      <c r="R3" s="97" t="s">
+      <c r="R3" s="94" t="s">
         <v>51</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="76">
+      <c r="T3" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="73">
         <v>10</v>
       </c>
-      <c r="V3" s="78" t="s">
+      <c r="V3" s="75" t="s">
         <v>84</v>
       </c>
       <c r="W3" s="32"/>
-      <c r="X3" s="126">
+      <c r="X3" s="123">
         <v>0</v>
       </c>
       <c r="Y3" s="66"/>
     </row>
     <row r="4" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="175"/>
-      <c r="B4" s="104" t="s">
+      <c r="A4" s="169"/>
+      <c r="B4" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
@@ -7813,7 +7688,7 @@
       <c r="G4" s="33"/>
       <c r="H4" s="33"/>
       <c r="I4" s="67"/>
-      <c r="J4" s="98" t="s">
+      <c r="J4" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K4" t="s">
@@ -7822,11 +7697,11 @@
       <c r="L4" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="162"/>
+      <c r="M4" s="155"/>
       <c r="O4" s="33"/>
       <c r="P4" s="33"/>
       <c r="Q4" s="67"/>
-      <c r="R4" s="98" t="s">
+      <c r="R4" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S4" t="s">
@@ -7837,12 +7712,12 @@
       </c>
       <c r="U4" s="49"/>
       <c r="W4" s="33"/>
-      <c r="X4" s="129"/>
+      <c r="X4" s="126"/>
       <c r="Y4" s="67"/>
     </row>
     <row r="5" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="175"/>
-      <c r="B5" s="104" t="s">
+      <c r="A5" s="169"/>
+      <c r="B5" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C5" t="s">
@@ -7854,7 +7729,7 @@
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
       <c r="I5" s="67"/>
-      <c r="J5" s="98" t="s">
+      <c r="J5" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K5" t="s">
@@ -7863,11 +7738,11 @@
       <c r="L5" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="162"/>
+      <c r="M5" s="155"/>
       <c r="O5" s="33"/>
       <c r="P5" s="33"/>
       <c r="Q5" s="67"/>
-      <c r="R5" s="98" t="s">
+      <c r="R5" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S5" t="s">
@@ -7878,12 +7753,12 @@
       </c>
       <c r="U5" s="49"/>
       <c r="W5" s="33"/>
-      <c r="X5" s="129"/>
+      <c r="X5" s="126"/>
       <c r="Y5" s="67"/>
     </row>
     <row r="6" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="175"/>
-      <c r="B6" s="104" t="s">
+      <c r="A6" s="169"/>
+      <c r="B6" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C6" t="s">
@@ -7895,7 +7770,7 @@
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
       <c r="I6" s="67"/>
-      <c r="J6" s="98" t="s">
+      <c r="J6" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K6" t="s">
@@ -7904,11 +7779,11 @@
       <c r="L6" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="162"/>
+      <c r="M6" s="155"/>
       <c r="O6" s="33"/>
       <c r="P6" s="33"/>
       <c r="Q6" s="67"/>
-      <c r="R6" s="98" t="s">
+      <c r="R6" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S6" t="s">
@@ -7919,12 +7794,12 @@
       </c>
       <c r="U6" s="49"/>
       <c r="W6" s="33"/>
-      <c r="X6" s="129"/>
+      <c r="X6" s="126"/>
       <c r="Y6" s="67"/>
     </row>
     <row r="7" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="175"/>
-      <c r="B7" s="104" t="s">
+      <c r="A7" s="169"/>
+      <c r="B7" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C7" t="s">
@@ -7936,7 +7811,7 @@
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="67"/>
-      <c r="J7" s="98" t="s">
+      <c r="J7" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K7" t="s">
@@ -7945,11 +7820,11 @@
       <c r="L7" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="162"/>
+      <c r="M7" s="155"/>
       <c r="O7" s="33"/>
       <c r="P7" s="33"/>
       <c r="Q7" s="67"/>
-      <c r="R7" s="98" t="s">
+      <c r="R7" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S7" t="s">
@@ -7960,12 +7835,12 @@
       </c>
       <c r="U7" s="49"/>
       <c r="W7" s="33"/>
-      <c r="X7" s="129"/>
+      <c r="X7" s="126"/>
       <c r="Y7" s="67"/>
     </row>
     <row r="8" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="175"/>
-      <c r="B8" s="104" t="s">
+      <c r="A8" s="169"/>
+      <c r="B8" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
@@ -7977,7 +7852,7 @@
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
       <c r="I8" s="67"/>
-      <c r="J8" s="98" t="s">
+      <c r="J8" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K8" t="s">
@@ -7986,11 +7861,11 @@
       <c r="L8" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="162"/>
+      <c r="M8" s="155"/>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
       <c r="Q8" s="67"/>
-      <c r="R8" s="98" t="s">
+      <c r="R8" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S8" t="s">
@@ -8001,12 +7876,12 @@
       </c>
       <c r="U8" s="49"/>
       <c r="W8" s="33"/>
-      <c r="X8" s="129"/>
+      <c r="X8" s="126"/>
       <c r="Y8" s="67"/>
     </row>
     <row r="9" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="175"/>
-      <c r="B9" s="104" t="s">
+      <c r="A9" s="169"/>
+      <c r="B9" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
@@ -8018,7 +7893,7 @@
       <c r="G9" s="33"/>
       <c r="H9" s="33"/>
       <c r="I9" s="67"/>
-      <c r="J9" s="98" t="s">
+      <c r="J9" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K9" t="s">
@@ -8027,11 +7902,11 @@
       <c r="L9" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="162"/>
+      <c r="M9" s="155"/>
       <c r="O9" s="33"/>
       <c r="P9" s="33"/>
       <c r="Q9" s="67"/>
-      <c r="R9" s="98" t="s">
+      <c r="R9" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S9" t="s">
@@ -8042,12 +7917,12 @@
       </c>
       <c r="U9" s="49"/>
       <c r="W9" s="33"/>
-      <c r="X9" s="129"/>
+      <c r="X9" s="126"/>
       <c r="Y9" s="67"/>
     </row>
     <row r="10" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="175"/>
-      <c r="B10" s="104" t="s">
+      <c r="A10" s="169"/>
+      <c r="B10" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C10" t="s">
@@ -8059,7 +7934,7 @@
       <c r="G10" s="33"/>
       <c r="H10" s="33"/>
       <c r="I10" s="67"/>
-      <c r="J10" s="98" t="s">
+      <c r="J10" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K10" t="s">
@@ -8068,11 +7943,11 @@
       <c r="L10" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="162"/>
+      <c r="M10" s="155"/>
       <c r="O10" s="33"/>
       <c r="P10" s="33"/>
       <c r="Q10" s="67"/>
-      <c r="R10" s="99" t="s">
+      <c r="R10" s="96" t="s">
         <v>51</v>
       </c>
       <c r="S10" s="1" t="s">
@@ -8082,14 +7957,14 @@
         <v>47</v>
       </c>
       <c r="U10" s="51"/>
-      <c r="V10" s="80"/>
+      <c r="V10" s="77"/>
       <c r="W10" s="35"/>
-      <c r="X10" s="127"/>
+      <c r="X10" s="124"/>
       <c r="Y10" s="68"/>
     </row>
     <row r="11" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="175"/>
-      <c r="B11" s="104" t="s">
+      <c r="A11" s="169"/>
+      <c r="B11" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C11" t="s">
@@ -8101,7 +7976,7 @@
       <c r="G11" s="33"/>
       <c r="H11" s="33"/>
       <c r="I11" s="67"/>
-      <c r="J11" s="98" t="s">
+      <c r="J11" s="95" t="s">
         <v>54</v>
       </c>
       <c r="K11" t="s">
@@ -8110,11 +7985,11 @@
       <c r="L11" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="162"/>
+      <c r="M11" s="155"/>
       <c r="O11" s="33"/>
       <c r="P11" s="33"/>
       <c r="Q11" s="67"/>
-      <c r="R11" s="100" t="s">
+      <c r="R11" s="97" t="s">
         <v>52</v>
       </c>
       <c r="S11" s="2" t="s">
@@ -8123,14 +7998,14 @@
       <c r="T11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="V11" s="79"/>
+      <c r="V11" s="76"/>
       <c r="W11" s="34"/>
-      <c r="X11" s="128"/>
-      <c r="Y11" s="131"/>
+      <c r="X11" s="125"/>
+      <c r="Y11" s="128"/>
     </row>
     <row r="12" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="175"/>
-      <c r="B12" s="104" t="s">
+      <c r="A12" s="169"/>
+      <c r="B12" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
@@ -8142,7 +8017,7 @@
       <c r="G12" s="33"/>
       <c r="H12" s="33"/>
       <c r="I12" s="67"/>
-      <c r="J12" s="104" t="s">
+      <c r="J12" s="101" t="s">
         <v>92</v>
       </c>
       <c r="K12" s="48" t="s">
@@ -8151,14 +8026,14 @@
       <c r="L12" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="190"/>
+      <c r="M12" s="161"/>
       <c r="N12" s="4"/>
       <c r="O12" s="36"/>
       <c r="P12" s="36"/>
       <c r="Q12" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="R12" s="101" t="s">
+      <c r="R12" s="98" t="s">
         <v>52</v>
       </c>
       <c r="S12" s="60" t="s">
@@ -8169,16 +8044,16 @@
       </c>
       <c r="U12" s="49"/>
       <c r="W12" s="33"/>
-      <c r="X12" s="129"/>
-      <c r="Y12" s="130"/>
+      <c r="X12" s="126"/>
+      <c r="Y12" s="127"/>
     </row>
     <row r="13" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="175"/>
-      <c r="B13" s="104" t="s">
+      <c r="A13" s="169"/>
+      <c r="B13" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D13" s="53" t="s">
         <v>36</v>
@@ -8186,7 +8061,7 @@
       <c r="G13" s="33"/>
       <c r="H13" s="33"/>
       <c r="I13" s="67"/>
-      <c r="J13" s="99" t="s">
+      <c r="J13" s="96" t="s">
         <v>93</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -8195,14 +8070,14 @@
       <c r="L13" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="M13" s="190"/>
+      <c r="M13" s="161"/>
       <c r="N13" s="1"/>
       <c r="O13" s="35"/>
       <c r="P13" s="35"/>
       <c r="Q13" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="R13" s="102" t="s">
+      <c r="R13" s="99" t="s">
         <v>52</v>
       </c>
       <c r="S13" s="61" t="s">
@@ -8211,19 +8086,19 @@
       <c r="T13" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="U13" s="80"/>
-      <c r="V13" s="80"/>
+      <c r="U13" s="77"/>
+      <c r="V13" s="77"/>
       <c r="W13" s="35"/>
-      <c r="X13" s="127"/>
+      <c r="X13" s="124"/>
       <c r="Y13" s="68"/>
     </row>
     <row r="14" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="175"/>
-      <c r="B14" s="104" t="s">
+      <c r="A14" s="169"/>
+      <c r="B14" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D14" s="53" t="s">
         <v>36</v>
@@ -8231,21 +8106,21 @@
       <c r="G14" s="33"/>
       <c r="H14" s="33"/>
       <c r="I14" s="67"/>
-      <c r="J14" s="104" t="s">
-        <v>155</v>
+      <c r="J14" s="101" t="s">
+        <v>152</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L14" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="M14" s="191"/>
+        <v>154</v>
+      </c>
+      <c r="M14" s="157"/>
       <c r="N14" s="4"/>
       <c r="O14" s="36"/>
-      <c r="P14" s="135"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="101" t="s">
+      <c r="P14" s="132"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S14" s="60" t="s">
@@ -8256,16 +8131,16 @@
       </c>
       <c r="U14" s="50"/>
       <c r="W14" s="33"/>
-      <c r="X14" s="129"/>
+      <c r="X14" s="126"/>
       <c r="Y14" s="67"/>
     </row>
     <row r="15" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="175"/>
-      <c r="B15" s="104" t="s">
+      <c r="A15" s="169"/>
+      <c r="B15" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" s="53" t="s">
         <v>47</v>
@@ -8273,12 +8148,12 @@
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
       <c r="I15" s="67"/>
-      <c r="J15" s="145"/>
+      <c r="J15" s="142"/>
       <c r="L15" s="6"/>
-      <c r="M15" s="192"/>
+      <c r="M15" s="162"/>
       <c r="O15" s="33"/>
-      <c r="P15" s="146"/>
-      <c r="R15" s="101" t="s">
+      <c r="P15" s="143"/>
+      <c r="R15" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S15" s="60" t="s">
@@ -8289,16 +8164,16 @@
       </c>
       <c r="U15" s="49"/>
       <c r="W15" s="33"/>
-      <c r="X15" s="129"/>
+      <c r="X15" s="126"/>
       <c r="Y15" s="67"/>
     </row>
     <row r="16" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="175"/>
-      <c r="B16" s="104" t="s">
+      <c r="A16" s="169"/>
+      <c r="B16" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D16" s="53" t="s">
         <v>47</v>
@@ -8306,11 +8181,11 @@
       <c r="G16" s="33"/>
       <c r="H16" s="33"/>
       <c r="I16" s="67"/>
-      <c r="J16" s="145"/>
+      <c r="J16" s="142"/>
       <c r="L16" s="6"/>
       <c r="O16" s="33"/>
-      <c r="P16" s="146"/>
-      <c r="R16" s="101" t="s">
+      <c r="P16" s="143"/>
+      <c r="R16" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S16" s="60" t="s">
@@ -8321,12 +8196,12 @@
       </c>
       <c r="U16" s="49"/>
       <c r="W16" s="33"/>
-      <c r="X16" s="129"/>
+      <c r="X16" s="126"/>
       <c r="Y16" s="67"/>
     </row>
     <row r="17" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="175"/>
-      <c r="B17" s="110" t="s">
+      <c r="A17" s="169"/>
+      <c r="B17" s="107" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -8335,14 +8210,14 @@
       <c r="D17" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="79"/>
+      <c r="E17" s="76"/>
       <c r="F17" s="3"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="69"/>
       <c r="O17" s="33"/>
       <c r="P17" s="33"/>
-      <c r="R17" s="101" t="s">
+      <c r="R17" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S17" s="60" t="s">
@@ -8353,12 +8228,12 @@
       </c>
       <c r="U17" s="49"/>
       <c r="W17" s="33"/>
-      <c r="X17" s="129"/>
+      <c r="X17" s="126"/>
       <c r="Y17" s="67"/>
     </row>
     <row r="18" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="175"/>
-      <c r="B18" s="110" t="s">
+      <c r="A18" s="169"/>
+      <c r="B18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
@@ -8374,7 +8249,7 @@
       <c r="O18" s="33"/>
       <c r="P18" s="33"/>
       <c r="Q18" s="13"/>
-      <c r="R18" s="101" t="s">
+      <c r="R18" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S18" s="60" t="s">
@@ -8385,12 +8260,12 @@
       </c>
       <c r="U18" s="49"/>
       <c r="W18" s="33"/>
-      <c r="X18" s="129"/>
+      <c r="X18" s="126"/>
       <c r="Y18" s="67"/>
     </row>
     <row r="19" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="175"/>
-      <c r="B19" s="110" t="s">
+      <c r="A19" s="169"/>
+      <c r="B19" s="107" t="s">
         <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -8399,7 +8274,7 @@
       <c r="D19" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="79"/>
+      <c r="E19" s="76"/>
       <c r="F19" s="3"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
@@ -8408,7 +8283,7 @@
       <c r="O19" s="33"/>
       <c r="P19" s="33"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="101" t="s">
+      <c r="R19" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S19" s="60" t="s">
@@ -8419,12 +8294,12 @@
       </c>
       <c r="U19" s="49"/>
       <c r="W19" s="33"/>
-      <c r="X19" s="129"/>
+      <c r="X19" s="126"/>
       <c r="Y19" s="67"/>
     </row>
     <row r="20" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="175"/>
-      <c r="B20" s="110" t="s">
+      <c r="A20" s="169"/>
+      <c r="B20" s="107" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -8440,7 +8315,7 @@
       <c r="J20" s="18"/>
       <c r="O20" s="33"/>
       <c r="P20" s="33"/>
-      <c r="R20" s="101" t="s">
+      <c r="R20" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S20" s="60" t="s">
@@ -8451,12 +8326,12 @@
       </c>
       <c r="U20" s="49"/>
       <c r="W20" s="33"/>
-      <c r="X20" s="129"/>
+      <c r="X20" s="126"/>
       <c r="Y20" s="67"/>
     </row>
     <row r="21" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="175"/>
-      <c r="B21" s="104" t="s">
+      <c r="A21" s="169"/>
+      <c r="B21" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -8474,7 +8349,7 @@
       </c>
       <c r="O21" s="33"/>
       <c r="P21" s="33"/>
-      <c r="R21" s="102" t="s">
+      <c r="R21" s="99" t="s">
         <v>53</v>
       </c>
       <c r="S21" s="61" t="s">
@@ -8484,14 +8359,14 @@
         <v>47</v>
       </c>
       <c r="U21" s="51"/>
-      <c r="V21" s="80"/>
+      <c r="V21" s="77"/>
       <c r="W21" s="35"/>
-      <c r="X21" s="127"/>
+      <c r="X21" s="124"/>
       <c r="Y21" s="68"/>
     </row>
     <row r="22" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="175"/>
-      <c r="B22" s="104" t="s">
+      <c r="A22" s="169"/>
+      <c r="B22" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -8506,7 +8381,7 @@
       <c r="I22" s="67"/>
       <c r="O22" s="33"/>
       <c r="P22" s="33"/>
-      <c r="R22" s="98" t="s">
+      <c r="R22" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S22" t="s">
@@ -8517,14 +8392,14 @@
       </c>
       <c r="U22" s="50"/>
       <c r="W22" s="33"/>
-      <c r="X22" s="129"/>
+      <c r="X22" s="126"/>
       <c r="Y22" s="67" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="175"/>
-      <c r="B23" s="104" t="s">
+      <c r="A23" s="169"/>
+      <c r="B23" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -8540,7 +8415,7 @@
       <c r="I23" s="68"/>
       <c r="O23" s="33"/>
       <c r="P23" s="33"/>
-      <c r="R23" s="98" t="s">
+      <c r="R23" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S23" s="14" t="s">
@@ -8551,12 +8426,12 @@
       </c>
       <c r="U23" s="49"/>
       <c r="W23" s="33"/>
-      <c r="X23" s="129"/>
+      <c r="X23" s="126"/>
       <c r="Y23" s="67"/>
     </row>
     <row r="24" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="175"/>
-      <c r="B24" s="104" t="s">
+      <c r="A24" s="169"/>
+      <c r="B24" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -8573,7 +8448,7 @@
       </c>
       <c r="O24" s="33"/>
       <c r="P24" s="33"/>
-      <c r="R24" s="98" t="s">
+      <c r="R24" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S24" s="14" t="s">
@@ -8584,12 +8459,12 @@
       </c>
       <c r="U24" s="49"/>
       <c r="W24" s="33"/>
-      <c r="X24" s="129"/>
+      <c r="X24" s="126"/>
       <c r="Y24" s="67"/>
     </row>
     <row r="25" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="175"/>
-      <c r="B25" s="104" t="s">
+      <c r="A25" s="169"/>
+      <c r="B25" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -8603,7 +8478,7 @@
       <c r="I25" s="67"/>
       <c r="O25" s="33"/>
       <c r="P25" s="33"/>
-      <c r="R25" s="98" t="s">
+      <c r="R25" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S25" s="23" t="s">
@@ -8614,12 +8489,12 @@
       </c>
       <c r="U25" s="49"/>
       <c r="W25" s="33"/>
-      <c r="X25" s="129"/>
+      <c r="X25" s="126"/>
       <c r="Y25" s="67"/>
     </row>
     <row r="26" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="175"/>
-      <c r="B26" s="104" t="s">
+      <c r="A26" s="169"/>
+      <c r="B26" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -8633,7 +8508,7 @@
       <c r="I26" s="67"/>
       <c r="O26" s="33"/>
       <c r="P26" s="33"/>
-      <c r="R26" s="98" t="s">
+      <c r="R26" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S26" s="23" t="s">
@@ -8644,12 +8519,12 @@
       </c>
       <c r="U26" s="49"/>
       <c r="W26" s="33"/>
-      <c r="X26" s="129"/>
+      <c r="X26" s="126"/>
       <c r="Y26" s="67"/>
     </row>
     <row r="27" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="175"/>
-      <c r="B27" s="104" t="s">
+      <c r="A27" s="169"/>
+      <c r="B27" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -8666,26 +8541,26 @@
       <c r="O27" s="33"/>
       <c r="P27" s="33"/>
       <c r="Q27" s="13"/>
-      <c r="R27" s="103" t="s">
-        <v>149</v>
+      <c r="R27" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T27" s="50" t="s">
         <v>47</v>
       </c>
       <c r="U27" s="50"/>
-      <c r="V27" s="79"/>
+      <c r="V27" s="76"/>
       <c r="W27" s="34"/>
-      <c r="X27" s="128"/>
+      <c r="X27" s="125"/>
       <c r="Y27" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="175"/>
-      <c r="B28" s="104" t="s">
+      <c r="A28" s="169"/>
+      <c r="B28" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -8701,8 +8576,8 @@
       <c r="O28" s="33"/>
       <c r="P28" s="33"/>
       <c r="Q28" s="13"/>
-      <c r="R28" s="98" t="s">
-        <v>149</v>
+      <c r="R28" s="95" t="s">
+        <v>146</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>75</v>
@@ -8712,12 +8587,12 @@
       </c>
       <c r="U28" s="49"/>
       <c r="W28" s="33"/>
-      <c r="X28" s="129"/>
+      <c r="X28" s="126"/>
       <c r="Y28" s="67"/>
     </row>
     <row r="29" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="175"/>
-      <c r="B29" s="104" t="s">
+      <c r="A29" s="169"/>
+      <c r="B29" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -8734,8 +8609,8 @@
       <c r="O29" s="33"/>
       <c r="P29" s="33"/>
       <c r="Q29" s="13"/>
-      <c r="R29" s="99" t="s">
-        <v>149</v>
+      <c r="R29" s="96" t="s">
+        <v>146</v>
       </c>
       <c r="S29" s="22" t="s">
         <v>76</v>
@@ -8744,14 +8619,14 @@
         <v>58</v>
       </c>
       <c r="U29" s="51"/>
-      <c r="V29" s="80"/>
+      <c r="V29" s="77"/>
       <c r="W29" s="35"/>
-      <c r="X29" s="127"/>
+      <c r="X29" s="124"/>
       <c r="Y29" s="68"/>
     </row>
     <row r="30" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="175"/>
-      <c r="B30" s="104" t="s">
+      <c r="A30" s="169"/>
+      <c r="B30" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -8768,26 +8643,26 @@
       <c r="O30" s="33"/>
       <c r="P30" s="33"/>
       <c r="Q30" s="13"/>
-      <c r="R30" s="103" t="s">
-        <v>150</v>
+      <c r="R30" s="100" t="s">
+        <v>147</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="T30" s="50" t="s">
         <v>47</v>
       </c>
       <c r="U30" s="49"/>
-      <c r="V30" s="79"/>
+      <c r="V30" s="76"/>
       <c r="W30" s="34"/>
-      <c r="X30" s="128"/>
+      <c r="X30" s="125"/>
       <c r="Y30" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="175"/>
-      <c r="B31" s="104" t="s">
+      <c r="A31" s="169"/>
+      <c r="B31" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -8804,8 +8679,8 @@
       <c r="O31" s="33"/>
       <c r="P31" s="33"/>
       <c r="Q31" s="13"/>
-      <c r="R31" s="98" t="s">
-        <v>150</v>
+      <c r="R31" s="95" t="s">
+        <v>147</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>75</v>
@@ -8815,12 +8690,12 @@
       </c>
       <c r="U31" s="49"/>
       <c r="W31" s="33"/>
-      <c r="X31" s="129"/>
+      <c r="X31" s="126"/>
       <c r="Y31" s="67"/>
     </row>
     <row r="32" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="175"/>
-      <c r="B32" s="104" t="s">
+      <c r="A32" s="169"/>
+      <c r="B32" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -8836,8 +8711,8 @@
       <c r="O32" s="33"/>
       <c r="P32" s="33"/>
       <c r="Q32" s="13"/>
-      <c r="R32" s="99" t="s">
-        <v>150</v>
+      <c r="R32" s="96" t="s">
+        <v>147</v>
       </c>
       <c r="S32" s="22" t="s">
         <v>76</v>
@@ -8846,14 +8721,14 @@
         <v>58</v>
       </c>
       <c r="U32" s="51"/>
-      <c r="V32" s="80"/>
+      <c r="V32" s="77"/>
       <c r="W32" s="35"/>
-      <c r="X32" s="127"/>
+      <c r="X32" s="124"/>
       <c r="Y32" s="68"/>
     </row>
     <row r="33" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="175"/>
-      <c r="B33" s="104" t="s">
+      <c r="A33" s="169"/>
+      <c r="B33" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -8873,8 +8748,8 @@
       <c r="X33" s="33"/>
     </row>
     <row r="34" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="175"/>
-      <c r="B34" s="104" t="s">
+      <c r="A34" s="169"/>
+      <c r="B34" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="21" t="s">
@@ -8895,8 +8770,8 @@
       <c r="X34" s="33"/>
     </row>
     <row r="35" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="175"/>
-      <c r="B35" s="104" t="s">
+      <c r="A35" s="169"/>
+      <c r="B35" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C35" t="s">
@@ -8919,8 +8794,8 @@
       <c r="X35" s="33"/>
     </row>
     <row r="36" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="175"/>
-      <c r="B36" s="104" t="s">
+      <c r="A36" s="169"/>
+      <c r="B36" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C36" s="14" t="s">
@@ -8940,8 +8815,8 @@
       <c r="X36" s="33"/>
     </row>
     <row r="37" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="175"/>
-      <c r="B37" s="104" t="s">
+      <c r="A37" s="169"/>
+      <c r="B37" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="14" t="s">
@@ -8963,8 +8838,8 @@
       <c r="Y37" s="13"/>
     </row>
     <row r="38" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="175"/>
-      <c r="B38" s="104" t="s">
+      <c r="A38" s="169"/>
+      <c r="B38" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C38" s="14" t="s">
@@ -8986,8 +8861,8 @@
       <c r="Y38" s="13"/>
     </row>
     <row r="39" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="175"/>
-      <c r="B39" s="104" t="s">
+      <c r="A39" s="169"/>
+      <c r="B39" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C39" s="14" t="s">
@@ -9009,8 +8884,8 @@
       <c r="Y39" s="13"/>
     </row>
     <row r="40" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="175"/>
-      <c r="B40" s="104" t="s">
+      <c r="A40" s="169"/>
+      <c r="B40" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C40" s="14" t="s">
@@ -9032,8 +8907,8 @@
       <c r="Y40" s="13"/>
     </row>
     <row r="41" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="175"/>
-      <c r="B41" s="104" t="s">
+      <c r="A41" s="169"/>
+      <c r="B41" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C41" s="14" t="s">
@@ -9055,8 +8930,8 @@
       <c r="Y41" s="13"/>
     </row>
     <row r="42" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="175"/>
-      <c r="B42" s="104" t="s">
+      <c r="A42" s="169"/>
+      <c r="B42" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="14" t="s">
@@ -9078,8 +8953,8 @@
       <c r="Y42" s="13"/>
     </row>
     <row r="43" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="175"/>
-      <c r="B43" s="104" t="s">
+      <c r="A43" s="169"/>
+      <c r="B43" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C43" s="14" t="s">
@@ -9102,8 +8977,8 @@
       <c r="Y43" s="13"/>
     </row>
     <row r="44" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="175"/>
-      <c r="B44" s="104" t="s">
+      <c r="A44" s="169"/>
+      <c r="B44" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -9126,8 +9001,8 @@
       <c r="Y44" s="13"/>
     </row>
     <row r="45" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="175"/>
-      <c r="B45" s="104" t="s">
+      <c r="A45" s="169"/>
+      <c r="B45" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -9150,8 +9025,8 @@
       <c r="Y45" s="13"/>
     </row>
     <row r="46" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="175"/>
-      <c r="B46" s="104" t="s">
+      <c r="A46" s="169"/>
+      <c r="B46" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -9174,8 +9049,8 @@
       <c r="Y46" s="13"/>
     </row>
     <row r="47" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="175"/>
-      <c r="B47" s="104" t="s">
+      <c r="A47" s="169"/>
+      <c r="B47" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -9198,8 +9073,8 @@
       <c r="Y47" s="13"/>
     </row>
     <row r="48" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="175"/>
-      <c r="B48" s="104" t="s">
+      <c r="A48" s="169"/>
+      <c r="B48" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -9221,8 +9096,8 @@
       <c r="Y48" s="13"/>
     </row>
     <row r="49" spans="1:25" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="176"/>
-      <c r="B49" s="111" t="s">
+      <c r="A49" s="170"/>
+      <c r="B49" s="108" t="s">
         <v>68</v>
       </c>
       <c r="C49" s="20" t="s">
@@ -9231,10 +9106,10 @@
       <c r="D49" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="81"/>
+      <c r="E49" s="78"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="112"/>
-      <c r="H49" s="112"/>
+      <c r="G49" s="109"/>
+      <c r="H49" s="109"/>
       <c r="I49" s="72"/>
       <c r="J49" s="18"/>
       <c r="O49" s="33"/>
@@ -9243,17 +9118,17 @@
       <c r="R49" s="19"/>
       <c r="S49" s="15"/>
       <c r="T49" s="15"/>
-      <c r="U49" s="81"/>
-      <c r="V49" s="81"/>
-      <c r="W49" s="112"/>
-      <c r="X49" s="112"/>
+      <c r="U49" s="78"/>
+      <c r="V49" s="78"/>
+      <c r="W49" s="109"/>
+      <c r="X49" s="109"/>
       <c r="Y49" s="16"/>
     </row>
     <row r="50" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="174" t="s">
+      <c r="A50" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="106" t="s">
+      <c r="B50" s="103" t="s">
         <v>51</v>
       </c>
       <c r="C50" t="s">
@@ -9267,7 +9142,7 @@
       </c>
       <c r="H50" s="33"/>
       <c r="I50" s="67"/>
-      <c r="J50" s="92" t="s">
+      <c r="J50" s="89" t="s">
         <v>54</v>
       </c>
       <c r="K50" s="12" t="s">
@@ -9276,14 +9151,14 @@
       <c r="L50" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="M50" s="78">
+      <c r="M50" s="75">
         <v>0</v>
       </c>
       <c r="N50" s="12"/>
       <c r="O50" s="12"/>
       <c r="P50" s="32"/>
       <c r="Q50" s="66"/>
-      <c r="R50" s="98" t="s">
+      <c r="R50" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S50" t="s">
@@ -9292,15 +9167,15 @@
       <c r="T50" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="U50" s="76">
+      <c r="U50" s="73">
         <v>0</v>
       </c>
       <c r="X50" s="33"/>
       <c r="Y50" s="67"/>
     </row>
     <row r="51" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="175"/>
-      <c r="B51" s="95" t="s">
+      <c r="A51" s="169"/>
+      <c r="B51" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C51" t="s">
@@ -9311,7 +9186,7 @@
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="67"/>
-      <c r="J51" s="91" t="s">
+      <c r="J51" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K51" t="s">
@@ -9322,7 +9197,7 @@
       </c>
       <c r="P51" s="33"/>
       <c r="Q51" s="67"/>
-      <c r="R51" s="98" t="s">
+      <c r="R51" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S51" t="s">
@@ -9336,8 +9211,8 @@
       <c r="Y51" s="67"/>
     </row>
     <row r="52" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="175"/>
-      <c r="B52" s="95" t="s">
+      <c r="A52" s="169"/>
+      <c r="B52" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C52" t="s">
@@ -9348,7 +9223,7 @@
       </c>
       <c r="H52" s="33"/>
       <c r="I52" s="67"/>
-      <c r="J52" s="91" t="s">
+      <c r="J52" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K52" t="s">
@@ -9359,7 +9234,7 @@
       </c>
       <c r="P52" s="33"/>
       <c r="Q52" s="67"/>
-      <c r="R52" s="98" t="s">
+      <c r="R52" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S52" t="s">
@@ -9373,8 +9248,8 @@
       <c r="Y52" s="67"/>
     </row>
     <row r="53" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="175"/>
-      <c r="B53" s="95" t="s">
+      <c r="A53" s="169"/>
+      <c r="B53" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C53" t="s">
@@ -9385,7 +9260,7 @@
       </c>
       <c r="H53" s="33"/>
       <c r="I53" s="67"/>
-      <c r="J53" s="91" t="s">
+      <c r="J53" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K53" t="s">
@@ -9396,7 +9271,7 @@
       </c>
       <c r="P53" s="33"/>
       <c r="Q53" s="67"/>
-      <c r="R53" s="98" t="s">
+      <c r="R53" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S53" t="s">
@@ -9410,8 +9285,8 @@
       <c r="Y53" s="67"/>
     </row>
     <row r="54" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="175"/>
-      <c r="B54" s="95" t="s">
+      <c r="A54" s="169"/>
+      <c r="B54" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C54" t="s">
@@ -9422,7 +9297,7 @@
       </c>
       <c r="H54" s="33"/>
       <c r="I54" s="67"/>
-      <c r="J54" s="91" t="s">
+      <c r="J54" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K54" t="s">
@@ -9433,7 +9308,7 @@
       </c>
       <c r="P54" s="33"/>
       <c r="Q54" s="67"/>
-      <c r="R54" s="98" t="s">
+      <c r="R54" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S54" t="s">
@@ -9447,8 +9322,8 @@
       <c r="Y54" s="67"/>
     </row>
     <row r="55" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="175"/>
-      <c r="B55" s="95" t="s">
+      <c r="A55" s="169"/>
+      <c r="B55" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C55" t="s">
@@ -9459,7 +9334,7 @@
       </c>
       <c r="H55" s="33"/>
       <c r="I55" s="67"/>
-      <c r="J55" s="91" t="s">
+      <c r="J55" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K55" t="s">
@@ -9470,7 +9345,7 @@
       </c>
       <c r="P55" s="33"/>
       <c r="Q55" s="67"/>
-      <c r="R55" s="98" t="s">
+      <c r="R55" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S55" t="s">
@@ -9484,8 +9359,8 @@
       <c r="Y55" s="67"/>
     </row>
     <row r="56" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="175"/>
-      <c r="B56" s="95" t="s">
+      <c r="A56" s="169"/>
+      <c r="B56" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C56" t="s">
@@ -9496,7 +9371,7 @@
       </c>
       <c r="H56" s="33"/>
       <c r="I56" s="67"/>
-      <c r="J56" s="91" t="s">
+      <c r="J56" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K56" t="s">
@@ -9507,7 +9382,7 @@
       </c>
       <c r="P56" s="33"/>
       <c r="Q56" s="67"/>
-      <c r="R56" s="98" t="s">
+      <c r="R56" s="95" t="s">
         <v>51</v>
       </c>
       <c r="S56" s="58" t="s">
@@ -9521,8 +9396,8 @@
       <c r="Y56" s="67"/>
     </row>
     <row r="57" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="175"/>
-      <c r="B57" s="95" t="s">
+      <c r="A57" s="169"/>
+      <c r="B57" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C57" t="s">
@@ -9533,7 +9408,7 @@
       </c>
       <c r="H57" s="33"/>
       <c r="I57" s="67"/>
-      <c r="J57" s="91" t="s">
+      <c r="J57" s="88" t="s">
         <v>54</v>
       </c>
       <c r="K57" t="s">
@@ -9544,7 +9419,7 @@
       </c>
       <c r="P57" s="33"/>
       <c r="Q57" s="67"/>
-      <c r="R57" s="99" t="s">
+      <c r="R57" s="96" t="s">
         <v>51</v>
       </c>
       <c r="S57" s="58" t="s">
@@ -9554,14 +9429,14 @@
         <v>47</v>
       </c>
       <c r="U57" s="49"/>
-      <c r="V57" s="80"/>
+      <c r="V57" s="77"/>
       <c r="W57" s="1"/>
       <c r="X57" s="35"/>
       <c r="Y57" s="68"/>
     </row>
     <row r="58" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="175"/>
-      <c r="B58" s="95" t="s">
+      <c r="A58" s="169"/>
+      <c r="B58" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C58" t="s">
@@ -9572,7 +9447,7 @@
       </c>
       <c r="H58" s="33"/>
       <c r="I58" s="67"/>
-      <c r="J58" s="93" t="s">
+      <c r="J58" s="90" t="s">
         <v>54</v>
       </c>
       <c r="K58" s="1" t="s">
@@ -9583,7 +9458,7 @@
       </c>
       <c r="P58" s="33"/>
       <c r="Q58" s="67"/>
-      <c r="R58" s="100" t="s">
+      <c r="R58" s="97" t="s">
         <v>52</v>
       </c>
       <c r="S58" s="2" t="s">
@@ -9597,8 +9472,8 @@
       <c r="Y58" s="67"/>
     </row>
     <row r="59" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="175"/>
-      <c r="B59" s="95" t="s">
+      <c r="A59" s="169"/>
+      <c r="B59" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C59" t="s">
@@ -9609,7 +9484,7 @@
       </c>
       <c r="H59" s="33"/>
       <c r="I59" s="67"/>
-      <c r="J59" s="104" t="s">
+      <c r="J59" s="101" t="s">
         <v>92</v>
       </c>
       <c r="K59" s="4" t="s">
@@ -9618,14 +9493,14 @@
       <c r="L59" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="M59" s="83"/>
+      <c r="M59" s="80"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
       <c r="P59" s="36"/>
       <c r="Q59" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="R59" s="101" t="s">
+      <c r="R59" s="98" t="s">
         <v>52</v>
       </c>
       <c r="S59" s="60" t="s">
@@ -9639,19 +9514,19 @@
       <c r="Y59" s="67"/>
     </row>
     <row r="60" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="175"/>
-      <c r="B60" s="95" t="s">
+      <c r="A60" s="169"/>
+      <c r="B60" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D60" s="53" t="s">
         <v>36</v>
       </c>
       <c r="H60" s="33"/>
       <c r="I60" s="67"/>
-      <c r="J60" s="99" t="s">
+      <c r="J60" s="96" t="s">
         <v>93</v>
       </c>
       <c r="K60" s="1" t="s">
@@ -9660,14 +9535,14 @@
       <c r="L60" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="M60" s="80"/>
+      <c r="M60" s="77"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="35"/>
       <c r="Q60" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="R60" s="102" t="s">
+      <c r="R60" s="99" t="s">
         <v>52</v>
       </c>
       <c r="S60" s="61" t="s">
@@ -9681,33 +9556,33 @@
       <c r="Y60" s="67"/>
     </row>
     <row r="61" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="175"/>
-      <c r="B61" s="95" t="s">
+      <c r="A61" s="169"/>
+      <c r="B61" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C61" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D61" s="53" t="s">
         <v>36</v>
       </c>
       <c r="H61" s="33"/>
       <c r="I61" s="67"/>
-      <c r="J61" s="104" t="s">
-        <v>155</v>
+      <c r="J61" s="101" t="s">
+        <v>152</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L61" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="M61" s="83"/>
+        <v>154</v>
+      </c>
+      <c r="M61" s="80"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="135"/>
-      <c r="Q61" s="134"/>
-      <c r="R61" s="101" t="s">
+      <c r="P61" s="132"/>
+      <c r="Q61" s="131"/>
+      <c r="R61" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S61" s="57" t="s">
@@ -9717,28 +9592,28 @@
         <v>47</v>
       </c>
       <c r="U61" s="49"/>
-      <c r="V61" s="79"/>
+      <c r="V61" s="76"/>
       <c r="W61" s="3"/>
       <c r="X61" s="34"/>
       <c r="Y61" s="69"/>
     </row>
     <row r="62" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="175"/>
-      <c r="B62" s="95" t="s">
+      <c r="A62" s="169"/>
+      <c r="B62" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D62" s="53" t="s">
         <v>47</v>
       </c>
       <c r="H62" s="33"/>
       <c r="I62" s="67"/>
-      <c r="J62" s="145"/>
+      <c r="J62" s="142"/>
       <c r="L62" s="6"/>
-      <c r="P62" s="146"/>
-      <c r="R62" s="101" t="s">
+      <c r="P62" s="143"/>
+      <c r="R62" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S62" s="58" t="s">
@@ -9752,22 +9627,22 @@
       <c r="Y62" s="67"/>
     </row>
     <row r="63" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="175"/>
-      <c r="B63" s="95" t="s">
+      <c r="A63" s="169"/>
+      <c r="B63" s="92" t="s">
         <v>51</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D63" s="53" t="s">
         <v>47</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="67"/>
-      <c r="J63" s="145"/>
+      <c r="J63" s="142"/>
       <c r="L63" s="6"/>
-      <c r="P63" s="146"/>
-      <c r="R63" s="101" t="s">
+      <c r="P63" s="143"/>
+      <c r="R63" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S63" s="58" t="s">
@@ -9781,8 +9656,8 @@
       <c r="Y63" s="67"/>
     </row>
     <row r="64" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="175"/>
-      <c r="B64" s="96" t="s">
+      <c r="A64" s="169"/>
+      <c r="B64" s="93" t="s">
         <v>52</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -9797,7 +9672,7 @@
       <c r="H64" s="34"/>
       <c r="I64" s="69"/>
       <c r="P64" s="33"/>
-      <c r="R64" s="101" t="s">
+      <c r="R64" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S64" s="58" t="s">
@@ -9811,8 +9686,8 @@
       <c r="Y64" s="67"/>
     </row>
     <row r="65" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="175"/>
-      <c r="B65" s="96" t="s">
+      <c r="A65" s="169"/>
+      <c r="B65" s="93" t="s">
         <v>52</v>
       </c>
       <c r="C65" t="s">
@@ -9829,7 +9704,7 @@
       <c r="J65" s="18"/>
       <c r="P65" s="33"/>
       <c r="Q65" s="13"/>
-      <c r="R65" s="101" t="s">
+      <c r="R65" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S65" s="58" t="s">
@@ -9843,8 +9718,8 @@
       <c r="Y65" s="67"/>
     </row>
     <row r="66" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="175"/>
-      <c r="B66" s="96" t="s">
+      <c r="A66" s="169"/>
+      <c r="B66" s="93" t="s">
         <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -9858,7 +9733,7 @@
       <c r="J66" s="18"/>
       <c r="P66" s="33"/>
       <c r="Q66" s="13"/>
-      <c r="R66" s="101" t="s">
+      <c r="R66" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S66" s="58" t="s">
@@ -9872,8 +9747,8 @@
       <c r="Y66" s="67"/>
     </row>
     <row r="67" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="175"/>
-      <c r="B67" s="96" t="s">
+      <c r="A67" s="169"/>
+      <c r="B67" s="93" t="s">
         <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -9887,7 +9762,7 @@
       <c r="J67" s="18"/>
       <c r="P67" s="33"/>
       <c r="Q67" s="13"/>
-      <c r="R67" s="101" t="s">
+      <c r="R67" s="98" t="s">
         <v>53</v>
       </c>
       <c r="S67" s="58" t="s">
@@ -9901,8 +9776,8 @@
       <c r="Y67" s="67"/>
     </row>
     <row r="68" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="175"/>
-      <c r="B68" s="95" t="s">
+      <c r="A68" s="169"/>
+      <c r="B68" s="92" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -9921,7 +9796,7 @@
       <c r="J68" s="18"/>
       <c r="P68" s="33"/>
       <c r="Q68" s="13"/>
-      <c r="R68" s="102" t="s">
+      <c r="R68" s="99" t="s">
         <v>53</v>
       </c>
       <c r="S68" s="59" t="s">
@@ -9931,14 +9806,14 @@
         <v>47</v>
       </c>
       <c r="U68" s="49"/>
-      <c r="V68" s="80"/>
+      <c r="V68" s="77"/>
       <c r="W68" s="1"/>
       <c r="X68" s="35"/>
       <c r="Y68" s="68"/>
     </row>
     <row r="69" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="175"/>
-      <c r="B69" s="95" t="s">
+      <c r="A69" s="169"/>
+      <c r="B69" s="92" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -9953,7 +9828,7 @@
       <c r="J69" s="17"/>
       <c r="P69" s="33"/>
       <c r="Q69" s="13"/>
-      <c r="R69" s="98" t="s">
+      <c r="R69" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S69" s="58" t="s">
@@ -9969,8 +9844,8 @@
       </c>
     </row>
     <row r="70" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="175"/>
-      <c r="B70" s="95" t="s">
+      <c r="A70" s="169"/>
+      <c r="B70" s="92" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="21" t="s">
@@ -9987,7 +9862,7 @@
       <c r="J70" s="17"/>
       <c r="P70" s="33"/>
       <c r="Q70" s="13"/>
-      <c r="R70" s="98" t="s">
+      <c r="R70" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S70" s="63" t="s">
@@ -10001,8 +9876,8 @@
       <c r="Y70" s="67"/>
     </row>
     <row r="71" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="175"/>
-      <c r="B71" s="95" t="s">
+      <c r="A71" s="169"/>
+      <c r="B71" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -10020,7 +9895,7 @@
       <c r="J71" s="18"/>
       <c r="P71" s="33"/>
       <c r="Q71" s="13"/>
-      <c r="R71" s="98" t="s">
+      <c r="R71" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S71" s="63" t="s">
@@ -10034,8 +9909,8 @@
       <c r="Y71" s="67"/>
     </row>
     <row r="72" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="175"/>
-      <c r="B72" s="95" t="s">
+      <c r="A72" s="169"/>
+      <c r="B72" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C72" s="8" t="s">
@@ -10049,7 +9924,7 @@
       <c r="J72" s="18"/>
       <c r="P72" s="33"/>
       <c r="Q72" s="13"/>
-      <c r="R72" s="98" t="s">
+      <c r="R72" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S72" s="64" t="s">
@@ -10063,8 +9938,8 @@
       <c r="Y72" s="67"/>
     </row>
     <row r="73" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="175"/>
-      <c r="B73" s="95" t="s">
+      <c r="A73" s="169"/>
+      <c r="B73" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -10078,7 +9953,7 @@
       <c r="J73" s="18"/>
       <c r="P73" s="33"/>
       <c r="Q73" s="13"/>
-      <c r="R73" s="98" t="s">
+      <c r="R73" s="95" t="s">
         <v>74</v>
       </c>
       <c r="S73" s="64" t="s">
@@ -10092,8 +9967,8 @@
       <c r="Y73" s="67"/>
     </row>
     <row r="74" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="175"/>
-      <c r="B74" s="95" t="s">
+      <c r="A74" s="169"/>
+      <c r="B74" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C74" s="8" t="s">
@@ -10108,17 +9983,17 @@
       <c r="L74" s="6"/>
       <c r="P74" s="33"/>
       <c r="Q74" s="13"/>
-      <c r="R74" s="103" t="s">
-        <v>149</v>
+      <c r="R74" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T74" s="50" t="s">
         <v>47</v>
       </c>
       <c r="U74" s="49"/>
-      <c r="V74" s="79"/>
+      <c r="V74" s="76"/>
       <c r="W74" s="3"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="69" t="s">
@@ -10126,8 +10001,8 @@
       </c>
     </row>
     <row r="75" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="175"/>
-      <c r="B75" s="95" t="s">
+      <c r="A75" s="169"/>
+      <c r="B75" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -10141,8 +10016,8 @@
       <c r="J75" s="17"/>
       <c r="P75" s="33"/>
       <c r="Q75" s="13"/>
-      <c r="R75" s="98" t="s">
-        <v>149</v>
+      <c r="R75" s="95" t="s">
+        <v>146</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>75</v>
@@ -10155,8 +10030,8 @@
       <c r="Y75" s="67"/>
     </row>
     <row r="76" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="175"/>
-      <c r="B76" s="95" t="s">
+      <c r="A76" s="169"/>
+      <c r="B76" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -10171,8 +10046,8 @@
       <c r="L76" s="6"/>
       <c r="P76" s="33"/>
       <c r="Q76" s="13"/>
-      <c r="R76" s="99" t="s">
-        <v>149</v>
+      <c r="R76" s="96" t="s">
+        <v>146</v>
       </c>
       <c r="S76" s="22" t="s">
         <v>76</v>
@@ -10181,14 +10056,14 @@
         <v>58</v>
       </c>
       <c r="U76" s="49"/>
-      <c r="V76" s="80"/>
+      <c r="V76" s="77"/>
       <c r="W76" s="1"/>
       <c r="X76" s="35"/>
       <c r="Y76" s="68"/>
     </row>
     <row r="77" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="175"/>
-      <c r="B77" s="95" t="s">
+      <c r="A77" s="169"/>
+      <c r="B77" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -10203,17 +10078,17 @@
       <c r="L77" s="6"/>
       <c r="P77" s="33"/>
       <c r="Q77" s="13"/>
-      <c r="R77" s="103" t="s">
-        <v>150</v>
+      <c r="R77" s="100" t="s">
+        <v>147</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="T77" s="50" t="s">
         <v>47</v>
       </c>
       <c r="U77" s="50"/>
-      <c r="V77" s="79"/>
+      <c r="V77" s="76"/>
       <c r="W77" s="3"/>
       <c r="X77" s="34"/>
       <c r="Y77" s="69" t="s">
@@ -10221,8 +10096,8 @@
       </c>
     </row>
     <row r="78" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="175"/>
-      <c r="B78" s="95" t="s">
+      <c r="A78" s="169"/>
+      <c r="B78" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="8" t="s">
@@ -10237,8 +10112,8 @@
       <c r="L78" s="6"/>
       <c r="P78" s="33"/>
       <c r="Q78" s="13"/>
-      <c r="R78" s="98" t="s">
-        <v>150</v>
+      <c r="R78" s="95" t="s">
+        <v>147</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>75</v>
@@ -10251,8 +10126,8 @@
       <c r="Y78" s="67"/>
     </row>
     <row r="79" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="175"/>
-      <c r="B79" s="95" t="s">
+      <c r="A79" s="169"/>
+      <c r="B79" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="8" t="s">
@@ -10266,8 +10141,8 @@
       <c r="J79" s="17"/>
       <c r="P79" s="33"/>
       <c r="Q79" s="13"/>
-      <c r="R79" s="99" t="s">
-        <v>150</v>
+      <c r="R79" s="96" t="s">
+        <v>147</v>
       </c>
       <c r="S79" s="22" t="s">
         <v>76</v>
@@ -10276,14 +10151,14 @@
         <v>58</v>
       </c>
       <c r="U79" s="51"/>
-      <c r="V79" s="80"/>
+      <c r="V79" s="77"/>
       <c r="W79" s="1"/>
       <c r="X79" s="35"/>
       <c r="Y79" s="68"/>
     </row>
     <row r="80" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="175"/>
-      <c r="B80" s="95" t="s">
+      <c r="A80" s="169"/>
+      <c r="B80" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -10300,8 +10175,8 @@
       <c r="X80" s="33"/>
     </row>
     <row r="81" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="175"/>
-      <c r="B81" s="95" t="s">
+      <c r="A81" s="169"/>
+      <c r="B81" s="92" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="21" t="s">
@@ -10320,8 +10195,8 @@
       <c r="X81" s="33"/>
     </row>
     <row r="82" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="175"/>
-      <c r="B82" s="95" t="s">
+      <c r="A82" s="169"/>
+      <c r="B82" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C82" t="s">
@@ -10341,8 +10216,8 @@
       <c r="X82" s="33"/>
     </row>
     <row r="83" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="175"/>
-      <c r="B83" s="95" t="s">
+      <c r="A83" s="169"/>
+      <c r="B83" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="14" t="s">
@@ -10359,8 +10234,8 @@
       <c r="X83" s="33"/>
     </row>
     <row r="84" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="175"/>
-      <c r="B84" s="95" t="s">
+      <c r="A84" s="169"/>
+      <c r="B84" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C84" s="14" t="s">
@@ -10379,8 +10254,8 @@
       <c r="Y84" s="13"/>
     </row>
     <row r="85" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="175"/>
-      <c r="B85" s="95" t="s">
+      <c r="A85" s="169"/>
+      <c r="B85" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C85" s="14" t="s">
@@ -10399,8 +10274,8 @@
       <c r="Y85" s="13"/>
     </row>
     <row r="86" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="175"/>
-      <c r="B86" s="95" t="s">
+      <c r="A86" s="169"/>
+      <c r="B86" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C86" s="14" t="s">
@@ -10419,8 +10294,8 @@
       <c r="Y86" s="13"/>
     </row>
     <row r="87" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="175"/>
-      <c r="B87" s="95" t="s">
+      <c r="A87" s="169"/>
+      <c r="B87" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C87" s="14" t="s">
@@ -10439,8 +10314,8 @@
       <c r="Y87" s="13"/>
     </row>
     <row r="88" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="175"/>
-      <c r="B88" s="95" t="s">
+      <c r="A88" s="169"/>
+      <c r="B88" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="14" t="s">
@@ -10459,8 +10334,8 @@
       <c r="Y88" s="13"/>
     </row>
     <row r="89" spans="1:25" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="175"/>
-      <c r="B89" s="94" t="s">
+      <c r="A89" s="169"/>
+      <c r="B89" s="91" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -10479,8 +10354,8 @@
       <c r="Y89" s="13"/>
     </row>
     <row r="90" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="175"/>
-      <c r="B90" s="95" t="s">
+      <c r="A90" s="169"/>
+      <c r="B90" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="14" t="s">
@@ -10500,8 +10375,8 @@
       <c r="Y90" s="13"/>
     </row>
     <row r="91" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="175"/>
-      <c r="B91" s="95" t="s">
+      <c r="A91" s="169"/>
+      <c r="B91" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C91" s="14" t="s">
@@ -10521,8 +10396,8 @@
       <c r="Y91" s="13"/>
     </row>
     <row r="92" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="175"/>
-      <c r="B92" s="95" t="s">
+      <c r="A92" s="169"/>
+      <c r="B92" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="14" t="s">
@@ -10542,8 +10417,8 @@
       <c r="Y92" s="13"/>
     </row>
     <row r="93" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="175"/>
-      <c r="B93" s="95" t="s">
+      <c r="A93" s="169"/>
+      <c r="B93" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C93" s="14" t="s">
@@ -10563,8 +10438,8 @@
       <c r="Y93" s="13"/>
     </row>
     <row r="94" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="175"/>
-      <c r="B94" s="95" t="s">
+      <c r="A94" s="169"/>
+      <c r="B94" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C94" s="14" t="s">
@@ -10584,8 +10459,8 @@
       <c r="Y94" s="13"/>
     </row>
     <row r="95" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="175"/>
-      <c r="B95" s="95" t="s">
+      <c r="A95" s="169"/>
+      <c r="B95" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C95" s="14" t="s">
@@ -10604,8 +10479,8 @@
       <c r="Y95" s="13"/>
     </row>
     <row r="96" spans="1:25" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="176"/>
-      <c r="B96" s="95" t="s">
+      <c r="A96" s="170"/>
+      <c r="B96" s="92" t="s">
         <v>68</v>
       </c>
       <c r="C96" s="20" t="s">
@@ -10614,26 +10489,26 @@
       <c r="D96" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="E96" s="81"/>
+      <c r="E96" s="78"/>
       <c r="F96" s="15"/>
       <c r="G96" s="15"/>
-      <c r="H96" s="112"/>
+      <c r="H96" s="109"/>
       <c r="I96" s="72"/>
       <c r="J96" s="19"/>
       <c r="K96" s="15"/>
       <c r="L96" s="15"/>
-      <c r="M96" s="81"/>
+      <c r="M96" s="78"/>
       <c r="N96" s="15"/>
       <c r="O96" s="15"/>
-      <c r="P96" s="112"/>
+      <c r="P96" s="109"/>
       <c r="Q96" s="16"/>
       <c r="R96" s="19"/>
       <c r="S96" s="15"/>
       <c r="T96" s="15"/>
-      <c r="U96" s="81"/>
-      <c r="V96" s="81"/>
+      <c r="U96" s="78"/>
+      <c r="V96" s="78"/>
       <c r="W96" s="15"/>
-      <c r="X96" s="112"/>
+      <c r="X96" s="109"/>
       <c r="Y96" s="16"/>
     </row>
     <row r="97" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10839,52 +10714,52 @@
     <col min="20" max="20" width="16.1796875" customWidth="1"/>
     <col min="21" max="21" width="51.54296875" customWidth="1"/>
     <col min="22" max="22" width="9.1796875" customWidth="1"/>
-    <col min="23" max="23" width="11.81640625" style="114" customWidth="1"/>
+    <col min="23" max="23" width="11.81640625" style="111" customWidth="1"/>
     <col min="24" max="24" width="11.81640625" style="6" customWidth="1"/>
     <col min="25" max="25" width="27.453125" customWidth="1"/>
     <col min="26" max="26" width="22.1796875" customWidth="1"/>
-    <col min="27" max="27" width="18.453125" style="114" customWidth="1"/>
+    <col min="27" max="27" width="18.453125" style="111" customWidth="1"/>
     <col min="28" max="28" width="41.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="5" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="177"/>
-      <c r="B1" s="171" t="s">
+      <c r="A1" s="171"/>
+      <c r="B1" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="171" t="s">
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="173"/>
-      <c r="T1" s="171" t="s">
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="167"/>
+      <c r="T1" s="165" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="172"/>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="172"/>
-      <c r="AB1" s="173"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="166"/>
+      <c r="AA1" s="166"/>
+      <c r="AB1" s="167"/>
     </row>
     <row r="2" spans="1:28" s="5" customFormat="1" ht="56.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="178"/>
+      <c r="A2" s="172"/>
       <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
@@ -10907,7 +10782,7 @@
         <v>125</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>17</v>
@@ -10960,7 +10835,7 @@
         <f t="shared" si="2"/>
         <v>Unité</v>
       </c>
-      <c r="W2" s="155" t="str">
+      <c r="W2" s="152" t="str">
         <f t="shared" si="2"/>
         <v>Quantité</v>
       </c>
@@ -10976,7 +10851,7 @@
         <f t="shared" si="2"/>
         <v>Pourcentage de reconditionnement (%)</v>
       </c>
-      <c r="AA2" s="155" t="str">
+      <c r="AA2" s="152" t="str">
         <f t="shared" si="2"/>
         <v>Durée de vie totale (an)</v>
       </c>
@@ -10986,10 +10861,10 @@
       </c>
     </row>
     <row r="3" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="174" t="s">
+      <c r="A3" s="168" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="104" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -10998,21 +10873,21 @@
       <c r="D3" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="75">
         <v>50</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="F3" s="75" t="s">
         <v>83</v>
       </c>
       <c r="G3" s="32"/>
-      <c r="H3" s="78">
+      <c r="H3" s="75">
         <v>0.2</v>
       </c>
-      <c r="I3" s="78">
+      <c r="I3" s="75">
         <v>10</v>
       </c>
-      <c r="J3" s="150"/>
-      <c r="K3" s="97" t="s">
+      <c r="J3" s="147"/>
+      <c r="K3" s="94" t="s">
         <v>54</v>
       </c>
       <c r="L3" t="s">
@@ -11021,21 +10896,21 @@
       <c r="M3" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="185">
+      <c r="N3" s="158">
         <v>1000</v>
       </c>
-      <c r="O3" s="79" t="s">
+      <c r="O3" s="76" t="s">
         <v>82</v>
       </c>
       <c r="P3" s="34"/>
-      <c r="Q3" s="85">
+      <c r="Q3" s="82">
         <v>0</v>
       </c>
       <c r="R3" s="6">
         <v>6</v>
       </c>
       <c r="S3" s="66"/>
-      <c r="T3" s="97" t="s">
+      <c r="T3" s="94" t="s">
         <v>51</v>
       </c>
       <c r="U3" s="12" t="s">
@@ -11044,24 +10919,24 @@
       <c r="V3" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="W3" s="113">
+      <c r="W3" s="110">
         <v>50</v>
       </c>
-      <c r="X3" s="78" t="s">
+      <c r="X3" s="75" t="s">
         <v>83</v>
       </c>
       <c r="Y3" s="32"/>
-      <c r="Z3" s="88">
+      <c r="Z3" s="85">
         <v>0.2</v>
       </c>
-      <c r="AA3" s="113">
+      <c r="AA3" s="110">
         <v>9</v>
       </c>
       <c r="AB3" s="66"/>
     </row>
     <row r="4" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="175"/>
-      <c r="B4" s="104" t="s">
+      <c r="A4" s="169"/>
+      <c r="B4" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
@@ -11072,7 +10947,7 @@
       </c>
       <c r="G4" s="33"/>
       <c r="J4" s="67"/>
-      <c r="K4" s="98" t="s">
+      <c r="K4" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L4" t="s">
@@ -11081,13 +10956,13 @@
       <c r="M4" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="186"/>
+      <c r="N4" s="159"/>
       <c r="O4" s="6"/>
       <c r="P4" s="33"/>
-      <c r="Q4" s="84"/>
+      <c r="Q4" s="81"/>
       <c r="R4" s="6"/>
       <c r="S4" s="67"/>
-      <c r="T4" s="98" t="s">
+      <c r="T4" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U4" t="s">
@@ -11096,14 +10971,14 @@
       <c r="V4" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W4" s="187"/>
+      <c r="W4" s="149"/>
       <c r="Y4" s="33"/>
-      <c r="Z4" s="84"/>
+      <c r="Z4" s="81"/>
       <c r="AB4" s="67"/>
     </row>
     <row r="5" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="175"/>
-      <c r="B5" s="104" t="s">
+      <c r="A5" s="169"/>
+      <c r="B5" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C5" t="s">
@@ -11114,7 +10989,7 @@
       </c>
       <c r="G5" s="33"/>
       <c r="J5" s="67"/>
-      <c r="K5" s="98" t="s">
+      <c r="K5" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L5" t="s">
@@ -11123,13 +10998,13 @@
       <c r="M5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="186"/>
+      <c r="N5" s="159"/>
       <c r="O5" s="6"/>
       <c r="P5" s="33"/>
-      <c r="Q5" s="84"/>
+      <c r="Q5" s="81"/>
       <c r="R5" s="6"/>
       <c r="S5" s="67"/>
-      <c r="T5" s="98" t="s">
+      <c r="T5" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U5" t="s">
@@ -11138,14 +11013,14 @@
       <c r="V5" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W5" s="187"/>
+      <c r="W5" s="149"/>
       <c r="Y5" s="33"/>
-      <c r="Z5" s="84"/>
+      <c r="Z5" s="81"/>
       <c r="AB5" s="67"/>
     </row>
     <row r="6" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="175"/>
-      <c r="B6" s="104" t="s">
+      <c r="A6" s="169"/>
+      <c r="B6" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C6" t="s">
@@ -11156,7 +11031,7 @@
       </c>
       <c r="G6" s="33"/>
       <c r="J6" s="67"/>
-      <c r="K6" s="98" t="s">
+      <c r="K6" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L6" t="s">
@@ -11165,13 +11040,13 @@
       <c r="M6" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="186"/>
+      <c r="N6" s="159"/>
       <c r="O6" s="6"/>
       <c r="P6" s="33"/>
-      <c r="Q6" s="84"/>
+      <c r="Q6" s="81"/>
       <c r="R6" s="6"/>
       <c r="S6" s="67"/>
-      <c r="T6" s="98" t="s">
+      <c r="T6" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U6" t="s">
@@ -11180,14 +11055,14 @@
       <c r="V6" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W6" s="187"/>
+      <c r="W6" s="149"/>
       <c r="Y6" s="33"/>
-      <c r="Z6" s="84"/>
+      <c r="Z6" s="81"/>
       <c r="AB6" s="67"/>
     </row>
     <row r="7" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="175"/>
-      <c r="B7" s="104" t="s">
+      <c r="A7" s="169"/>
+      <c r="B7" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C7" t="s">
@@ -11198,7 +11073,7 @@
       </c>
       <c r="G7" s="33"/>
       <c r="J7" s="67"/>
-      <c r="K7" s="98" t="s">
+      <c r="K7" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L7" t="s">
@@ -11207,13 +11082,13 @@
       <c r="M7" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="186"/>
+      <c r="N7" s="159"/>
       <c r="O7" s="6"/>
       <c r="P7" s="33"/>
-      <c r="Q7" s="84"/>
+      <c r="Q7" s="81"/>
       <c r="R7" s="6"/>
       <c r="S7" s="67"/>
-      <c r="T7" s="98" t="s">
+      <c r="T7" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U7" t="s">
@@ -11222,14 +11097,14 @@
       <c r="V7" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W7" s="187"/>
+      <c r="W7" s="149"/>
       <c r="Y7" s="33"/>
-      <c r="Z7" s="84"/>
+      <c r="Z7" s="81"/>
       <c r="AB7" s="67"/>
     </row>
     <row r="8" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="175"/>
-      <c r="B8" s="104" t="s">
+      <c r="A8" s="169"/>
+      <c r="B8" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
@@ -11240,7 +11115,7 @@
       </c>
       <c r="G8" s="33"/>
       <c r="J8" s="67"/>
-      <c r="K8" s="98" t="s">
+      <c r="K8" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L8" t="s">
@@ -11249,13 +11124,13 @@
       <c r="M8" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="186"/>
+      <c r="N8" s="159"/>
       <c r="O8" s="6"/>
       <c r="P8" s="33"/>
-      <c r="Q8" s="84"/>
+      <c r="Q8" s="81"/>
       <c r="R8" s="6"/>
       <c r="S8" s="67"/>
-      <c r="T8" s="98" t="s">
+      <c r="T8" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U8" t="s">
@@ -11264,14 +11139,14 @@
       <c r="V8" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W8" s="187"/>
+      <c r="W8" s="149"/>
       <c r="Y8" s="33"/>
-      <c r="Z8" s="84"/>
+      <c r="Z8" s="81"/>
       <c r="AB8" s="67"/>
     </row>
     <row r="9" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="175"/>
-      <c r="B9" s="104" t="s">
+      <c r="A9" s="169"/>
+      <c r="B9" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
@@ -11282,7 +11157,7 @@
       </c>
       <c r="G9" s="33"/>
       <c r="J9" s="67"/>
-      <c r="K9" s="98" t="s">
+      <c r="K9" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L9" t="s">
@@ -11291,13 +11166,13 @@
       <c r="M9" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="186"/>
+      <c r="N9" s="159"/>
       <c r="O9" s="6"/>
       <c r="P9" s="33"/>
-      <c r="Q9" s="84"/>
+      <c r="Q9" s="81"/>
       <c r="R9" s="6"/>
       <c r="S9" s="67"/>
-      <c r="T9" s="98" t="s">
+      <c r="T9" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U9" t="s">
@@ -11306,14 +11181,14 @@
       <c r="V9" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W9" s="187"/>
+      <c r="W9" s="149"/>
       <c r="Y9" s="33"/>
-      <c r="Z9" s="84"/>
+      <c r="Z9" s="81"/>
       <c r="AB9" s="67"/>
     </row>
     <row r="10" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="175"/>
-      <c r="B10" s="104" t="s">
+      <c r="A10" s="169"/>
+      <c r="B10" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C10" t="s">
@@ -11324,7 +11199,7 @@
       </c>
       <c r="G10" s="33"/>
       <c r="J10" s="67"/>
-      <c r="K10" s="98" t="s">
+      <c r="K10" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L10" t="s">
@@ -11333,13 +11208,13 @@
       <c r="M10" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N10" s="186"/>
+      <c r="N10" s="159"/>
       <c r="O10" s="6"/>
       <c r="P10" s="33"/>
-      <c r="Q10" s="84"/>
+      <c r="Q10" s="81"/>
       <c r="R10" s="6"/>
       <c r="S10" s="67"/>
-      <c r="T10" s="99" t="s">
+      <c r="T10" s="96" t="s">
         <v>51</v>
       </c>
       <c r="U10" s="1" t="s">
@@ -11348,16 +11223,16 @@
       <c r="V10" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="W10" s="187"/>
-      <c r="X10" s="80"/>
+      <c r="W10" s="149"/>
+      <c r="X10" s="77"/>
       <c r="Y10" s="35"/>
-      <c r="Z10" s="87"/>
-      <c r="AA10" s="116"/>
+      <c r="Z10" s="84"/>
+      <c r="AA10" s="113"/>
       <c r="AB10" s="68"/>
     </row>
     <row r="11" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="175"/>
-      <c r="B11" s="104" t="s">
+      <c r="A11" s="169"/>
+      <c r="B11" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C11" t="s">
@@ -11366,10 +11241,10 @@
       <c r="D11" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="139"/>
+      <c r="E11" s="136"/>
       <c r="G11" s="33"/>
       <c r="J11" s="67"/>
-      <c r="K11" s="98" t="s">
+      <c r="K11" s="95" t="s">
         <v>54</v>
       </c>
       <c r="L11" t="s">
@@ -11378,13 +11253,13 @@
       <c r="M11" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="N11" s="180"/>
+      <c r="N11" s="136"/>
       <c r="O11" s="6"/>
       <c r="P11" s="33"/>
-      <c r="Q11" s="84"/>
+      <c r="Q11" s="81"/>
       <c r="R11" s="6"/>
       <c r="S11" s="67"/>
-      <c r="T11" s="100" t="s">
+      <c r="T11" s="97" t="s">
         <v>52</v>
       </c>
       <c r="U11" s="2" t="s">
@@ -11393,16 +11268,16 @@
       <c r="V11" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W11" s="188"/>
-      <c r="X11" s="79"/>
+      <c r="W11" s="150"/>
+      <c r="X11" s="76"/>
       <c r="Y11" s="34"/>
-      <c r="Z11" s="85"/>
-      <c r="AA11" s="115"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="112"/>
       <c r="AB11" s="69"/>
     </row>
     <row r="12" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="175"/>
-      <c r="B12" s="104" t="s">
+      <c r="A12" s="169"/>
+      <c r="B12" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
@@ -11411,10 +11286,10 @@
       <c r="D12" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="180"/>
+      <c r="E12" s="136"/>
       <c r="G12" s="33"/>
       <c r="J12" s="67"/>
-      <c r="K12" s="104" t="s">
+      <c r="K12" s="101" t="s">
         <v>92</v>
       </c>
       <c r="L12" s="48" t="s">
@@ -11423,15 +11298,15 @@
       <c r="M12" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="161"/>
-      <c r="O12" s="83"/>
+      <c r="N12" s="154"/>
+      <c r="O12" s="80"/>
       <c r="P12" s="36"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="83"/>
+      <c r="Q12" s="119"/>
+      <c r="R12" s="80"/>
       <c r="S12" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="T12" s="101" t="s">
+      <c r="T12" s="98" t="s">
         <v>52</v>
       </c>
       <c r="U12" s="60" t="s">
@@ -11440,26 +11315,26 @@
       <c r="V12" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W12" s="187"/>
+      <c r="W12" s="149"/>
       <c r="Y12" s="33"/>
-      <c r="Z12" s="84"/>
+      <c r="Z12" s="81"/>
       <c r="AB12" s="67"/>
     </row>
     <row r="13" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="175"/>
-      <c r="B13" s="104" t="s">
+      <c r="A13" s="169"/>
+      <c r="B13" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D13" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="180"/>
+      <c r="E13" s="136"/>
       <c r="G13" s="33"/>
       <c r="J13" s="67"/>
-      <c r="K13" s="99" t="s">
+      <c r="K13" s="96" t="s">
         <v>93</v>
       </c>
       <c r="L13" s="1" t="s">
@@ -11468,15 +11343,15 @@
       <c r="M13" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="N13" s="160"/>
-      <c r="O13" s="80"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="77"/>
       <c r="P13" s="35"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="80"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="77"/>
       <c r="S13" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="T13" s="102" t="s">
+      <c r="T13" s="99" t="s">
         <v>52</v>
       </c>
       <c r="U13" s="61" t="s">
@@ -11485,43 +11360,43 @@
       <c r="V13" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="W13" s="183"/>
-      <c r="X13" s="80"/>
+      <c r="W13" s="151"/>
+      <c r="X13" s="77"/>
       <c r="Y13" s="35"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="116"/>
+      <c r="Z13" s="84"/>
+      <c r="AA13" s="113"/>
       <c r="AB13" s="68"/>
     </row>
     <row r="14" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="175"/>
-      <c r="B14" s="104" t="s">
+      <c r="A14" s="169"/>
+      <c r="B14" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D14" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="162"/>
+      <c r="E14" s="155"/>
       <c r="G14" s="33"/>
       <c r="J14" s="67"/>
-      <c r="K14" s="104" t="s">
-        <v>155</v>
+      <c r="K14" s="101" t="s">
+        <v>152</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M14" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="N14" s="164"/>
+        <v>154</v>
+      </c>
+      <c r="N14" s="157"/>
       <c r="O14" s="4"/>
       <c r="P14" s="36"/>
-      <c r="Q14" s="122"/>
-      <c r="R14" s="133"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="101" t="s">
+      <c r="Q14" s="119"/>
+      <c r="R14" s="130"/>
+      <c r="S14" s="131"/>
+      <c r="T14" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U14" s="60" t="s">
@@ -11530,31 +11405,30 @@
       <c r="V14" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W14" s="187"/>
+      <c r="W14" s="149"/>
       <c r="Y14" s="33"/>
-      <c r="Z14" s="84"/>
+      <c r="Z14" s="81"/>
       <c r="AB14" s="67"/>
     </row>
     <row r="15" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="175"/>
-      <c r="B15" s="104" t="s">
+      <c r="A15" s="169"/>
+      <c r="B15" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="181"/>
       <c r="G15" s="33"/>
       <c r="J15" s="67"/>
-      <c r="K15" s="145"/>
+      <c r="K15" s="142"/>
       <c r="M15" s="6"/>
       <c r="P15" s="33"/>
-      <c r="Q15" s="84"/>
+      <c r="Q15" s="81"/>
       <c r="R15" s="6"/>
-      <c r="T15" s="101" t="s">
+      <c r="T15" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U15" s="60" t="s">
@@ -11563,29 +11437,28 @@
       <c r="V15" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W15" s="187"/>
+      <c r="W15" s="149"/>
       <c r="Y15" s="33"/>
-      <c r="Z15" s="84"/>
+      <c r="Z15" s="81"/>
       <c r="AB15" s="67"/>
     </row>
     <row r="16" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="175"/>
-      <c r="B16" s="104" t="s">
+      <c r="A16" s="169"/>
+      <c r="B16" s="101" t="s">
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D16" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="181"/>
       <c r="G16" s="33"/>
       <c r="J16" s="67"/>
-      <c r="K16" s="145"/>
+      <c r="K16" s="142"/>
       <c r="M16" s="6"/>
       <c r="P16" s="33"/>
-      <c r="T16" s="101" t="s">
+      <c r="T16" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U16" s="60" t="s">
@@ -11594,14 +11467,14 @@
       <c r="V16" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W16" s="187"/>
+      <c r="W16" s="149"/>
       <c r="Y16" s="33"/>
-      <c r="Z16" s="84"/>
+      <c r="Z16" s="81"/>
       <c r="AB16" s="67"/>
     </row>
     <row r="17" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="175"/>
-      <c r="B17" s="110" t="s">
+      <c r="A17" s="169"/>
+      <c r="B17" s="107" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -11610,14 +11483,14 @@
       <c r="D17" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="182"/>
-      <c r="F17" s="79"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="76"/>
       <c r="G17" s="34"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
       <c r="J17" s="69"/>
       <c r="P17" s="33"/>
-      <c r="T17" s="101" t="s">
+      <c r="T17" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U17" s="60" t="s">
@@ -11626,14 +11499,14 @@
       <c r="V17" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W17" s="187"/>
+      <c r="W17" s="149"/>
       <c r="Y17" s="33"/>
-      <c r="Z17" s="84"/>
+      <c r="Z17" s="81"/>
       <c r="AB17" s="67"/>
     </row>
     <row r="18" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="175"/>
-      <c r="B18" s="110" t="s">
+      <c r="A18" s="169"/>
+      <c r="B18" s="107" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
@@ -11642,13 +11515,13 @@
       <c r="D18" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="183"/>
+      <c r="E18" s="151"/>
       <c r="G18" s="33"/>
       <c r="J18" s="67"/>
       <c r="K18" s="17"/>
       <c r="P18" s="33"/>
       <c r="S18" s="13"/>
-      <c r="T18" s="101" t="s">
+      <c r="T18" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U18" s="60" t="s">
@@ -11657,14 +11530,14 @@
       <c r="V18" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W18" s="187"/>
+      <c r="W18" s="149"/>
       <c r="Y18" s="33"/>
-      <c r="Z18" s="84"/>
+      <c r="Z18" s="81"/>
       <c r="AB18" s="67"/>
     </row>
     <row r="19" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="175"/>
-      <c r="B19" s="110" t="s">
+      <c r="A19" s="169"/>
+      <c r="B19" s="107" t="s">
         <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -11673,16 +11546,16 @@
       <c r="D19" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="184"/>
-      <c r="F19" s="79"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="76"/>
       <c r="G19" s="34"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76"/>
       <c r="J19" s="69"/>
       <c r="K19" s="17"/>
       <c r="P19" s="33"/>
       <c r="S19" s="13"/>
-      <c r="T19" s="101" t="s">
+      <c r="T19" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U19" s="60" t="s">
@@ -11691,14 +11564,14 @@
       <c r="V19" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W19" s="187"/>
+      <c r="W19" s="149"/>
       <c r="Y19" s="33"/>
-      <c r="Z19" s="84"/>
+      <c r="Z19" s="81"/>
       <c r="AB19" s="67"/>
     </row>
     <row r="20" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="175"/>
-      <c r="B20" s="110" t="s">
+      <c r="A20" s="169"/>
+      <c r="B20" s="107" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -11707,15 +11580,14 @@
       <c r="D20" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="181"/>
-      <c r="F20" s="80"/>
+      <c r="F20" s="77"/>
       <c r="G20" s="35"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
       <c r="J20" s="68"/>
       <c r="K20" s="18"/>
       <c r="P20" s="33"/>
-      <c r="T20" s="101" t="s">
+      <c r="T20" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U20" s="60" t="s">
@@ -11724,14 +11596,14 @@
       <c r="V20" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W20" s="187"/>
+      <c r="W20" s="149"/>
       <c r="Y20" s="33"/>
-      <c r="Z20" s="84"/>
+      <c r="Z20" s="81"/>
       <c r="AB20" s="67"/>
     </row>
     <row r="21" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="175"/>
-      <c r="B21" s="104" t="s">
+      <c r="A21" s="169"/>
+      <c r="B21" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -11741,16 +11613,16 @@
         <v>47</v>
       </c>
       <c r="E21" s="50"/>
-      <c r="F21" s="79"/>
+      <c r="F21" s="76"/>
       <c r="G21" s="34"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
       <c r="J21" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="L21" s="136"/>
+      <c r="L21" s="133"/>
       <c r="P21" s="33"/>
-      <c r="T21" s="102" t="s">
+      <c r="T21" s="99" t="s">
         <v>53</v>
       </c>
       <c r="U21" s="61" t="s">
@@ -11759,16 +11631,16 @@
       <c r="V21" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="W21" s="187"/>
-      <c r="X21" s="80"/>
+      <c r="W21" s="149"/>
+      <c r="X21" s="77"/>
       <c r="Y21" s="35"/>
-      <c r="Z21" s="87"/>
-      <c r="AA21" s="116"/>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="113"/>
       <c r="AB21" s="68"/>
     </row>
     <row r="22" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="175"/>
-      <c r="B22" s="104" t="s">
+      <c r="A22" s="169"/>
+      <c r="B22" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -11781,7 +11653,7 @@
       <c r="G22" s="33"/>
       <c r="J22" s="67"/>
       <c r="P22" s="33"/>
-      <c r="T22" s="98" t="s">
+      <c r="T22" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U22" t="s">
@@ -11790,16 +11662,16 @@
       <c r="V22" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W22" s="188"/>
+      <c r="W22" s="150"/>
       <c r="Y22" s="33"/>
-      <c r="Z22" s="84"/>
+      <c r="Z22" s="81"/>
       <c r="AB22" s="67" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="175"/>
-      <c r="B23" s="104" t="s">
+      <c r="A23" s="169"/>
+      <c r="B23" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -11809,13 +11681,13 @@
         <v>58</v>
       </c>
       <c r="E23" s="51"/>
-      <c r="F23" s="80"/>
+      <c r="F23" s="77"/>
       <c r="G23" s="35"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
       <c r="J23" s="68"/>
       <c r="P23" s="33"/>
-      <c r="T23" s="98" t="s">
+      <c r="T23" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U23" s="14" t="s">
@@ -11824,14 +11696,14 @@
       <c r="V23" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W23" s="187"/>
+      <c r="W23" s="149"/>
       <c r="Y23" s="33"/>
-      <c r="Z23" s="84"/>
+      <c r="Z23" s="81"/>
       <c r="AB23" s="67"/>
     </row>
     <row r="24" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="175"/>
-      <c r="B24" s="104" t="s">
+      <c r="A24" s="169"/>
+      <c r="B24" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -11840,15 +11712,15 @@
       <c r="D24" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="79"/>
+      <c r="F24" s="76"/>
       <c r="G24" s="34"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
       <c r="J24" s="71" t="s">
         <v>106</v>
       </c>
       <c r="P24" s="33"/>
-      <c r="T24" s="98" t="s">
+      <c r="T24" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U24" s="14" t="s">
@@ -11857,14 +11729,14 @@
       <c r="V24" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="W24" s="152"/>
+      <c r="W24" s="149"/>
       <c r="Y24" s="33"/>
-      <c r="Z24" s="84"/>
+      <c r="Z24" s="81"/>
       <c r="AB24" s="67"/>
     </row>
     <row r="25" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="175"/>
-      <c r="B25" s="104" t="s">
+      <c r="A25" s="169"/>
+      <c r="B25" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -11876,7 +11748,7 @@
       <c r="G25" s="33"/>
       <c r="J25" s="67"/>
       <c r="P25" s="33"/>
-      <c r="T25" s="98" t="s">
+      <c r="T25" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U25" s="23" t="s">
@@ -11885,14 +11757,14 @@
       <c r="V25" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W25" s="152"/>
+      <c r="W25" s="149"/>
       <c r="Y25" s="33"/>
-      <c r="Z25" s="84"/>
+      <c r="Z25" s="81"/>
       <c r="AB25" s="67"/>
     </row>
     <row r="26" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="175"/>
-      <c r="B26" s="104" t="s">
+      <c r="A26" s="169"/>
+      <c r="B26" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -11904,7 +11776,7 @@
       <c r="G26" s="33"/>
       <c r="J26" s="67"/>
       <c r="P26" s="33"/>
-      <c r="T26" s="98" t="s">
+      <c r="T26" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U26" s="23" t="s">
@@ -11913,14 +11785,14 @@
       <c r="V26" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W26" s="154"/>
+      <c r="W26" s="151"/>
       <c r="Y26" s="33"/>
-      <c r="Z26" s="84"/>
+      <c r="Z26" s="81"/>
       <c r="AB26" s="67"/>
     </row>
     <row r="27" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="175"/>
-      <c r="B27" s="104" t="s">
+      <c r="A27" s="169"/>
+      <c r="B27" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -11935,27 +11807,27 @@
       <c r="M27" s="6"/>
       <c r="P27" s="33"/>
       <c r="S27" s="13"/>
-      <c r="T27" s="103" t="s">
-        <v>149</v>
+      <c r="T27" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="V27" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W27" s="152"/>
-      <c r="X27" s="79"/>
+      <c r="W27" s="149"/>
+      <c r="X27" s="76"/>
       <c r="Y27" s="34"/>
-      <c r="Z27" s="85"/>
-      <c r="AA27" s="115"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="112"/>
       <c r="AB27" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="175"/>
-      <c r="B28" s="104" t="s">
+      <c r="A28" s="169"/>
+      <c r="B28" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -11969,8 +11841,8 @@
       <c r="K28" s="17"/>
       <c r="P28" s="33"/>
       <c r="S28" s="13"/>
-      <c r="T28" s="98" t="s">
-        <v>149</v>
+      <c r="T28" s="95" t="s">
+        <v>146</v>
       </c>
       <c r="U28" s="14" t="s">
         <v>75</v>
@@ -11978,14 +11850,14 @@
       <c r="V28" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W28" s="152"/>
+      <c r="W28" s="149"/>
       <c r="Y28" s="33"/>
-      <c r="Z28" s="84"/>
+      <c r="Z28" s="81"/>
       <c r="AB28" s="67"/>
     </row>
     <row r="29" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="175"/>
-      <c r="B29" s="104" t="s">
+      <c r="A29" s="169"/>
+      <c r="B29" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -12000,8 +11872,8 @@
       <c r="M29" s="6"/>
       <c r="P29" s="33"/>
       <c r="S29" s="13"/>
-      <c r="T29" s="99" t="s">
-        <v>149</v>
+      <c r="T29" s="96" t="s">
+        <v>146</v>
       </c>
       <c r="U29" s="22" t="s">
         <v>76</v>
@@ -12009,16 +11881,16 @@
       <c r="V29" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="W29" s="152"/>
-      <c r="X29" s="80"/>
+      <c r="W29" s="149"/>
+      <c r="X29" s="77"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="87"/>
-      <c r="AA29" s="116"/>
+      <c r="Z29" s="84"/>
+      <c r="AA29" s="113"/>
       <c r="AB29" s="68"/>
     </row>
     <row r="30" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="175"/>
-      <c r="B30" s="104" t="s">
+      <c r="A30" s="169"/>
+      <c r="B30" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -12033,27 +11905,27 @@
       <c r="M30" s="6"/>
       <c r="P30" s="33"/>
       <c r="S30" s="13"/>
-      <c r="T30" s="103" t="s">
-        <v>150</v>
+      <c r="T30" s="100" t="s">
+        <v>147</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="V30" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W30" s="153"/>
-      <c r="X30" s="79"/>
+      <c r="W30" s="150"/>
+      <c r="X30" s="76"/>
       <c r="Y30" s="34"/>
-      <c r="Z30" s="85"/>
-      <c r="AA30" s="115"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="112"/>
       <c r="AB30" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="175"/>
-      <c r="B31" s="104" t="s">
+      <c r="A31" s="169"/>
+      <c r="B31" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -12068,8 +11940,8 @@
       <c r="M31" s="6"/>
       <c r="P31" s="33"/>
       <c r="S31" s="13"/>
-      <c r="T31" s="98" t="s">
-        <v>150</v>
+      <c r="T31" s="95" t="s">
+        <v>147</v>
       </c>
       <c r="U31" s="14" t="s">
         <v>75</v>
@@ -12077,14 +11949,14 @@
       <c r="V31" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W31" s="152"/>
+      <c r="W31" s="149"/>
       <c r="Y31" s="33"/>
-      <c r="Z31" s="84"/>
+      <c r="Z31" s="81"/>
       <c r="AB31" s="67"/>
     </row>
     <row r="32" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="175"/>
-      <c r="B32" s="104" t="s">
+      <c r="A32" s="169"/>
+      <c r="B32" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -12098,8 +11970,8 @@
       <c r="K32" s="17"/>
       <c r="P32" s="33"/>
       <c r="S32" s="13"/>
-      <c r="T32" s="99" t="s">
-        <v>150</v>
+      <c r="T32" s="96" t="s">
+        <v>147</v>
       </c>
       <c r="U32" s="22" t="s">
         <v>76</v>
@@ -12107,16 +11979,16 @@
       <c r="V32" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="W32" s="154"/>
-      <c r="X32" s="80"/>
+      <c r="W32" s="151"/>
+      <c r="X32" s="77"/>
       <c r="Y32" s="35"/>
-      <c r="Z32" s="87"/>
-      <c r="AA32" s="116"/>
+      <c r="Z32" s="84"/>
+      <c r="AA32" s="113"/>
       <c r="AB32" s="68"/>
     </row>
     <row r="33" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="175"/>
-      <c r="B33" s="104" t="s">
+      <c r="A33" s="169"/>
+      <c r="B33" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -12133,8 +12005,8 @@
       <c r="Y33" s="33"/>
     </row>
     <row r="34" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="175"/>
-      <c r="B34" s="104" t="s">
+      <c r="A34" s="169"/>
+      <c r="B34" s="101" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="21" t="s">
@@ -12143,10 +12015,10 @@
       <c r="D34" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="80"/>
+      <c r="F34" s="77"/>
       <c r="G34" s="35"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
       <c r="J34" s="68"/>
       <c r="K34" s="18"/>
       <c r="P34" s="33"/>
@@ -12154,8 +12026,8 @@
       <c r="Y34" s="33"/>
     </row>
     <row r="35" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="175"/>
-      <c r="B35" s="104" t="s">
+      <c r="A35" s="169"/>
+      <c r="B35" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C35" t="s">
@@ -12175,8 +12047,8 @@
       <c r="Y35" s="33"/>
     </row>
     <row r="36" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="175"/>
-      <c r="B36" s="104" t="s">
+      <c r="A36" s="169"/>
+      <c r="B36" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C36" s="14" t="s">
@@ -12193,8 +12065,8 @@
       <c r="Y36" s="33"/>
     </row>
     <row r="37" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="175"/>
-      <c r="B37" s="104" t="s">
+      <c r="A37" s="169"/>
+      <c r="B37" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="14" t="s">
@@ -12213,8 +12085,8 @@
       <c r="AB37" s="13"/>
     </row>
     <row r="38" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="175"/>
-      <c r="B38" s="104" t="s">
+      <c r="A38" s="169"/>
+      <c r="B38" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C38" s="14" t="s">
@@ -12233,8 +12105,8 @@
       <c r="AB38" s="13"/>
     </row>
     <row r="39" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="175"/>
-      <c r="B39" s="104" t="s">
+      <c r="A39" s="169"/>
+      <c r="B39" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C39" s="14" t="s">
@@ -12253,8 +12125,8 @@
       <c r="AB39" s="13"/>
     </row>
     <row r="40" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="175"/>
-      <c r="B40" s="104" t="s">
+      <c r="A40" s="169"/>
+      <c r="B40" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C40" s="14" t="s">
@@ -12273,8 +12145,8 @@
       <c r="AB40" s="13"/>
     </row>
     <row r="41" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="175"/>
-      <c r="B41" s="104" t="s">
+      <c r="A41" s="169"/>
+      <c r="B41" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C41" s="14" t="s">
@@ -12293,8 +12165,8 @@
       <c r="AB41" s="13"/>
     </row>
     <row r="42" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="175"/>
-      <c r="B42" s="104" t="s">
+      <c r="A42" s="169"/>
+      <c r="B42" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="14" t="s">
@@ -12313,8 +12185,8 @@
       <c r="AB42" s="13"/>
     </row>
     <row r="43" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="175"/>
-      <c r="B43" s="104" t="s">
+      <c r="A43" s="169"/>
+      <c r="B43" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C43" s="14" t="s">
@@ -12334,8 +12206,8 @@
       <c r="AB43" s="13"/>
     </row>
     <row r="44" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="175"/>
-      <c r="B44" s="104" t="s">
+      <c r="A44" s="169"/>
+      <c r="B44" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -12355,8 +12227,8 @@
       <c r="AB44" s="13"/>
     </row>
     <row r="45" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="175"/>
-      <c r="B45" s="104" t="s">
+      <c r="A45" s="169"/>
+      <c r="B45" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -12376,8 +12248,8 @@
       <c r="AB45" s="13"/>
     </row>
     <row r="46" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="175"/>
-      <c r="B46" s="104" t="s">
+      <c r="A46" s="169"/>
+      <c r="B46" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -12397,8 +12269,8 @@
       <c r="AB46" s="13"/>
     </row>
     <row r="47" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="175"/>
-      <c r="B47" s="104" t="s">
+      <c r="A47" s="169"/>
+      <c r="B47" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -12418,8 +12290,8 @@
       <c r="AB47" s="13"/>
     </row>
     <row r="48" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="175"/>
-      <c r="B48" s="104" t="s">
+      <c r="A48" s="169"/>
+      <c r="B48" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -12438,8 +12310,8 @@
       <c r="AB48" s="13"/>
     </row>
     <row r="49" spans="1:28" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="176"/>
-      <c r="B49" s="111" t="s">
+      <c r="A49" s="170"/>
+      <c r="B49" s="108" t="s">
         <v>68</v>
       </c>
       <c r="C49" s="20" t="s">
@@ -12448,11 +12320,11 @@
       <c r="D49" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="112"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="109"/>
+      <c r="H49" s="78"/>
+      <c r="I49" s="78"/>
       <c r="J49" s="72"/>
       <c r="K49" s="18"/>
       <c r="P49" s="33"/>
@@ -12462,10 +12334,10 @@
       <c r="AB49" s="13"/>
     </row>
     <row r="50" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="174" t="s">
+      <c r="A50" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="118" t="s">
+      <c r="B50" s="115" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="12" t="s">
@@ -12474,23 +12346,23 @@
       <c r="D50" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="E50" s="78">
+      <c r="E50" s="75">
         <v>100</v>
       </c>
-      <c r="F50" s="78" t="s">
+      <c r="F50" s="75" t="s">
         <v>83</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H50" s="78">
+        <v>157</v>
+      </c>
+      <c r="H50" s="75">
         <v>0</v>
       </c>
-      <c r="I50" s="78">
+      <c r="I50" s="75">
         <v>5</v>
       </c>
       <c r="J50" s="66"/>
-      <c r="K50" s="92" t="s">
+      <c r="K50" s="89" t="s">
         <v>54</v>
       </c>
       <c r="L50" s="12" t="s">
@@ -12499,23 +12371,23 @@
       <c r="M50" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="N50" s="78">
+      <c r="N50" s="75">
         <v>100</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>84</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q50" s="88">
+        <v>157</v>
+      </c>
+      <c r="Q50" s="85">
         <v>0.2</v>
       </c>
-      <c r="R50" s="88">
+      <c r="R50" s="85">
         <v>6</v>
       </c>
       <c r="S50" s="66"/>
-      <c r="T50" s="97" t="s">
+      <c r="T50" s="94" t="s">
         <v>51</v>
       </c>
       <c r="U50" s="12" t="s">
@@ -12524,26 +12396,26 @@
       <c r="V50" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="W50" s="113">
+      <c r="W50" s="110">
         <v>200</v>
       </c>
-      <c r="X50" s="78" t="s">
+      <c r="X50" s="75" t="s">
         <v>83</v>
       </c>
       <c r="Y50" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z50" s="78">
+        <v>157</v>
+      </c>
+      <c r="Z50" s="75">
         <v>0.1</v>
       </c>
-      <c r="AA50" s="113">
+      <c r="AA50" s="110">
         <v>2</v>
       </c>
       <c r="AB50" s="66"/>
     </row>
     <row r="51" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="175"/>
-      <c r="B51" s="119" t="s">
+      <c r="A51" s="169"/>
+      <c r="B51" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C51" t="s">
@@ -12553,7 +12425,7 @@
         <v>47</v>
       </c>
       <c r="J51" s="67"/>
-      <c r="K51" s="91" t="s">
+      <c r="K51" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L51" t="s">
@@ -12562,10 +12434,10 @@
       <c r="M51" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q51" s="84"/>
-      <c r="R51" s="84"/>
+      <c r="Q51" s="81"/>
+      <c r="R51" s="81"/>
       <c r="S51" s="67"/>
-      <c r="T51" s="98" t="s">
+      <c r="T51" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U51" t="s">
@@ -12578,8 +12450,8 @@
       <c r="AB51" s="67"/>
     </row>
     <row r="52" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="175"/>
-      <c r="B52" s="119" t="s">
+      <c r="A52" s="169"/>
+      <c r="B52" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C52" t="s">
@@ -12589,7 +12461,7 @@
         <v>47</v>
       </c>
       <c r="J52" s="67"/>
-      <c r="K52" s="91" t="s">
+      <c r="K52" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L52" t="s">
@@ -12598,10 +12470,10 @@
       <c r="M52" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q52" s="84"/>
-      <c r="R52" s="84"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="81"/>
       <c r="S52" s="67"/>
-      <c r="T52" s="98" t="s">
+      <c r="T52" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U52" t="s">
@@ -12614,8 +12486,8 @@
       <c r="AB52" s="67"/>
     </row>
     <row r="53" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="175"/>
-      <c r="B53" s="119" t="s">
+      <c r="A53" s="169"/>
+      <c r="B53" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C53" t="s">
@@ -12625,7 +12497,7 @@
         <v>47</v>
       </c>
       <c r="J53" s="67"/>
-      <c r="K53" s="91" t="s">
+      <c r="K53" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L53" t="s">
@@ -12634,10 +12506,10 @@
       <c r="M53" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q53" s="84"/>
-      <c r="R53" s="84"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="81"/>
       <c r="S53" s="67"/>
-      <c r="T53" s="98" t="s">
+      <c r="T53" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U53" t="s">
@@ -12650,8 +12522,8 @@
       <c r="AB53" s="67"/>
     </row>
     <row r="54" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="175"/>
-      <c r="B54" s="119" t="s">
+      <c r="A54" s="169"/>
+      <c r="B54" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C54" t="s">
@@ -12661,7 +12533,7 @@
         <v>47</v>
       </c>
       <c r="J54" s="67"/>
-      <c r="K54" s="91" t="s">
+      <c r="K54" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L54" t="s">
@@ -12670,10 +12542,10 @@
       <c r="M54" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q54" s="84"/>
-      <c r="R54" s="84"/>
+      <c r="Q54" s="81"/>
+      <c r="R54" s="81"/>
       <c r="S54" s="67"/>
-      <c r="T54" s="98" t="s">
+      <c r="T54" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U54" t="s">
@@ -12686,8 +12558,8 @@
       <c r="AB54" s="67"/>
     </row>
     <row r="55" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="175"/>
-      <c r="B55" s="119" t="s">
+      <c r="A55" s="169"/>
+      <c r="B55" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C55" t="s">
@@ -12697,7 +12569,7 @@
         <v>47</v>
       </c>
       <c r="J55" s="67"/>
-      <c r="K55" s="91" t="s">
+      <c r="K55" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L55" t="s">
@@ -12706,10 +12578,10 @@
       <c r="M55" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q55" s="84"/>
-      <c r="R55" s="84"/>
+      <c r="Q55" s="81"/>
+      <c r="R55" s="81"/>
       <c r="S55" s="67"/>
-      <c r="T55" s="98" t="s">
+      <c r="T55" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U55" t="s">
@@ -12722,8 +12594,8 @@
       <c r="AB55" s="67"/>
     </row>
     <row r="56" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="175"/>
-      <c r="B56" s="119" t="s">
+      <c r="A56" s="169"/>
+      <c r="B56" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C56" t="s">
@@ -12733,7 +12605,7 @@
         <v>47</v>
       </c>
       <c r="J56" s="67"/>
-      <c r="K56" s="91" t="s">
+      <c r="K56" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L56" t="s">
@@ -12742,10 +12614,10 @@
       <c r="M56" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q56" s="84"/>
-      <c r="R56" s="84"/>
+      <c r="Q56" s="81"/>
+      <c r="R56" s="81"/>
       <c r="S56" s="67"/>
-      <c r="T56" s="98" t="s">
+      <c r="T56" s="95" t="s">
         <v>51</v>
       </c>
       <c r="U56" s="58" t="s">
@@ -12758,8 +12630,8 @@
       <c r="AB56" s="67"/>
     </row>
     <row r="57" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="175"/>
-      <c r="B57" s="119" t="s">
+      <c r="A57" s="169"/>
+      <c r="B57" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C57" t="s">
@@ -12769,7 +12641,7 @@
         <v>47</v>
       </c>
       <c r="J57" s="67"/>
-      <c r="K57" s="91" t="s">
+      <c r="K57" s="88" t="s">
         <v>54</v>
       </c>
       <c r="L57" t="s">
@@ -12778,10 +12650,10 @@
       <c r="M57" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="Q57" s="84"/>
-      <c r="R57" s="84"/>
+      <c r="Q57" s="81"/>
+      <c r="R57" s="81"/>
       <c r="S57" s="67"/>
-      <c r="T57" s="99" t="s">
+      <c r="T57" s="96" t="s">
         <v>51</v>
       </c>
       <c r="U57" s="58" t="s">
@@ -12790,16 +12662,16 @@
       <c r="V57" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W57" s="152"/>
-      <c r="X57" s="80"/>
+      <c r="W57" s="149"/>
+      <c r="X57" s="77"/>
       <c r="Y57" s="1"/>
-      <c r="Z57" s="80"/>
-      <c r="AA57" s="116"/>
+      <c r="Z57" s="77"/>
+      <c r="AA57" s="113"/>
       <c r="AB57" s="68"/>
     </row>
     <row r="58" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="175"/>
-      <c r="B58" s="119" t="s">
+      <c r="A58" s="169"/>
+      <c r="B58" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C58" t="s">
@@ -12809,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="J58" s="67"/>
-      <c r="K58" s="93" t="s">
+      <c r="K58" s="90" t="s">
         <v>54</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -12818,10 +12690,10 @@
       <c r="M58" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="Q58" s="84"/>
-      <c r="R58" s="84"/>
+      <c r="Q58" s="81"/>
+      <c r="R58" s="81"/>
       <c r="S58" s="67"/>
-      <c r="T58" s="100" t="s">
+      <c r="T58" s="97" t="s">
         <v>52</v>
       </c>
       <c r="U58" s="2" t="s">
@@ -12830,13 +12702,13 @@
       <c r="V58" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W58" s="153"/>
+      <c r="W58" s="150"/>
       <c r="Z58" s="6"/>
       <c r="AB58" s="67"/>
     </row>
     <row r="59" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="175"/>
-      <c r="B59" s="119" t="s">
+      <c r="A59" s="169"/>
+      <c r="B59" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C59" t="s">
@@ -12846,7 +12718,7 @@
         <v>36</v>
       </c>
       <c r="J59" s="67"/>
-      <c r="K59" s="104" t="s">
+      <c r="K59" s="101" t="s">
         <v>92</v>
       </c>
       <c r="L59" s="4" t="s">
@@ -12855,15 +12727,15 @@
       <c r="M59" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="N59" s="83"/>
+      <c r="N59" s="80"/>
       <c r="O59" s="4"/>
       <c r="P59" s="4"/>
-      <c r="Q59" s="122"/>
-      <c r="R59" s="122"/>
+      <c r="Q59" s="119"/>
+      <c r="R59" s="119"/>
       <c r="S59" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="T59" s="101" t="s">
+      <c r="T59" s="98" t="s">
         <v>52</v>
       </c>
       <c r="U59" s="60" t="s">
@@ -12872,23 +12744,23 @@
       <c r="V59" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W59" s="152"/>
+      <c r="W59" s="149"/>
       <c r="Z59" s="6"/>
       <c r="AB59" s="67"/>
     </row>
     <row r="60" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="175"/>
-      <c r="B60" s="119" t="s">
+      <c r="A60" s="169"/>
+      <c r="B60" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D60" s="53" t="s">
         <v>36</v>
       </c>
       <c r="J60" s="67"/>
-      <c r="K60" s="99" t="s">
+      <c r="K60" s="96" t="s">
         <v>93</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -12897,15 +12769,15 @@
       <c r="M60" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="N60" s="80"/>
+      <c r="N60" s="77"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
-      <c r="Q60" s="87"/>
-      <c r="R60" s="87"/>
+      <c r="Q60" s="84"/>
+      <c r="R60" s="84"/>
       <c r="S60" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="T60" s="102" t="s">
+      <c r="T60" s="99" t="s">
         <v>52</v>
       </c>
       <c r="U60" s="61" t="s">
@@ -12914,38 +12786,38 @@
       <c r="V60" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="W60" s="154"/>
+      <c r="W60" s="151"/>
       <c r="Z60" s="6"/>
       <c r="AB60" s="67"/>
     </row>
     <row r="61" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="175"/>
-      <c r="B61" s="119" t="s">
+      <c r="A61" s="169"/>
+      <c r="B61" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C61" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D61" s="53" t="s">
         <v>36</v>
       </c>
       <c r="J61" s="67"/>
-      <c r="K61" s="104" t="s">
-        <v>155</v>
+      <c r="K61" s="101" t="s">
+        <v>152</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M61" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="N61" s="83"/>
+        <v>154</v>
+      </c>
+      <c r="N61" s="80"/>
       <c r="O61" s="4"/>
       <c r="P61" s="4"/>
-      <c r="Q61" s="122"/>
-      <c r="R61" s="151"/>
-      <c r="S61" s="134"/>
-      <c r="T61" s="101" t="s">
+      <c r="Q61" s="119"/>
+      <c r="R61" s="148"/>
+      <c r="S61" s="131"/>
+      <c r="T61" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U61" s="57" t="s">
@@ -12954,20 +12826,20 @@
       <c r="V61" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W61" s="152"/>
-      <c r="X61" s="79"/>
+      <c r="W61" s="149"/>
+      <c r="X61" s="76"/>
       <c r="Y61" s="3"/>
-      <c r="Z61" s="79"/>
-      <c r="AA61" s="115"/>
+      <c r="Z61" s="76"/>
+      <c r="AA61" s="112"/>
       <c r="AB61" s="69"/>
     </row>
     <row r="62" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="175"/>
-      <c r="B62" s="119" t="s">
+      <c r="A62" s="169"/>
+      <c r="B62" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D62" s="53" t="s">
         <v>47</v>
@@ -12975,11 +12847,11 @@
       <c r="E62" s="49"/>
       <c r="G62" s="6"/>
       <c r="J62" s="67"/>
-      <c r="K62" s="145"/>
+      <c r="K62" s="142"/>
       <c r="M62" s="6"/>
-      <c r="Q62" s="84"/>
-      <c r="R62" s="84"/>
-      <c r="T62" s="101" t="s">
+      <c r="Q62" s="81"/>
+      <c r="R62" s="81"/>
+      <c r="T62" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U62" s="58" t="s">
@@ -12988,17 +12860,17 @@
       <c r="V62" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W62" s="152"/>
+      <c r="W62" s="149"/>
       <c r="Z62" s="6"/>
       <c r="AB62" s="67"/>
     </row>
     <row r="63" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="175"/>
-      <c r="B63" s="119" t="s">
+      <c r="A63" s="169"/>
+      <c r="B63" s="116" t="s">
         <v>51</v>
       </c>
       <c r="C63" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D63" s="53" t="s">
         <v>47</v>
@@ -13006,9 +12878,9 @@
       <c r="E63" s="49"/>
       <c r="G63" s="6"/>
       <c r="J63" s="67"/>
-      <c r="K63" s="145"/>
+      <c r="K63" s="142"/>
       <c r="M63" s="6"/>
-      <c r="T63" s="101" t="s">
+      <c r="T63" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U63" s="58" t="s">
@@ -13017,13 +12889,13 @@
       <c r="V63" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W63" s="152"/>
+      <c r="W63" s="149"/>
       <c r="Z63" s="6"/>
       <c r="AB63" s="67"/>
     </row>
     <row r="64" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="175"/>
-      <c r="B64" s="120" t="s">
+      <c r="A64" s="169"/>
+      <c r="B64" s="117" t="s">
         <v>52</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -13033,12 +12905,12 @@
         <v>47</v>
       </c>
       <c r="E64" s="50"/>
-      <c r="F64" s="79"/>
+      <c r="F64" s="76"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="79"/>
-      <c r="I64" s="79"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
       <c r="J64" s="69"/>
-      <c r="T64" s="101" t="s">
+      <c r="T64" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U64" s="58" t="s">
@@ -13047,13 +12919,13 @@
       <c r="V64" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W64" s="152"/>
+      <c r="W64" s="149"/>
       <c r="Z64" s="6"/>
       <c r="AB64" s="67"/>
     </row>
     <row r="65" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="175"/>
-      <c r="B65" s="120" t="s">
+      <c r="A65" s="169"/>
+      <c r="B65" s="117" t="s">
         <v>52</v>
       </c>
       <c r="C65" t="s">
@@ -13063,14 +12935,14 @@
         <v>47</v>
       </c>
       <c r="E65" s="51"/>
-      <c r="F65" s="80"/>
+      <c r="F65" s="77"/>
       <c r="G65" s="1"/>
-      <c r="H65" s="80"/>
-      <c r="I65" s="80"/>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
       <c r="J65" s="68"/>
       <c r="K65" s="18"/>
       <c r="S65" s="13"/>
-      <c r="T65" s="101" t="s">
+      <c r="T65" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U65" s="58" t="s">
@@ -13079,13 +12951,13 @@
       <c r="V65" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W65" s="152"/>
+      <c r="W65" s="149"/>
       <c r="Z65" s="6"/>
       <c r="AB65" s="67"/>
     </row>
     <row r="66" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="175"/>
-      <c r="B66" s="120" t="s">
+      <c r="A66" s="169"/>
+      <c r="B66" s="117" t="s">
         <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -13097,7 +12969,7 @@
       <c r="J66" s="67"/>
       <c r="K66" s="18"/>
       <c r="S66" s="13"/>
-      <c r="T66" s="101" t="s">
+      <c r="T66" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U66" s="58" t="s">
@@ -13106,13 +12978,13 @@
       <c r="V66" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W66" s="152"/>
+      <c r="W66" s="149"/>
       <c r="Z66" s="6"/>
       <c r="AB66" s="67"/>
     </row>
     <row r="67" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="175"/>
-      <c r="B67" s="120" t="s">
+      <c r="A67" s="169"/>
+      <c r="B67" s="117" t="s">
         <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -13124,7 +12996,7 @@
       <c r="J67" s="67"/>
       <c r="K67" s="18"/>
       <c r="S67" s="13"/>
-      <c r="T67" s="101" t="s">
+      <c r="T67" s="98" t="s">
         <v>53</v>
       </c>
       <c r="U67" s="58" t="s">
@@ -13133,13 +13005,13 @@
       <c r="V67" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W67" s="152"/>
+      <c r="W67" s="149"/>
       <c r="Z67" s="6"/>
       <c r="AB67" s="67"/>
     </row>
     <row r="68" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="175"/>
-      <c r="B68" s="119" t="s">
+      <c r="A68" s="169"/>
+      <c r="B68" s="116" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -13149,16 +13021,16 @@
         <v>47</v>
       </c>
       <c r="E68" s="50"/>
-      <c r="F68" s="79"/>
+      <c r="F68" s="76"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="79"/>
+      <c r="H68" s="76"/>
+      <c r="I68" s="76"/>
       <c r="J68" s="71" t="s">
         <v>106</v>
       </c>
       <c r="K68" s="18"/>
       <c r="S68" s="13"/>
-      <c r="T68" s="102" t="s">
+      <c r="T68" s="99" t="s">
         <v>53</v>
       </c>
       <c r="U68" s="59" t="s">
@@ -13167,16 +13039,16 @@
       <c r="V68" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="W68" s="152"/>
-      <c r="X68" s="80"/>
+      <c r="W68" s="149"/>
+      <c r="X68" s="77"/>
       <c r="Y68" s="1"/>
-      <c r="Z68" s="80"/>
-      <c r="AA68" s="116"/>
+      <c r="Z68" s="77"/>
+      <c r="AA68" s="113"/>
       <c r="AB68" s="68"/>
     </row>
     <row r="69" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="175"/>
-      <c r="B69" s="119" t="s">
+      <c r="A69" s="169"/>
+      <c r="B69" s="116" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -13189,7 +13061,7 @@
       <c r="J69" s="67"/>
       <c r="K69" s="17"/>
       <c r="S69" s="13"/>
-      <c r="T69" s="98" t="s">
+      <c r="T69" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U69" s="58" t="s">
@@ -13198,15 +13070,15 @@
       <c r="V69" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W69" s="153"/>
+      <c r="W69" s="150"/>
       <c r="Z69" s="6"/>
       <c r="AB69" s="67" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="175"/>
-      <c r="B70" s="119" t="s">
+      <c r="A70" s="169"/>
+      <c r="B70" s="116" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="21" t="s">
@@ -13216,14 +13088,14 @@
         <v>58</v>
       </c>
       <c r="E70" s="51"/>
-      <c r="F70" s="80"/>
+      <c r="F70" s="77"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="80"/>
-      <c r="I70" s="80"/>
+      <c r="H70" s="77"/>
+      <c r="I70" s="77"/>
       <c r="J70" s="68"/>
       <c r="K70" s="17"/>
       <c r="S70" s="13"/>
-      <c r="T70" s="98" t="s">
+      <c r="T70" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U70" s="63" t="s">
@@ -13232,13 +13104,13 @@
       <c r="V70" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W70" s="152"/>
+      <c r="W70" s="149"/>
       <c r="Z70" s="6"/>
       <c r="AB70" s="67"/>
     </row>
     <row r="71" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="175"/>
-      <c r="B71" s="119" t="s">
+      <c r="A71" s="169"/>
+      <c r="B71" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -13247,16 +13119,16 @@
       <c r="D71" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="F71" s="79"/>
+      <c r="F71" s="76"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="79"/>
-      <c r="I71" s="79"/>
+      <c r="H71" s="76"/>
+      <c r="I71" s="76"/>
       <c r="J71" s="71" t="s">
         <v>106</v>
       </c>
       <c r="K71" s="18"/>
       <c r="S71" s="13"/>
-      <c r="T71" s="98" t="s">
+      <c r="T71" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U71" s="63" t="s">
@@ -13265,13 +13137,13 @@
       <c r="V71" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="W71" s="152"/>
+      <c r="W71" s="149"/>
       <c r="Z71" s="6"/>
       <c r="AB71" s="67"/>
     </row>
     <row r="72" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="175"/>
-      <c r="B72" s="119" t="s">
+      <c r="A72" s="169"/>
+      <c r="B72" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C72" s="8" t="s">
@@ -13283,7 +13155,7 @@
       <c r="J72" s="67"/>
       <c r="K72" s="18"/>
       <c r="S72" s="13"/>
-      <c r="T72" s="98" t="s">
+      <c r="T72" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U72" s="64" t="s">
@@ -13292,13 +13164,13 @@
       <c r="V72" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W72" s="152"/>
+      <c r="W72" s="149"/>
       <c r="Z72" s="6"/>
       <c r="AB72" s="67"/>
     </row>
     <row r="73" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="175"/>
-      <c r="B73" s="119" t="s">
+      <c r="A73" s="169"/>
+      <c r="B73" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -13310,7 +13182,7 @@
       <c r="J73" s="67"/>
       <c r="K73" s="18"/>
       <c r="S73" s="13"/>
-      <c r="T73" s="98" t="s">
+      <c r="T73" s="95" t="s">
         <v>74</v>
       </c>
       <c r="U73" s="64" t="s">
@@ -13319,13 +13191,13 @@
       <c r="V73" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="W73" s="154"/>
+      <c r="W73" s="151"/>
       <c r="Z73" s="6"/>
       <c r="AB73" s="67"/>
     </row>
     <row r="74" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="175"/>
-      <c r="B74" s="119" t="s">
+      <c r="A74" s="169"/>
+      <c r="B74" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C74" s="8" t="s">
@@ -13338,27 +13210,27 @@
       <c r="K74" s="17"/>
       <c r="M74" s="6"/>
       <c r="S74" s="13"/>
-      <c r="T74" s="103" t="s">
-        <v>149</v>
+      <c r="T74" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="U74" s="57" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="V74" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W74" s="152"/>
-      <c r="X74" s="79"/>
+      <c r="W74" s="149"/>
+      <c r="X74" s="76"/>
       <c r="Y74" s="3"/>
-      <c r="Z74" s="79"/>
-      <c r="AA74" s="115"/>
+      <c r="Z74" s="76"/>
+      <c r="AA74" s="112"/>
       <c r="AB74" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="175"/>
-      <c r="B75" s="119" t="s">
+      <c r="A75" s="169"/>
+      <c r="B75" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -13370,8 +13242,8 @@
       <c r="J75" s="67"/>
       <c r="K75" s="17"/>
       <c r="S75" s="13"/>
-      <c r="T75" s="98" t="s">
-        <v>149</v>
+      <c r="T75" s="95" t="s">
+        <v>146</v>
       </c>
       <c r="U75" s="63" t="s">
         <v>75</v>
@@ -13379,13 +13251,13 @@
       <c r="V75" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W75" s="152"/>
+      <c r="W75" s="149"/>
       <c r="Z75" s="6"/>
       <c r="AB75" s="67"/>
     </row>
     <row r="76" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="175"/>
-      <c r="B76" s="119" t="s">
+      <c r="A76" s="169"/>
+      <c r="B76" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -13398,8 +13270,8 @@
       <c r="K76" s="17"/>
       <c r="M76" s="6"/>
       <c r="S76" s="13"/>
-      <c r="T76" s="99" t="s">
-        <v>149</v>
+      <c r="T76" s="96" t="s">
+        <v>146</v>
       </c>
       <c r="U76" s="65" t="s">
         <v>76</v>
@@ -13407,16 +13279,16 @@
       <c r="V76" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="W76" s="152"/>
-      <c r="X76" s="80"/>
+      <c r="W76" s="149"/>
+      <c r="X76" s="77"/>
       <c r="Y76" s="1"/>
-      <c r="Z76" s="80"/>
-      <c r="AA76" s="116"/>
+      <c r="Z76" s="77"/>
+      <c r="AA76" s="113"/>
       <c r="AB76" s="68"/>
     </row>
     <row r="77" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="175"/>
-      <c r="B77" s="119" t="s">
+      <c r="A77" s="169"/>
+      <c r="B77" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -13429,27 +13301,27 @@
       <c r="K77" s="17"/>
       <c r="M77" s="6"/>
       <c r="S77" s="13"/>
-      <c r="T77" s="103" t="s">
-        <v>150</v>
+      <c r="T77" s="100" t="s">
+        <v>147</v>
       </c>
       <c r="U77" s="57" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="V77" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="W77" s="153"/>
-      <c r="X77" s="79"/>
+      <c r="W77" s="150"/>
+      <c r="X77" s="76"/>
       <c r="Y77" s="3"/>
-      <c r="Z77" s="79"/>
-      <c r="AA77" s="115"/>
+      <c r="Z77" s="76"/>
+      <c r="AA77" s="112"/>
       <c r="AB77" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="175"/>
-      <c r="B78" s="119" t="s">
+      <c r="A78" s="169"/>
+      <c r="B78" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="8" t="s">
@@ -13462,8 +13334,8 @@
       <c r="K78" s="17"/>
       <c r="M78" s="6"/>
       <c r="S78" s="13"/>
-      <c r="T78" s="98" t="s">
-        <v>150</v>
+      <c r="T78" s="95" t="s">
+        <v>147</v>
       </c>
       <c r="U78" s="63" t="s">
         <v>75</v>
@@ -13471,13 +13343,13 @@
       <c r="V78" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W78" s="152"/>
+      <c r="W78" s="149"/>
       <c r="Z78" s="6"/>
       <c r="AB78" s="67"/>
     </row>
     <row r="79" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="175"/>
-      <c r="B79" s="119" t="s">
+      <c r="A79" s="169"/>
+      <c r="B79" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="8" t="s">
@@ -13489,8 +13361,8 @@
       <c r="J79" s="67"/>
       <c r="K79" s="17"/>
       <c r="S79" s="13"/>
-      <c r="T79" s="99" t="s">
-        <v>150</v>
+      <c r="T79" s="96" t="s">
+        <v>147</v>
       </c>
       <c r="U79" s="65" t="s">
         <v>76</v>
@@ -13498,16 +13370,16 @@
       <c r="V79" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="W79" s="154"/>
-      <c r="X79" s="80"/>
+      <c r="W79" s="151"/>
+      <c r="X79" s="77"/>
       <c r="Y79" s="1"/>
-      <c r="Z79" s="80"/>
-      <c r="AA79" s="116"/>
+      <c r="Z79" s="77"/>
+      <c r="AA79" s="113"/>
       <c r="AB79" s="68"/>
     </row>
     <row r="80" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="175"/>
-      <c r="B80" s="119" t="s">
+      <c r="A80" s="169"/>
+      <c r="B80" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -13521,8 +13393,8 @@
       <c r="S80" s="13"/>
     </row>
     <row r="81" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="175"/>
-      <c r="B81" s="119" t="s">
+      <c r="A81" s="169"/>
+      <c r="B81" s="116" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="21" t="s">
@@ -13531,17 +13403,17 @@
       <c r="D81" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="F81" s="80"/>
+      <c r="F81" s="77"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
+      <c r="H81" s="77"/>
+      <c r="I81" s="77"/>
       <c r="J81" s="68"/>
       <c r="K81" s="18"/>
       <c r="S81" s="13"/>
     </row>
     <row r="82" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="175"/>
-      <c r="B82" s="119" t="s">
+      <c r="A82" s="169"/>
+      <c r="B82" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C82" t="s">
@@ -13559,8 +13431,8 @@
       <c r="S82" s="13"/>
     </row>
     <row r="83" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="175"/>
-      <c r="B83" s="119" t="s">
+      <c r="A83" s="169"/>
+      <c r="B83" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="14" t="s">
@@ -13574,8 +13446,8 @@
       <c r="S83" s="13"/>
     </row>
     <row r="84" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="175"/>
-      <c r="B84" s="119" t="s">
+      <c r="A84" s="169"/>
+      <c r="B84" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C84" s="14" t="s">
@@ -13591,8 +13463,8 @@
       <c r="AB84" s="13"/>
     </row>
     <row r="85" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="175"/>
-      <c r="B85" s="119" t="s">
+      <c r="A85" s="169"/>
+      <c r="B85" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C85" s="14" t="s">
@@ -13608,8 +13480,8 @@
       <c r="AB85" s="13"/>
     </row>
     <row r="86" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="175"/>
-      <c r="B86" s="119" t="s">
+      <c r="A86" s="169"/>
+      <c r="B86" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C86" s="14" t="s">
@@ -13625,8 +13497,8 @@
       <c r="AB86" s="13"/>
     </row>
     <row r="87" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="175"/>
-      <c r="B87" s="119" t="s">
+      <c r="A87" s="169"/>
+      <c r="B87" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C87" s="14" t="s">
@@ -13642,8 +13514,8 @@
       <c r="AB87" s="13"/>
     </row>
     <row r="88" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="175"/>
-      <c r="B88" s="119" t="s">
+      <c r="A88" s="169"/>
+      <c r="B88" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C88" s="14" t="s">
@@ -13659,8 +13531,8 @@
       <c r="AB88" s="13"/>
     </row>
     <row r="89" spans="1:28" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="175"/>
-      <c r="B89" s="104" t="s">
+      <c r="A89" s="169"/>
+      <c r="B89" s="101" t="s">
         <v>68</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -13676,8 +13548,8 @@
       <c r="AB89" s="13"/>
     </row>
     <row r="90" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="175"/>
-      <c r="B90" s="119" t="s">
+      <c r="A90" s="169"/>
+      <c r="B90" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="14" t="s">
@@ -13694,8 +13566,8 @@
       <c r="AB90" s="13"/>
     </row>
     <row r="91" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="175"/>
-      <c r="B91" s="119" t="s">
+      <c r="A91" s="169"/>
+      <c r="B91" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C91" s="14" t="s">
@@ -13712,8 +13584,8 @@
       <c r="AB91" s="13"/>
     </row>
     <row r="92" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="175"/>
-      <c r="B92" s="119" t="s">
+      <c r="A92" s="169"/>
+      <c r="B92" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="14" t="s">
@@ -13730,8 +13602,8 @@
       <c r="AB92" s="13"/>
     </row>
     <row r="93" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="175"/>
-      <c r="B93" s="119" t="s">
+      <c r="A93" s="169"/>
+      <c r="B93" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C93" s="14" t="s">
@@ -13748,8 +13620,8 @@
       <c r="AB93" s="13"/>
     </row>
     <row r="94" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="175"/>
-      <c r="B94" s="119" t="s">
+      <c r="A94" s="169"/>
+      <c r="B94" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C94" s="14" t="s">
@@ -13766,8 +13638,8 @@
       <c r="AB94" s="13"/>
     </row>
     <row r="95" spans="1:28" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="175"/>
-      <c r="B95" s="119" t="s">
+      <c r="A95" s="169"/>
+      <c r="B95" s="116" t="s">
         <v>68</v>
       </c>
       <c r="C95" s="14" t="s">
@@ -13783,8 +13655,8 @@
       <c r="AB95" s="13"/>
     </row>
     <row r="96" spans="1:28" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="176"/>
-      <c r="B96" s="121" t="s">
+      <c r="A96" s="170"/>
+      <c r="B96" s="118" t="s">
         <v>68</v>
       </c>
       <c r="C96" s="20" t="s">
@@ -13793,16 +13665,16 @@
       <c r="D96" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="E96" s="81"/>
-      <c r="F96" s="81"/>
+      <c r="E96" s="78"/>
+      <c r="F96" s="78"/>
       <c r="G96" s="15"/>
-      <c r="H96" s="81"/>
-      <c r="I96" s="81"/>
+      <c r="H96" s="78"/>
+      <c r="I96" s="78"/>
       <c r="J96" s="72"/>
       <c r="K96" s="19"/>
       <c r="L96" s="15"/>
       <c r="M96" s="15"/>
-      <c r="N96" s="81"/>
+      <c r="N96" s="78"/>
       <c r="O96" s="15"/>
       <c r="P96" s="15"/>
       <c r="Q96" s="15"/>
@@ -13811,11 +13683,11 @@
       <c r="T96" s="19"/>
       <c r="U96" s="15"/>
       <c r="V96" s="15"/>
-      <c r="W96" s="117"/>
-      <c r="X96" s="81"/>
+      <c r="W96" s="114"/>
+      <c r="X96" s="78"/>
       <c r="Y96" s="15"/>
       <c r="Z96" s="15"/>
-      <c r="AA96" s="117"/>
+      <c r="AA96" s="114"/>
       <c r="AB96" s="16"/>
     </row>
     <row r="97" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -13846,27 +13718,27 @@
       <c r="A101" s="46"/>
       <c r="B101" s="45"/>
       <c r="C101" s="5"/>
-      <c r="D101" s="149"/>
+      <c r="D101" s="146"/>
     </row>
     <row r="102" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="46"/>
       <c r="B102" s="45"/>
       <c r="C102" s="5"/>
-      <c r="D102" s="149"/>
+      <c r="D102" s="146"/>
       <c r="V102" s="6"/>
     </row>
     <row r="103" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="46"/>
       <c r="B103" s="45"/>
       <c r="C103" s="5"/>
-      <c r="D103" s="149"/>
+      <c r="D103" s="146"/>
       <c r="V103" s="6"/>
     </row>
     <row r="104" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="46"/>
       <c r="B104" s="45"/>
       <c r="C104" s="5"/>
-      <c r="D104" s="149"/>
+      <c r="D104" s="146"/>
       <c r="V104" s="6"/>
     </row>
     <row r="105" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -13988,208 +13860,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B7AF6B-56A3-432A-8534-C9963FC864C1}">
-  <dimension ref="B2:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2.54296875" customWidth="1"/>
-    <col min="2" max="2" width="23.54296875" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="24.54296875" customWidth="1"/>
-    <col min="5" max="5" width="38.81640625" customWidth="1"/>
-    <col min="6" max="6" width="38.26953125" customWidth="1"/>
-    <col min="7" max="7" width="19.90625" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C2" s="179" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="179"/>
-    </row>
-    <row r="3" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="75"/>
-      <c r="C3" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="73" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="165" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="166">
-        <f>7170000+5176000</f>
-        <v>12346000</v>
-      </c>
-      <c r="D4" s="166">
-        <v>26894203.602000002</v>
-      </c>
-      <c r="E4" s="166">
-        <f>2167526+25231645.82</f>
-        <v>27399171.82</v>
-      </c>
-      <c r="F4" s="84">
-        <v>3215400.4385939501</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="145" x14ac:dyDescent="0.35">
-      <c r="B5" s="156" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="157" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="157" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="157" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="157" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="6"/>
-      <c r="C6" s="159">
-        <f>C4/(C4+E4)</f>
-        <v>0.31062892509090678</v>
-      </c>
-      <c r="D6" s="159">
-        <f>D4/(D4+F4)</f>
-        <v>0.89321013872321509</v>
-      </c>
-      <c r="E6" s="159">
-        <f>E4/(C4+E4)</f>
-        <v>0.68937107490909322</v>
-      </c>
-      <c r="F6" s="159">
-        <f>F4/(F4+D4)</f>
-        <v>0.1067898612767849</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B8" s="6"/>
-      <c r="C8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B9" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9">
-        <v>327065</v>
-      </c>
-      <c r="D9">
-        <v>259704</v>
-      </c>
-      <c r="E9">
-        <v>294371</v>
-      </c>
-      <c r="F9">
-        <v>772657</v>
-      </c>
-      <c r="G9">
-        <v>208621</v>
-      </c>
-      <c r="H9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="158" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B10" s="6"/>
-      <c r="G10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11">
-        <f>(C9+(D9+E9+G9*0.5)*C6)*1.2</f>
-        <v>637894.29619252705</v>
-      </c>
-      <c r="G11">
-        <f>(C9+D9+E9+F9+G9*0.5)*1.2</f>
-        <v>2109729</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12">
-        <f>(F9+(D9+E9+G9*0.5)*E6)*1.2</f>
-        <v>1471834.7038074729</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B13" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13">
-        <f>SUM(C11:C12)</f>
-        <v>2109729</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>